--- a/security-testing/scripts/Sentinel_Load_Test_Report.xlsx
+++ b/security-testing/scripts/Sentinel_Load_Test_Report.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 10:51:39</t>
+          <t>2026-06-22 05:44:41</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>5.7 ms</t>
+          <t>5.3 ms</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>50.1 ms</t>
+          <t>49.4 ms</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>94.8 ms</t>
+          <t>93.6 ms</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>92.0 ms</t>
+          <t>89.7 ms</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -797,12 +797,12 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -811,19 +811,19 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>48.5</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>94.8</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -848,19 +848,19 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>52.6</v>
+        <v>48.9</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>94.40000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
@@ -871,12 +871,12 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -885,19 +885,19 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1.05</v>
+        <v>0.92</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>51.6</v>
+        <v>49.8</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>93</v>
+        <v>93.3</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
@@ -908,12 +908,12 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -922,19 +922,19 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1.03</v>
+        <v>0.88</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>46.5</v>
+        <v>50</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>94.3</v>
+        <v>93</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -959,19 +959,19 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.03</v>
+        <v>1.63</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>6.9</v>
+        <v>5.5</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>52.6</v>
+        <v>49.6</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>94.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
@@ -1051,29 +1051,29 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.971</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>User-40</t>
+          <t>User-13</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F2" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>20.66</v>
+        <v>36.55</v>
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
@@ -1087,29 +1087,29 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.971</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>User-50</t>
+          <t>User-56</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>50.4</v>
+        <v>15.56</v>
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
@@ -1123,29 +1123,29 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.971</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>User-42</t>
+          <t>User-80</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>44.99</v>
+        <v>35.67</v>
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.971</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>User-12</t>
+          <t>User-55</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1181,7 +1181,7 @@
         <v>200</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>76.65000000000001</v>
+        <v>33.35</v>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
@@ -1195,29 +1195,29 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.971</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>User-71</t>
+          <t>User-45</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>14.81</v>
+        <v>67.2</v>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
@@ -1231,29 +1231,29 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.971</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>User-32</t>
+          <t>User-80</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>61.17</v>
+        <v>13.83</v>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
@@ -1267,29 +1267,29 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.971</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>User-30</t>
+          <t>User-68</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>51.88</v>
+        <v>42.79</v>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
@@ -1303,29 +1303,29 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.971</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>User-7</t>
+          <t>User-40</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>25.26</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
@@ -1339,29 +1339,29 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.971</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>User-60</t>
+          <t>User-9</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>86.06999999999999</v>
+        <v>90.06</v>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
@@ -1375,29 +1375,29 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.971</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>User-73</t>
+          <t>User-12</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>42.38</v>
+        <v>41.7</v>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
@@ -1411,29 +1411,29 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.971</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>User-1</t>
+          <t>User-97</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>62.9</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
@@ -1447,29 +1447,29 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.971</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>User-53</t>
+          <t>User-41</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>71.93000000000001</v>
+        <v>64.78</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -1483,29 +1483,29 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.971</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>User-42</t>
+          <t>User-67</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>12.75</v>
+        <v>67.22</v>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
@@ -1519,29 +1519,29 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.971</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>User-61</t>
+          <t>User-36</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>70.59</v>
+        <v>35.63</v>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
@@ -1555,29 +1555,29 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.971</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>User-34</t>
+          <t>User-2</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>34.25</v>
+        <v>91.56</v>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
@@ -1591,29 +1591,29 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>User-93</t>
+          <t>User-5</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>40.93</v>
+        <v>37.12</v>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
@@ -1627,29 +1627,29 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>User-17</t>
+          <t>User-76</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>76.93000000000001</v>
+        <v>47.88</v>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
@@ -1663,29 +1663,29 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>User-34</t>
+          <t>User-77</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>10.07</v>
+        <v>87.16</v>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
@@ -1699,29 +1699,29 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>User-52</t>
+          <t>User-36</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>52.53</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
@@ -1735,29 +1735,29 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>User-16</t>
+          <t>User-49</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F21" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>56.11</v>
+        <v>6.04</v>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
@@ -1771,12 +1771,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>User-34</t>
+          <t>User-39</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1793,7 +1793,7 @@
         <v>200</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>27.76</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
@@ -1807,29 +1807,29 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>User-8</t>
+          <t>User-17</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>30.14</v>
+        <v>83.09</v>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
@@ -1843,29 +1843,29 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>User-44</t>
+          <t>User-39</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>68.08</v>
+        <v>92.03</v>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>User-39</t>
+          <t>User-67</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1901,7 +1901,7 @@
         <v>200</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>94.56999999999999</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
@@ -1915,29 +1915,29 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>User-71</t>
+          <t>User-37</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>72.36</v>
+        <v>36.05</v>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
@@ -1951,29 +1951,29 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>User-86</t>
+          <t>User-88</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>59.96</v>
+        <v>32.7</v>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
@@ -1987,29 +1987,29 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>User-47</t>
+          <t>User-37</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>74.08</v>
+        <v>45.21</v>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
@@ -2023,29 +2023,29 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>User-40</t>
+          <t>User-22</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>49.45</v>
+        <v>56.44</v>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
@@ -2059,29 +2059,29 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>User-68</t>
+          <t>User-20</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>65.01000000000001</v>
+        <v>58.42</v>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
@@ -2095,29 +2095,29 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>User-41</t>
+          <t>User-56</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>41.65</v>
+        <v>57.45</v>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
@@ -2131,29 +2131,29 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>User-54</t>
+          <t>User-92</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>41.39</v>
+        <v>78.66</v>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
@@ -2167,29 +2167,29 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>User-56</t>
+          <t>User-78</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F33" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>57.2</v>
+        <v>56.94</v>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
@@ -2203,29 +2203,29 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>User-1</t>
+          <t>User-12</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F34" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>42.58</v>
+        <v>59.14</v>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
@@ -2239,12 +2239,12 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>User-67</t>
+          <t>User-94</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2261,7 +2261,7 @@
         <v>200</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>87.48999999999999</v>
+        <v>82.38</v>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
@@ -2275,29 +2275,29 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>User-2</t>
+          <t>User-96</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F36" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>51.98</v>
+        <v>79.22</v>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
@@ -2311,29 +2311,29 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>User-38</t>
+          <t>User-13</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>58.11</v>
+        <v>64.27</v>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
@@ -2347,29 +2347,29 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>User-70</t>
+          <t>User-55</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F38" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>91.97</v>
+        <v>78.53</v>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
@@ -2383,29 +2383,29 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>User-93</t>
+          <t>User-41</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F39" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>49.23</v>
+        <v>65.56</v>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
@@ -2419,29 +2419,29 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>User-26</t>
+          <t>User-18</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>40.25</v>
+        <v>43.87</v>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
@@ -2455,29 +2455,29 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>User-1</t>
+          <t>User-81</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>18.46</v>
+        <v>43.97</v>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
@@ -2491,29 +2491,29 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>User-64</t>
+          <t>User-71</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>35.99</v>
+        <v>37.91</v>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
@@ -2527,29 +2527,29 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>User-85</t>
+          <t>User-27</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>19.92</v>
+        <v>82.8</v>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>User-90</t>
+          <t>User-67</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2585,7 +2585,7 @@
         <v>200</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>46.77</v>
+        <v>49.34</v>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
@@ -2599,29 +2599,29 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>User-84</t>
+          <t>User-95</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>77.5</v>
+        <v>34.84</v>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
@@ -2635,29 +2635,29 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>User-7</t>
+          <t>User-67</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>65.05</v>
+        <v>92.64</v>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
@@ -2671,12 +2671,12 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>User-54</t>
+          <t>User-72</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2693,7 +2693,7 @@
         <v>200</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>87.84</v>
+        <v>49.47</v>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
@@ -2707,29 +2707,29 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>User-34</t>
+          <t>User-65</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>86.06999999999999</v>
+        <v>42.57</v>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
@@ -2743,29 +2743,29 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>User-22</t>
+          <t>User-17</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F49" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>13.14</v>
+        <v>16.18</v>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
@@ -2779,29 +2779,29 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>User-70</t>
+          <t>User-88</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F50" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>61.82</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
@@ -2815,29 +2815,29 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>User-95</t>
+          <t>User-33</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F51" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>33.38</v>
+        <v>10.22</v>
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -2873,7 +2873,7 @@
         <v>200</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>42.99</v>
+        <v>64.12</v>
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
@@ -2887,29 +2887,29 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>User-70</t>
+          <t>User-6</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F53" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>12.98</v>
+        <v>53.09</v>
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
@@ -2923,29 +2923,29 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>User-94</t>
+          <t>User-55</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F54" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>25.06</v>
+        <v>41.65</v>
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
@@ -2959,29 +2959,29 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>User-2</t>
+          <t>User-93</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F55" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>17.8</v>
+        <v>31.77</v>
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
@@ -2995,29 +2995,29 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>User-34</t>
+          <t>User-15</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F56" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>67.11</v>
+        <v>14.45</v>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
@@ -3031,29 +3031,29 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>User-15</t>
+          <t>User-70</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F57" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>83.64</v>
+        <v>34.69</v>
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
@@ -3067,29 +3067,29 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>User-82</t>
+          <t>User-14</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F58" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>81.02</v>
+        <v>93.41</v>
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
@@ -3103,29 +3103,29 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>User-83</t>
+          <t>User-37</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F59" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>17.34</v>
+        <v>88.61</v>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
@@ -3139,29 +3139,29 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>User-15</t>
+          <t>User-26</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F60" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>8.380000000000001</v>
+        <v>71.06</v>
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
@@ -3175,29 +3175,29 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>User-32</t>
+          <t>User-31</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F61" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>8.41</v>
+        <v>45.95</v>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>User-85</t>
+          <t>User-99</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -3233,7 +3233,7 @@
         <v>200</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>56.86</v>
+        <v>7</v>
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
@@ -3247,29 +3247,29 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>User-59</t>
+          <t>User-49</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F63" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>52.59</v>
+        <v>90.3</v>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
@@ -3283,29 +3283,29 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>User-49</t>
+          <t>User-43</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F64" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>94.27</v>
+        <v>26.52</v>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
@@ -3319,12 +3319,12 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>User-12</t>
+          <t>User-52</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -3341,7 +3341,7 @@
         <v>200</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>46.92</v>
+        <v>54.13</v>
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
@@ -3355,29 +3355,29 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>User-1</t>
+          <t>User-52</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F66" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>9.25</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
@@ -3391,12 +3391,12 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.030</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>User-43</t>
+          <t>User-47</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -3413,7 +3413,7 @@
         <v>200</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>94.84</v>
+        <v>21.18</v>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
@@ -3427,29 +3427,29 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>User-71</t>
+          <t>User-54</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F68" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>44.34</v>
+        <v>82.75</v>
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
@@ -3463,12 +3463,12 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>User-94</t>
+          <t>User-73</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -3485,7 +3485,7 @@
         <v>200</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>41.77</v>
+        <v>44</v>
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
@@ -3499,12 +3499,12 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>User-20</t>
+          <t>User-68</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -3521,7 +3521,7 @@
         <v>200</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>33.82</v>
+        <v>76.92</v>
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
@@ -3535,12 +3535,12 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>User-36</t>
+          <t>User-15</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -3557,7 +3557,7 @@
         <v>200</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>89.01000000000001</v>
+        <v>36.26</v>
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
@@ -3571,29 +3571,29 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>User-75</t>
+          <t>User-92</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F72" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>39.56</v>
+        <v>8.26</v>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
@@ -3607,29 +3607,29 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>User-79</t>
+          <t>User-58</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F73" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>83.65000000000001</v>
+        <v>7.91</v>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
@@ -3643,29 +3643,29 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>User-49</t>
+          <t>User-41</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F74" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>28.09</v>
+        <v>26.25</v>
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
@@ -3679,29 +3679,29 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>User-2</t>
+          <t>User-74</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F75" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>6.92</v>
+        <v>51.22</v>
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
@@ -3715,29 +3715,29 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>User-47</t>
+          <t>User-94</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F76" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>93.02</v>
+        <v>25.61</v>
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
@@ -3751,29 +3751,29 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>User-86</t>
+          <t>User-73</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F77" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>88.84</v>
+        <v>48.17</v>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
@@ -3787,29 +3787,29 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>User-57</t>
+          <t>User-44</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F78" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>37.22</v>
+        <v>62.03</v>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
@@ -3823,29 +3823,29 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>User-50</t>
+          <t>User-71</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F79" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>61.63</v>
+        <v>40.59</v>
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
@@ -3859,29 +3859,29 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.972</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>User-58</t>
+          <t>User-13</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F80" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>19.63</v>
+        <v>31.64</v>
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
@@ -3895,29 +3895,29 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>User-55</t>
+          <t>User-85</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F81" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>26.71</v>
+        <v>21.53</v>
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
@@ -3931,29 +3931,29 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>User-69</t>
+          <t>User-45</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F82" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>25.71</v>
+        <v>59.94</v>
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
@@ -3967,29 +3967,29 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>User-31</t>
+          <t>User-65</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F83" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>12.7</v>
+        <v>33.64</v>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
@@ -4003,29 +4003,29 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>User-53</t>
+          <t>User-34</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F84" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>8.609999999999999</v>
+        <v>77.92</v>
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
@@ -4039,29 +4039,29 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>User-29</t>
+          <t>User-46</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F85" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>92.15000000000001</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
@@ -4075,29 +4075,29 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>User-27</t>
+          <t>User-89</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F86" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>23.63</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>User-65</t>
+          <t>User-80</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -4133,7 +4133,7 @@
         <v>200</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>38.75</v>
+        <v>77.56999999999999</v>
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
@@ -4147,29 +4147,29 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>User-21</t>
+          <t>User-81</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F88" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>91.17</v>
+        <v>32.09</v>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
@@ -4183,29 +4183,29 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>User-55</t>
+          <t>User-27</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F89" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>39.49</v>
+        <v>26.45</v>
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
@@ -4219,12 +4219,12 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>User-82</t>
+          <t>User-17</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -4241,7 +4241,7 @@
         <v>200</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>83.59</v>
+        <v>70.88</v>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>User-21</t>
+          <t>User-8</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -4277,7 +4277,7 @@
         <v>200</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>87.8</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
@@ -4291,12 +4291,12 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>User-10</t>
+          <t>User-79</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -4313,7 +4313,7 @@
         <v>200</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>60.03</v>
+        <v>16.75</v>
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
@@ -4327,29 +4327,29 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>User-40</t>
+          <t>User-82</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F93" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>91.72</v>
+        <v>18.27</v>
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
@@ -4363,12 +4363,12 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>User-86</t>
+          <t>User-75</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -4385,7 +4385,7 @@
         <v>200</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>25.35</v>
+        <v>67.56</v>
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
@@ -4399,29 +4399,29 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>User-27</t>
+          <t>User-76</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F95" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>18.76</v>
+        <v>64.52</v>
       </c>
       <c r="H95" s="7" t="inlineStr">
         <is>
@@ -4435,12 +4435,12 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>User-6</t>
+          <t>User-86</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -4457,7 +4457,7 @@
         <v>200</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>62.03</v>
+        <v>50.22</v>
       </c>
       <c r="H96" s="7" t="inlineStr">
         <is>
@@ -4471,29 +4471,29 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>User-83</t>
+          <t>User-4</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F97" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>86.22</v>
+        <v>63.95</v>
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
@@ -4507,29 +4507,29 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>User-59</t>
+          <t>User-80</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F98" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>53.08</v>
+        <v>71.88</v>
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -4553,19 +4553,19 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F99" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>36.5</v>
+        <v>85.41</v>
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
@@ -4579,29 +4579,29 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>User-80</t>
+          <t>User-23</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F100" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>10.8</v>
+        <v>30.03</v>
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
@@ -4615,29 +4615,29 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>User-16</t>
+          <t>User-72</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F101" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>10.99</v>
+        <v>13.34</v>
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
@@ -4651,29 +4651,29 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>User-98</t>
+          <t>User-13</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F102" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>11.18</v>
+        <v>10.52</v>
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
@@ -4687,12 +4687,12 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>User-98</t>
+          <t>User-68</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -4709,7 +4709,7 @@
         <v>200</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>22.79</v>
+        <v>93.28</v>
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
@@ -4723,29 +4723,29 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>User-79</t>
+          <t>User-49</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F104" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>43.6</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
@@ -4759,29 +4759,29 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>User-89</t>
+          <t>User-9</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F105" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>69.90000000000001</v>
+        <v>51.37</v>
       </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
@@ -4795,29 +4795,29 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>User-96</t>
+          <t>User-35</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F106" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>80.90000000000001</v>
+        <v>54.85</v>
       </c>
       <c r="H106" s="7" t="inlineStr">
         <is>
@@ -4831,29 +4831,29 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>User-78</t>
+          <t>User-33</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F107" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>42.28</v>
+        <v>67.48</v>
       </c>
       <c r="H107" s="7" t="inlineStr">
         <is>
@@ -4867,29 +4867,29 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>User-50</t>
+          <t>User-79</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F108" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>40.07</v>
+        <v>10.77</v>
       </c>
       <c r="H108" s="7" t="inlineStr">
         <is>
@@ -4903,12 +4903,12 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>User-26</t>
+          <t>User-65</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -4925,7 +4925,7 @@
         <v>200</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>20.55</v>
+        <v>85.09</v>
       </c>
       <c r="H109" s="7" t="inlineStr">
         <is>
@@ -4939,29 +4939,29 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>User-44</t>
+          <t>User-41</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F110" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>61.96</v>
+        <v>13.21</v>
       </c>
       <c r="H110" s="7" t="inlineStr">
         <is>
@@ -4975,29 +4975,29 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>User-70</t>
+          <t>User-20</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F111" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>30.83</v>
+        <v>29.47</v>
       </c>
       <c r="H111" s="7" t="inlineStr">
         <is>
@@ -5011,29 +5011,29 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>User-68</t>
+          <t>User-43</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F112" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>71.53</v>
+        <v>16.64</v>
       </c>
       <c r="H112" s="7" t="inlineStr">
         <is>
@@ -5047,12 +5047,12 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>User-2</t>
+          <t>User-88</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -5069,7 +5069,7 @@
         <v>200</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>85.17</v>
+        <v>11.86</v>
       </c>
       <c r="H113" s="7" t="inlineStr">
         <is>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>User-34</t>
+          <t>User-9</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -5105,7 +5105,7 @@
         <v>200</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>84.97</v>
+        <v>24.95</v>
       </c>
       <c r="H114" s="7" t="inlineStr">
         <is>
@@ -5119,29 +5119,29 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>User-58</t>
+          <t>User-92</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F115" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>92.54000000000001</v>
+        <v>57.53</v>
       </c>
       <c r="H115" s="7" t="inlineStr">
         <is>
@@ -5155,29 +5155,29 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>User-21</t>
+          <t>User-79</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F116" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>9.66</v>
+        <v>38.58</v>
       </c>
       <c r="H116" s="7" t="inlineStr">
         <is>
@@ -5191,29 +5191,29 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>User-26</t>
+          <t>User-15</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F117" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>37.08</v>
+        <v>79.16</v>
       </c>
       <c r="H117" s="7" t="inlineStr">
         <is>
@@ -5227,29 +5227,29 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>User-90</t>
+          <t>User-11</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F118" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>83.40000000000001</v>
+        <v>90.08</v>
       </c>
       <c r="H118" s="7" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -5273,19 +5273,19 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F119" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G119" s="4" t="n">
-        <v>35.88</v>
+        <v>62.14</v>
       </c>
       <c r="H119" s="7" t="inlineStr">
         <is>
@@ -5299,29 +5299,29 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>User-20</t>
+          <t>User-83</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F120" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>32.73</v>
+        <v>60.07</v>
       </c>
       <c r="H120" s="7" t="inlineStr">
         <is>
@@ -5335,29 +5335,29 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>User-45</t>
+          <t>User-56</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F121" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>64.45999999999999</v>
+        <v>48.09</v>
       </c>
       <c r="H121" s="7" t="inlineStr">
         <is>
@@ -5371,12 +5371,12 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>User-56</t>
+          <t>User-25</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -5393,7 +5393,7 @@
         <v>200</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>91.14</v>
+        <v>66.95</v>
       </c>
       <c r="H122" s="7" t="inlineStr">
         <is>
@@ -5407,29 +5407,29 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>User-87</t>
+          <t>User-50</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F123" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>11.5</v>
+        <v>75.28</v>
       </c>
       <c r="H123" s="7" t="inlineStr">
         <is>
@@ -5443,29 +5443,29 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>User-69</t>
+          <t>User-68</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F124" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G124" s="4" t="n">
-        <v>27.66</v>
+        <v>36.32</v>
       </c>
       <c r="H124" s="7" t="inlineStr">
         <is>
@@ -5479,29 +5479,29 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>User-21</t>
+          <t>User-36</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F125" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>72.56</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="H125" s="7" t="inlineStr">
         <is>
@@ -5515,29 +5515,29 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>User-93</t>
+          <t>User-66</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F126" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>63.27</v>
+        <v>12.37</v>
       </c>
       <c r="H126" s="7" t="inlineStr">
         <is>
@@ -5551,29 +5551,29 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>User-63</t>
+          <t>User-97</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F127" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G127" s="4" t="n">
-        <v>70.36</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
@@ -5587,29 +5587,29 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>User-56</t>
+          <t>User-84</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F128" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>92.34</v>
+        <v>27.86</v>
       </c>
       <c r="H128" s="7" t="inlineStr">
         <is>
@@ -5623,29 +5623,29 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>User-81</t>
+          <t>User-16</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F129" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G129" s="4" t="n">
-        <v>60.93</v>
+        <v>55.45</v>
       </c>
       <c r="H129" s="7" t="inlineStr">
         <is>
@@ -5659,29 +5659,29 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>User-86</t>
+          <t>User-80</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F130" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>29.56</v>
+        <v>87.81</v>
       </c>
       <c r="H130" s="7" t="inlineStr">
         <is>
@@ -5695,12 +5695,12 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>User-9</t>
+          <t>User-53</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -5717,7 +5717,7 @@
         <v>200</v>
       </c>
       <c r="G131" s="4" t="n">
-        <v>49.29</v>
+        <v>62.93</v>
       </c>
       <c r="H131" s="7" t="inlineStr">
         <is>
@@ -5731,29 +5731,29 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>User-14</t>
+          <t>User-73</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F132" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>31.41</v>
+        <v>20.57</v>
       </c>
       <c r="H132" s="7" t="inlineStr">
         <is>
@@ -5767,12 +5767,12 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>User-13</t>
+          <t>User-12</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -5789,7 +5789,7 @@
         <v>200</v>
       </c>
       <c r="G133" s="4" t="n">
-        <v>37.03</v>
+        <v>5.32</v>
       </c>
       <c r="H133" s="7" t="inlineStr">
         <is>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>User-49</t>
+          <t>User-45</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
@@ -5825,7 +5825,7 @@
         <v>200</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>66.98999999999999</v>
+        <v>30.86</v>
       </c>
       <c r="H134" s="7" t="inlineStr">
         <is>
@@ -5839,29 +5839,29 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>User-74</t>
+          <t>User-88</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F135" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G135" s="4" t="n">
-        <v>91.90000000000001</v>
+        <v>13.8</v>
       </c>
       <c r="H135" s="7" t="inlineStr">
         <is>
@@ -5875,29 +5875,29 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>User-24</t>
+          <t>User-82</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F136" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G136" s="4" t="n">
-        <v>86.20999999999999</v>
+        <v>61.76</v>
       </c>
       <c r="H136" s="7" t="inlineStr">
         <is>
@@ -5911,12 +5911,12 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>User-51</t>
+          <t>User-7</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -5933,7 +5933,7 @@
         <v>200</v>
       </c>
       <c r="G137" s="4" t="n">
-        <v>43.14</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="H137" s="7" t="inlineStr">
         <is>
@@ -5947,29 +5947,29 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>User-80</t>
+          <t>User-84</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F138" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>74.09</v>
+        <v>36.79</v>
       </c>
       <c r="H138" s="7" t="inlineStr">
         <is>
@@ -5983,29 +5983,29 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>User-59</t>
+          <t>User-17</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F139" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G139" s="4" t="n">
-        <v>52.41</v>
+        <v>78.95</v>
       </c>
       <c r="H139" s="7" t="inlineStr">
         <is>
@@ -6019,29 +6019,29 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>User-5</t>
+          <t>User-50</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F140" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>76.66</v>
+        <v>87.75</v>
       </c>
       <c r="H140" s="7" t="inlineStr">
         <is>
@@ -6055,29 +6055,29 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>User-88</t>
+          <t>User-23</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F141" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G141" s="4" t="n">
-        <v>44.07</v>
+        <v>47.57</v>
       </c>
       <c r="H141" s="7" t="inlineStr">
         <is>
@@ -6091,12 +6091,12 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>User-33</t>
+          <t>User-6</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
@@ -6113,7 +6113,7 @@
         <v>200</v>
       </c>
       <c r="G142" s="4" t="n">
-        <v>61.59</v>
+        <v>43.19</v>
       </c>
       <c r="H142" s="7" t="inlineStr">
         <is>
@@ -6127,12 +6127,12 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>User-3</t>
+          <t>User-88</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -6149,7 +6149,7 @@
         <v>200</v>
       </c>
       <c r="G143" s="4" t="n">
-        <v>39.1</v>
+        <v>80.84</v>
       </c>
       <c r="H143" s="7" t="inlineStr">
         <is>
@@ -6163,12 +6163,12 @@
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>User-59</t>
+          <t>User-99</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
@@ -6185,7 +6185,7 @@
         <v>200</v>
       </c>
       <c r="G144" s="4" t="n">
-        <v>34.37</v>
+        <v>49.82</v>
       </c>
       <c r="H144" s="7" t="inlineStr">
         <is>
@@ -6199,29 +6199,29 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.973</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>User-42</t>
+          <t>User-99</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F145" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G145" s="4" t="n">
-        <v>22.52</v>
+        <v>53.12</v>
       </c>
       <c r="H145" s="7" t="inlineStr">
         <is>
@@ -6235,29 +6235,29 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>User-15</t>
+          <t>User-73</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F146" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G146" s="4" t="n">
-        <v>35.48</v>
+        <v>38</v>
       </c>
       <c r="H146" s="7" t="inlineStr">
         <is>
@@ -6271,29 +6271,29 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>User-95</t>
+          <t>User-56</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F147" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G147" s="4" t="n">
-        <v>56.96</v>
+        <v>86.13</v>
       </c>
       <c r="H147" s="7" t="inlineStr">
         <is>
@@ -6307,29 +6307,29 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>User-89</t>
+          <t>User-8</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F148" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G148" s="4" t="n">
-        <v>22.3</v>
+        <v>11.08</v>
       </c>
       <c r="H148" s="7" t="inlineStr">
         <is>
@@ -6343,29 +6343,29 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>User-91</t>
+          <t>User-79</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F149" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G149" s="4" t="n">
-        <v>84.47</v>
+        <v>80.19</v>
       </c>
       <c r="H149" s="7" t="inlineStr">
         <is>
@@ -6379,29 +6379,29 @@
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>User-35</t>
+          <t>User-59</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F150" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G150" s="4" t="n">
-        <v>5.91</v>
+        <v>56.91</v>
       </c>
       <c r="H150" s="7" t="inlineStr">
         <is>
@@ -6415,12 +6415,12 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>User-73</t>
+          <t>User-1</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
@@ -6437,7 +6437,7 @@
         <v>200</v>
       </c>
       <c r="G151" s="4" t="n">
-        <v>25.84</v>
+        <v>85.31</v>
       </c>
       <c r="H151" s="7" t="inlineStr">
         <is>
@@ -6451,29 +6451,29 @@
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>User-66</t>
+          <t>User-35</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F152" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G152" s="4" t="n">
-        <v>59.74</v>
+        <v>48.02</v>
       </c>
       <c r="H152" s="7" t="inlineStr">
         <is>
@@ -6487,29 +6487,29 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>User-55</t>
+          <t>User-47</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F153" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G153" s="4" t="n">
-        <v>64.59999999999999</v>
+        <v>43.71</v>
       </c>
       <c r="H153" s="7" t="inlineStr">
         <is>
@@ -6523,29 +6523,29 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>User-70</t>
+          <t>User-64</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F154" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G154" s="4" t="n">
-        <v>41.91</v>
+        <v>40.26</v>
       </c>
       <c r="H154" s="7" t="inlineStr">
         <is>
@@ -6559,29 +6559,29 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>User-16</t>
+          <t>User-73</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F155" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G155" s="4" t="n">
-        <v>23.54</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="H155" s="7" t="inlineStr">
         <is>
@@ -6595,29 +6595,29 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>User-18</t>
+          <t>User-26</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F156" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G156" s="4" t="n">
-        <v>74.62</v>
+        <v>60.57</v>
       </c>
       <c r="H156" s="7" t="inlineStr">
         <is>
@@ -6631,29 +6631,29 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>User-12</t>
+          <t>User-8</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F157" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G157" s="4" t="n">
-        <v>50.67</v>
+        <v>53.13</v>
       </c>
       <c r="H157" s="7" t="inlineStr">
         <is>
@@ -6667,29 +6667,29 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>User-90</t>
+          <t>User-56</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F158" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G158" s="4" t="n">
-        <v>32.38</v>
+        <v>35.61</v>
       </c>
       <c r="H158" s="7" t="inlineStr">
         <is>
@@ -6703,29 +6703,29 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>User-36</t>
+          <t>User-33</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F159" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G159" s="4" t="n">
-        <v>22.24</v>
+        <v>57.19</v>
       </c>
       <c r="H159" s="7" t="inlineStr">
         <is>
@@ -6739,29 +6739,29 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>User-7</t>
+          <t>User-27</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F160" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G160" s="4" t="n">
-        <v>47.42</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H160" s="7" t="inlineStr">
         <is>
@@ -6775,12 +6775,12 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>User-20</t>
+          <t>User-97</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
@@ -6797,7 +6797,7 @@
         <v>200</v>
       </c>
       <c r="G161" s="4" t="n">
-        <v>66.95999999999999</v>
+        <v>92.95</v>
       </c>
       <c r="H161" s="7" t="inlineStr">
         <is>
@@ -6811,29 +6811,29 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>User-34</t>
+          <t>User-65</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F162" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G162" s="4" t="n">
-        <v>14.26</v>
+        <v>31.39</v>
       </c>
       <c r="H162" s="7" t="inlineStr">
         <is>
@@ -6847,29 +6847,29 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>User-93</t>
+          <t>User-62</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F163" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G163" s="4" t="n">
-        <v>12.35</v>
+        <v>33.23</v>
       </c>
       <c r="H163" s="7" t="inlineStr">
         <is>
@@ -6883,12 +6883,12 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>User-63</t>
+          <t>User-92</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
@@ -6905,7 +6905,7 @@
         <v>200</v>
       </c>
       <c r="G164" s="4" t="n">
-        <v>45.73</v>
+        <v>72.63</v>
       </c>
       <c r="H164" s="7" t="inlineStr">
         <is>
@@ -6919,29 +6919,29 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>User-31</t>
+          <t>User-78</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F165" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G165" s="4" t="n">
-        <v>74.48</v>
+        <v>14.8</v>
       </c>
       <c r="H165" s="7" t="inlineStr">
         <is>
@@ -6955,29 +6955,29 @@
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>User-20</t>
+          <t>User-55</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F166" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G166" s="4" t="n">
-        <v>49.55</v>
+        <v>23.05</v>
       </c>
       <c r="H166" s="7" t="inlineStr">
         <is>
@@ -6991,12 +6991,12 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>User-30</t>
+          <t>User-80</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
@@ -7013,7 +7013,7 @@
         <v>200</v>
       </c>
       <c r="G167" s="4" t="n">
-        <v>16.08</v>
+        <v>74.63</v>
       </c>
       <c r="H167" s="7" t="inlineStr">
         <is>
@@ -7027,29 +7027,29 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>User-3</t>
+          <t>User-7</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F168" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G168" s="4" t="n">
-        <v>15.59</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="H168" s="7" t="inlineStr">
         <is>
@@ -7063,29 +7063,29 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>User-79</t>
+          <t>User-12</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F169" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G169" s="4" t="n">
-        <v>6.46</v>
+        <v>11.16</v>
       </c>
       <c r="H169" s="7" t="inlineStr">
         <is>
@@ -7099,12 +7099,12 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>User-8</t>
+          <t>User-57</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
@@ -7121,7 +7121,7 @@
         <v>200</v>
       </c>
       <c r="G170" s="4" t="n">
-        <v>44.24</v>
+        <v>24.45</v>
       </c>
       <c r="H170" s="7" t="inlineStr">
         <is>
@@ -7135,12 +7135,12 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>User-5</t>
+          <t>User-8</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
@@ -7157,7 +7157,7 @@
         <v>200</v>
       </c>
       <c r="G171" s="4" t="n">
-        <v>64</v>
+        <v>23.59</v>
       </c>
       <c r="H171" s="7" t="inlineStr">
         <is>
@@ -7171,29 +7171,29 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>User-54</t>
+          <t>User-15</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F172" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G172" s="4" t="n">
-        <v>7.09</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="H172" s="7" t="inlineStr">
         <is>
@@ -7207,29 +7207,29 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>User-2</t>
+          <t>User-5</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F173" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G173" s="4" t="n">
-        <v>29.2</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="H173" s="7" t="inlineStr">
         <is>
@@ -7243,12 +7243,12 @@
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>User-37</t>
+          <t>User-36</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
@@ -7265,7 +7265,7 @@
         <v>200</v>
       </c>
       <c r="G174" s="4" t="n">
-        <v>22.79</v>
+        <v>54.31</v>
       </c>
       <c r="H174" s="7" t="inlineStr">
         <is>
@@ -7279,29 +7279,29 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>User-75</t>
+          <t>User-13</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F175" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G175" s="4" t="n">
-        <v>90.09</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="H175" s="7" t="inlineStr">
         <is>
@@ -7315,29 +7315,29 @@
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>User-44</t>
+          <t>User-72</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F176" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G176" s="4" t="n">
-        <v>26.9</v>
+        <v>35.68</v>
       </c>
       <c r="H176" s="7" t="inlineStr">
         <is>
@@ -7351,29 +7351,29 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>User-36</t>
+          <t>User-2</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F177" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G177" s="4" t="n">
-        <v>90.73</v>
+        <v>28.28</v>
       </c>
       <c r="H177" s="7" t="inlineStr">
         <is>
@@ -7387,29 +7387,29 @@
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>User-61</t>
+          <t>User-78</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F178" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G178" s="4" t="n">
-        <v>86.29000000000001</v>
+        <v>84.29000000000001</v>
       </c>
       <c r="H178" s="7" t="inlineStr">
         <is>
@@ -7423,29 +7423,29 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>User-37</t>
+          <t>User-87</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F179" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G179" s="4" t="n">
-        <v>67</v>
+        <v>39.64</v>
       </c>
       <c r="H179" s="7" t="inlineStr">
         <is>
@@ -7459,29 +7459,29 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>User-23</t>
+          <t>User-2</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F180" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G180" s="4" t="n">
-        <v>31.73</v>
+        <v>38.48</v>
       </c>
       <c r="H180" s="7" t="inlineStr">
         <is>
@@ -7495,29 +7495,29 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>User-38</t>
+          <t>User-74</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F181" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G181" s="4" t="n">
-        <v>70.01000000000001</v>
+        <v>19.83</v>
       </c>
       <c r="H181" s="7" t="inlineStr">
         <is>
@@ -7531,29 +7531,29 @@
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>User-35</t>
+          <t>User-8</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F182" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G182" s="4" t="n">
-        <v>84.03</v>
+        <v>18.58</v>
       </c>
       <c r="H182" s="7" t="inlineStr">
         <is>
@@ -7567,29 +7567,29 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>User-87</t>
+          <t>User-100</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F183" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G183" s="4" t="n">
-        <v>12.22</v>
+        <v>31.03</v>
       </c>
       <c r="H183" s="7" t="inlineStr">
         <is>
@@ -7603,29 +7603,29 @@
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>User-95</t>
+          <t>User-30</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F184" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G184" s="4" t="n">
-        <v>73.84999999999999</v>
+        <v>15.43</v>
       </c>
       <c r="H184" s="7" t="inlineStr">
         <is>
@@ -7639,12 +7639,12 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>User-75</t>
+          <t>User-17</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
@@ -7661,7 +7661,7 @@
         <v>200</v>
       </c>
       <c r="G185" s="4" t="n">
-        <v>20.48</v>
+        <v>39.25</v>
       </c>
       <c r="H185" s="7" t="inlineStr">
         <is>
@@ -7675,29 +7675,29 @@
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>User-14</t>
+          <t>User-22</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F186" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G186" s="4" t="n">
-        <v>51.85</v>
+        <v>29.55</v>
       </c>
       <c r="H186" s="7" t="inlineStr">
         <is>
@@ -7711,12 +7711,12 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>User-20</t>
+          <t>User-43</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
@@ -7733,7 +7733,7 @@
         <v>200</v>
       </c>
       <c r="G187" s="4" t="n">
-        <v>90.14</v>
+        <v>43.38</v>
       </c>
       <c r="H187" s="7" t="inlineStr">
         <is>
@@ -7747,29 +7747,29 @@
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>User-98</t>
+          <t>User-10</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F188" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G188" s="4" t="n">
-        <v>63.33</v>
+        <v>19.57</v>
       </c>
       <c r="H188" s="7" t="inlineStr">
         <is>
@@ -7783,29 +7783,29 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>User-36</t>
+          <t>User-16</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F189" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G189" s="4" t="n">
-        <v>64.61</v>
+        <v>45.53</v>
       </c>
       <c r="H189" s="7" t="inlineStr">
         <is>
@@ -7819,29 +7819,29 @@
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>User-33</t>
+          <t>User-3</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E190" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F190" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G190" s="4" t="n">
-        <v>35.03</v>
+        <v>46.65</v>
       </c>
       <c r="H190" s="7" t="inlineStr">
         <is>
@@ -7855,29 +7855,29 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>User-54</t>
+          <t>User-99</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F191" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G191" s="4" t="n">
-        <v>57.47</v>
+        <v>16.54</v>
       </c>
       <c r="H191" s="7" t="inlineStr">
         <is>
@@ -7891,29 +7891,29 @@
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>User-40</t>
+          <t>User-60</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F192" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G192" s="4" t="n">
-        <v>77.77</v>
+        <v>24.92</v>
       </c>
       <c r="H192" s="7" t="inlineStr">
         <is>
@@ -7927,29 +7927,29 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>User-66</t>
+          <t>User-3</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F193" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G193" s="4" t="n">
-        <v>93.27</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="H193" s="7" t="inlineStr">
         <is>
@@ -7963,29 +7963,29 @@
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>User-91</t>
+          <t>User-23</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F194" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G194" s="4" t="n">
-        <v>55.71</v>
+        <v>15.3</v>
       </c>
       <c r="H194" s="7" t="inlineStr">
         <is>
@@ -7999,29 +7999,29 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>User-72</t>
+          <t>User-37</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F195" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G195" s="4" t="n">
-        <v>57.13</v>
+        <v>25.16</v>
       </c>
       <c r="H195" s="7" t="inlineStr">
         <is>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>User-64</t>
+          <t>User-57</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
@@ -8057,7 +8057,7 @@
         <v>200</v>
       </c>
       <c r="G196" s="4" t="n">
-        <v>62.86</v>
+        <v>51.21</v>
       </c>
       <c r="H196" s="7" t="inlineStr">
         <is>
@@ -8071,29 +8071,29 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>User-53</t>
+          <t>User-20</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F197" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G197" s="4" t="n">
-        <v>73.2</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="H197" s="7" t="inlineStr">
         <is>
@@ -8107,29 +8107,29 @@
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>User-40</t>
+          <t>User-66</t>
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E198" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F198" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G198" s="4" t="n">
-        <v>50.3</v>
+        <v>41.55</v>
       </c>
       <c r="H198" s="7" t="inlineStr">
         <is>
@@ -8143,29 +8143,29 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>User-97</t>
+          <t>User-20</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F199" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G199" s="4" t="n">
-        <v>81.28</v>
+        <v>87.44</v>
       </c>
       <c r="H199" s="7" t="inlineStr">
         <is>
@@ -8179,29 +8179,29 @@
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>User-77</t>
+          <t>User-13</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E200" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F200" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G200" s="4" t="n">
-        <v>43.04</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="H200" s="7" t="inlineStr">
         <is>
@@ -8215,29 +8215,29 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>User-90</t>
+          <t>User-22</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F201" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G201" s="4" t="n">
-        <v>5.66</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="H201" s="7" t="inlineStr">
         <is>
@@ -8251,29 +8251,29 @@
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>User-84</t>
+          <t>User-94</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E202" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F202" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G202" s="4" t="n">
-        <v>16.73</v>
+        <v>48.71</v>
       </c>
       <c r="H202" s="7" t="inlineStr">
         <is>
@@ -8287,29 +8287,29 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>User-19</t>
+          <t>User-79</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F203" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G203" s="4" t="n">
-        <v>59.88</v>
+        <v>38.66</v>
       </c>
       <c r="H203" s="7" t="inlineStr">
         <is>
@@ -8323,12 +8323,12 @@
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>User-50</t>
+          <t>User-70</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr">
@@ -8345,7 +8345,7 @@
         <v>200</v>
       </c>
       <c r="G204" s="4" t="n">
-        <v>39.63</v>
+        <v>37.84</v>
       </c>
       <c r="H204" s="7" t="inlineStr">
         <is>
@@ -8359,12 +8359,12 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>User-35</t>
+          <t>User-67</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
@@ -8381,7 +8381,7 @@
         <v>200</v>
       </c>
       <c r="G205" s="4" t="n">
-        <v>75.28</v>
+        <v>44.21</v>
       </c>
       <c r="H205" s="7" t="inlineStr">
         <is>
@@ -8395,29 +8395,29 @@
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>User-66</t>
+          <t>User-8</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F206" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G206" s="4" t="n">
-        <v>38.3</v>
+        <v>90.95</v>
       </c>
       <c r="H206" s="7" t="inlineStr">
         <is>
@@ -8431,29 +8431,29 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>User-56</t>
+          <t>User-29</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F207" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G207" s="4" t="n">
-        <v>77.11</v>
+        <v>19.33</v>
       </c>
       <c r="H207" s="7" t="inlineStr">
         <is>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>User-88</t>
+          <t>User-70</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
@@ -8489,7 +8489,7 @@
         <v>200</v>
       </c>
       <c r="G208" s="4" t="n">
-        <v>53.4</v>
+        <v>81.28</v>
       </c>
       <c r="H208" s="7" t="inlineStr">
         <is>
@@ -8503,29 +8503,29 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>User-71</t>
+          <t>User-99</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F209" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G209" s="4" t="n">
-        <v>25.51</v>
+        <v>54.2</v>
       </c>
       <c r="H209" s="7" t="inlineStr">
         <is>
@@ -8539,29 +8539,29 @@
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>User-61</t>
+          <t>User-73</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F210" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G210" s="4" t="n">
-        <v>21.31</v>
+        <v>19.07</v>
       </c>
       <c r="H210" s="7" t="inlineStr">
         <is>
@@ -8575,29 +8575,29 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.974</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>User-7</t>
+          <t>User-3</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F211" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G211" s="4" t="n">
-        <v>27.65</v>
+        <v>34.33</v>
       </c>
       <c r="H211" s="7" t="inlineStr">
         <is>
@@ -8611,29 +8611,29 @@
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>User-99</t>
+          <t>User-19</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E212" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F212" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G212" s="4" t="n">
-        <v>78.72</v>
+        <v>19.2</v>
       </c>
       <c r="H212" s="7" t="inlineStr">
         <is>
@@ -8647,29 +8647,29 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>User-63</t>
+          <t>User-93</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E213" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F213" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G213" s="4" t="n">
-        <v>57.98</v>
+        <v>55.32</v>
       </c>
       <c r="H213" s="7" t="inlineStr">
         <is>
@@ -8683,29 +8683,29 @@
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>User-66</t>
+          <t>User-3</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E214" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F214" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G214" s="4" t="n">
-        <v>36.93</v>
+        <v>53.01</v>
       </c>
       <c r="H214" s="7" t="inlineStr">
         <is>
@@ -8719,29 +8719,29 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>User-93</t>
+          <t>User-87</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F215" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G215" s="4" t="n">
-        <v>61.89</v>
+        <v>75.61</v>
       </c>
       <c r="H215" s="7" t="inlineStr">
         <is>
@@ -8755,29 +8755,29 @@
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>User-89</t>
+          <t>User-72</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E216" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F216" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G216" s="4" t="n">
-        <v>91.29000000000001</v>
+        <v>70.67</v>
       </c>
       <c r="H216" s="7" t="inlineStr">
         <is>
@@ -8791,12 +8791,12 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>User-61</t>
+          <t>User-35</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
@@ -8813,7 +8813,7 @@
         <v>200</v>
       </c>
       <c r="G217" s="4" t="n">
-        <v>82.98999999999999</v>
+        <v>88.64</v>
       </c>
       <c r="H217" s="7" t="inlineStr">
         <is>
@@ -8827,29 +8827,29 @@
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>User-81</t>
+          <t>User-24</t>
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E218" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F218" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G218" s="4" t="n">
-        <v>83.23</v>
+        <v>7.2</v>
       </c>
       <c r="H218" s="7" t="inlineStr">
         <is>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>User-20</t>
+          <t>User-77</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
@@ -8885,7 +8885,7 @@
         <v>200</v>
       </c>
       <c r="G219" s="4" t="n">
-        <v>16.21</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="H219" s="7" t="inlineStr">
         <is>
@@ -8899,29 +8899,29 @@
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>User-50</t>
+          <t>User-24</t>
         </is>
       </c>
       <c r="D220" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E220" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F220" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G220" s="4" t="n">
-        <v>94.51000000000001</v>
+        <v>23.66</v>
       </c>
       <c r="H220" s="7" t="inlineStr">
         <is>
@@ -8935,29 +8935,29 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>User-34</t>
+          <t>User-29</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E221" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F221" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G221" s="4" t="n">
-        <v>53.47</v>
+        <v>9.82</v>
       </c>
       <c r="H221" s="7" t="inlineStr">
         <is>
@@ -8971,29 +8971,29 @@
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C222" s="4" t="inlineStr">
         <is>
-          <t>User-52</t>
+          <t>User-6</t>
         </is>
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E222" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F222" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G222" s="4" t="n">
-        <v>66.09</v>
+        <v>66.53</v>
       </c>
       <c r="H222" s="7" t="inlineStr">
         <is>
@@ -9007,29 +9007,29 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>User-32</t>
+          <t>User-78</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E223" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F223" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G223" s="4" t="n">
-        <v>37.71</v>
+        <v>61.57</v>
       </c>
       <c r="H223" s="7" t="inlineStr">
         <is>
@@ -9043,29 +9043,29 @@
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>User-16</t>
+          <t>User-41</t>
         </is>
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E224" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F224" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G224" s="4" t="n">
-        <v>26.51</v>
+        <v>20.83</v>
       </c>
       <c r="H224" s="7" t="inlineStr">
         <is>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>User-72</t>
+          <t>User-61</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
@@ -9101,7 +9101,7 @@
         <v>200</v>
       </c>
       <c r="G225" s="4" t="n">
-        <v>45.96</v>
+        <v>80.83</v>
       </c>
       <c r="H225" s="7" t="inlineStr">
         <is>
@@ -9115,29 +9115,29 @@
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>User-30</t>
+          <t>User-21</t>
         </is>
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E226" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F226" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G226" s="4" t="n">
-        <v>12.5</v>
+        <v>42.85</v>
       </c>
       <c r="H226" s="7" t="inlineStr">
         <is>
@@ -9151,29 +9151,29 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>User-36</t>
+          <t>User-41</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E227" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F227" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G227" s="4" t="n">
-        <v>58.23</v>
+        <v>45</v>
       </c>
       <c r="H227" s="7" t="inlineStr">
         <is>
@@ -9187,12 +9187,12 @@
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>User-50</t>
+          <t>User-3</t>
         </is>
       </c>
       <c r="D228" s="4" t="inlineStr">
@@ -9209,7 +9209,7 @@
         <v>200</v>
       </c>
       <c r="G228" s="4" t="n">
-        <v>47.24</v>
+        <v>69.28</v>
       </c>
       <c r="H228" s="7" t="inlineStr">
         <is>
@@ -9223,29 +9223,29 @@
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>User-22</t>
+          <t>User-16</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E229" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F229" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G229" s="4" t="n">
-        <v>94.39</v>
+        <v>23.97</v>
       </c>
       <c r="H229" s="7" t="inlineStr">
         <is>
@@ -9259,12 +9259,12 @@
       </c>
       <c r="B230" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C230" s="4" t="inlineStr">
         <is>
-          <t>User-86</t>
+          <t>User-35</t>
         </is>
       </c>
       <c r="D230" s="4" t="inlineStr">
@@ -9281,7 +9281,7 @@
         <v>200</v>
       </c>
       <c r="G230" s="4" t="n">
-        <v>22.6</v>
+        <v>63.91</v>
       </c>
       <c r="H230" s="7" t="inlineStr">
         <is>
@@ -9295,29 +9295,29 @@
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>User-48</t>
+          <t>User-97</t>
         </is>
       </c>
       <c r="D231" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E231" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F231" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G231" s="4" t="n">
-        <v>43.01</v>
+        <v>31.67</v>
       </c>
       <c r="H231" s="7" t="inlineStr">
         <is>
@@ -9331,29 +9331,29 @@
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>User-87</t>
+          <t>User-63</t>
         </is>
       </c>
       <c r="D232" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E232" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F232" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G232" s="4" t="n">
-        <v>15.48</v>
+        <v>20.22</v>
       </c>
       <c r="H232" s="7" t="inlineStr">
         <is>
@@ -9367,29 +9367,29 @@
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>User-49</t>
+          <t>User-67</t>
         </is>
       </c>
       <c r="D233" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E233" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F233" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G233" s="4" t="n">
-        <v>41.94</v>
+        <v>17.26</v>
       </c>
       <c r="H233" s="7" t="inlineStr">
         <is>
@@ -9403,29 +9403,29 @@
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>User-12</t>
+          <t>User-36</t>
         </is>
       </c>
       <c r="D234" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E234" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F234" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G234" s="4" t="n">
-        <v>34.68</v>
+        <v>28.75</v>
       </c>
       <c r="H234" s="7" t="inlineStr">
         <is>
@@ -9439,29 +9439,29 @@
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>User-2</t>
+          <t>User-25</t>
         </is>
       </c>
       <c r="D235" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E235" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F235" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G235" s="4" t="n">
-        <v>61.3</v>
+        <v>86.03</v>
       </c>
       <c r="H235" s="7" t="inlineStr">
         <is>
@@ -9475,29 +9475,29 @@
       </c>
       <c r="B236" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>User-47</t>
+          <t>User-32</t>
         </is>
       </c>
       <c r="D236" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E236" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F236" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G236" s="4" t="n">
-        <v>92.45999999999999</v>
+        <v>59.05</v>
       </c>
       <c r="H236" s="7" t="inlineStr">
         <is>
@@ -9511,29 +9511,29 @@
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>User-100</t>
+          <t>User-40</t>
         </is>
       </c>
       <c r="D237" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E237" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F237" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G237" s="4" t="n">
-        <v>49.45</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="H237" s="7" t="inlineStr">
         <is>
@@ -9547,29 +9547,29 @@
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>User-95</t>
+          <t>User-61</t>
         </is>
       </c>
       <c r="D238" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E238" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F238" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G238" s="4" t="n">
-        <v>20.03</v>
+        <v>80.18000000000001</v>
       </c>
       <c r="H238" s="7" t="inlineStr">
         <is>
@@ -9583,29 +9583,29 @@
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>User-55</t>
+          <t>User-61</t>
         </is>
       </c>
       <c r="D239" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E239" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F239" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G239" s="4" t="n">
-        <v>45.93</v>
+        <v>31.12</v>
       </c>
       <c r="H239" s="7" t="inlineStr">
         <is>
@@ -9619,29 +9619,29 @@
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>User-81</t>
+          <t>User-2</t>
         </is>
       </c>
       <c r="D240" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E240" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F240" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G240" s="4" t="n">
-        <v>45.93</v>
+        <v>91.63</v>
       </c>
       <c r="H240" s="7" t="inlineStr">
         <is>
@@ -9655,12 +9655,12 @@
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>User-18</t>
+          <t>User-73</t>
         </is>
       </c>
       <c r="D241" s="4" t="inlineStr">
@@ -9677,7 +9677,7 @@
         <v>200</v>
       </c>
       <c r="G241" s="4" t="n">
-        <v>36.73</v>
+        <v>33.8</v>
       </c>
       <c r="H241" s="7" t="inlineStr">
         <is>
@@ -9691,12 +9691,12 @@
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>User-7</t>
+          <t>User-82</t>
         </is>
       </c>
       <c r="D242" s="4" t="inlineStr">
@@ -9713,7 +9713,7 @@
         <v>200</v>
       </c>
       <c r="G242" s="4" t="n">
-        <v>28.15</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H242" s="7" t="inlineStr">
         <is>
@@ -9727,29 +9727,29 @@
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>User-57</t>
+          <t>User-40</t>
         </is>
       </c>
       <c r="D243" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E243" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F243" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G243" s="4" t="n">
-        <v>21.61</v>
+        <v>83.47</v>
       </c>
       <c r="H243" s="7" t="inlineStr">
         <is>
@@ -9763,12 +9763,12 @@
       </c>
       <c r="B244" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>User-93</t>
+          <t>User-34</t>
         </is>
       </c>
       <c r="D244" s="4" t="inlineStr">
@@ -9785,7 +9785,7 @@
         <v>200</v>
       </c>
       <c r="G244" s="4" t="n">
-        <v>43.92</v>
+        <v>79.14</v>
       </c>
       <c r="H244" s="7" t="inlineStr">
         <is>
@@ -9799,12 +9799,12 @@
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>User-52</t>
+          <t>User-28</t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
@@ -9821,7 +9821,7 @@
         <v>200</v>
       </c>
       <c r="G245" s="4" t="n">
-        <v>90.56999999999999</v>
+        <v>74.69</v>
       </c>
       <c r="H245" s="7" t="inlineStr">
         <is>
@@ -9835,29 +9835,29 @@
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>User-8</t>
+          <t>User-45</t>
         </is>
       </c>
       <c r="D246" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E246" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F246" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G246" s="4" t="n">
-        <v>43.6</v>
+        <v>80.22</v>
       </c>
       <c r="H246" s="7" t="inlineStr">
         <is>
@@ -9871,29 +9871,29 @@
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>User-31</t>
+          <t>User-6</t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E247" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F247" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G247" s="4" t="n">
-        <v>56.94</v>
+        <v>59.3</v>
       </c>
       <c r="H247" s="7" t="inlineStr">
         <is>
@@ -9907,12 +9907,12 @@
       </c>
       <c r="B248" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>User-13</t>
+          <t>User-64</t>
         </is>
       </c>
       <c r="D248" s="4" t="inlineStr">
@@ -9929,7 +9929,7 @@
         <v>200</v>
       </c>
       <c r="G248" s="4" t="n">
-        <v>8.74</v>
+        <v>31.65</v>
       </c>
       <c r="H248" s="7" t="inlineStr">
         <is>
@@ -9943,29 +9943,29 @@
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>User-78</t>
+          <t>User-73</t>
         </is>
       </c>
       <c r="D249" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E249" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F249" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G249" s="4" t="n">
-        <v>27.1</v>
+        <v>38.15</v>
       </c>
       <c r="H249" s="7" t="inlineStr">
         <is>
@@ -9979,29 +9979,29 @@
       </c>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>User-69</t>
+          <t>User-57</t>
         </is>
       </c>
       <c r="D250" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E250" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F250" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G250" s="4" t="n">
-        <v>21.51</v>
+        <v>54.18</v>
       </c>
       <c r="H250" s="7" t="inlineStr">
         <is>
@@ -10015,29 +10015,29 @@
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>User-14</t>
+          <t>User-29</t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E251" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F251" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G251" s="4" t="n">
-        <v>29.99</v>
+        <v>19.48</v>
       </c>
       <c r="H251" s="7" t="inlineStr">
         <is>
@@ -10051,29 +10051,29 @@
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>User-42</t>
+          <t>User-69</t>
         </is>
       </c>
       <c r="D252" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E252" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F252" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G252" s="4" t="n">
-        <v>82.53</v>
+        <v>43.81</v>
       </c>
       <c r="H252" s="7" t="inlineStr">
         <is>
@@ -10087,29 +10087,29 @@
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>User-91</t>
+          <t>User-89</t>
         </is>
       </c>
       <c r="D253" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E253" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F253" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G253" s="4" t="n">
-        <v>20.58</v>
+        <v>7.82</v>
       </c>
       <c r="H253" s="7" t="inlineStr">
         <is>
@@ -10123,29 +10123,29 @@
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>User-25</t>
+          <t>User-53</t>
         </is>
       </c>
       <c r="D254" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E254" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F254" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G254" s="4" t="n">
-        <v>62.28</v>
+        <v>79.7</v>
       </c>
       <c r="H254" s="7" t="inlineStr">
         <is>
@@ -10159,29 +10159,29 @@
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>User-30</t>
+          <t>User-94</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E255" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F255" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G255" s="4" t="n">
-        <v>25.46</v>
+        <v>64.06</v>
       </c>
       <c r="H255" s="7" t="inlineStr">
         <is>
@@ -10195,29 +10195,29 @@
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>User-86</t>
+          <t>User-53</t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E256" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F256" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G256" s="4" t="n">
-        <v>61.62</v>
+        <v>83.61</v>
       </c>
       <c r="H256" s="7" t="inlineStr">
         <is>
@@ -10231,29 +10231,29 @@
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>User-46</t>
+          <t>User-91</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E257" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F257" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G257" s="4" t="n">
-        <v>8.02</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="H257" s="7" t="inlineStr">
         <is>
@@ -10267,12 +10267,12 @@
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>User-51</t>
+          <t>User-53</t>
         </is>
       </c>
       <c r="D258" s="4" t="inlineStr">
@@ -10289,7 +10289,7 @@
         <v>200</v>
       </c>
       <c r="G258" s="4" t="n">
-        <v>31.81</v>
+        <v>25.57</v>
       </c>
       <c r="H258" s="7" t="inlineStr">
         <is>
@@ -10303,29 +10303,29 @@
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>User-58</t>
+          <t>User-8</t>
         </is>
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E259" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F259" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G259" s="4" t="n">
-        <v>49.58</v>
+        <v>32.72</v>
       </c>
       <c r="H259" s="7" t="inlineStr">
         <is>
@@ -10339,29 +10339,29 @@
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>User-88</t>
+          <t>User-12</t>
         </is>
       </c>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E260" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F260" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G260" s="4" t="n">
-        <v>25.09</v>
+        <v>39.37</v>
       </c>
       <c r="H260" s="7" t="inlineStr">
         <is>
@@ -10375,29 +10375,29 @@
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>User-90</t>
+          <t>User-2</t>
         </is>
       </c>
       <c r="D261" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E261" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F261" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G261" s="4" t="n">
-        <v>50.2</v>
+        <v>66.75</v>
       </c>
       <c r="H261" s="7" t="inlineStr">
         <is>
@@ -10411,29 +10411,29 @@
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>User-76</t>
+          <t>User-15</t>
         </is>
       </c>
       <c r="D262" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E262" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F262" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G262" s="4" t="n">
-        <v>92.98999999999999</v>
+        <v>41.77</v>
       </c>
       <c r="H262" s="7" t="inlineStr">
         <is>
@@ -10447,29 +10447,29 @@
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>User-9</t>
+          <t>User-52</t>
         </is>
       </c>
       <c r="D263" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E263" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F263" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G263" s="4" t="n">
-        <v>90.39</v>
+        <v>18.17</v>
       </c>
       <c r="H263" s="7" t="inlineStr">
         <is>
@@ -10483,12 +10483,12 @@
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>User-76</t>
+          <t>User-79</t>
         </is>
       </c>
       <c r="D264" s="4" t="inlineStr">
@@ -10505,7 +10505,7 @@
         <v>200</v>
       </c>
       <c r="G264" s="4" t="n">
-        <v>10.23</v>
+        <v>32.95</v>
       </c>
       <c r="H264" s="7" t="inlineStr">
         <is>
@@ -10519,29 +10519,29 @@
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>User-31</t>
+          <t>User-69</t>
         </is>
       </c>
       <c r="D265" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E265" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F265" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G265" s="4" t="n">
-        <v>30.89</v>
+        <v>73.23</v>
       </c>
       <c r="H265" s="7" t="inlineStr">
         <is>
@@ -10555,12 +10555,12 @@
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>User-52</t>
+          <t>User-45</t>
         </is>
       </c>
       <c r="D266" s="4" t="inlineStr">
@@ -10577,7 +10577,7 @@
         <v>200</v>
       </c>
       <c r="G266" s="4" t="n">
-        <v>89.05</v>
+        <v>32.28</v>
       </c>
       <c r="H266" s="7" t="inlineStr">
         <is>
@@ -10591,12 +10591,12 @@
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>User-92</t>
+          <t>User-3</t>
         </is>
       </c>
       <c r="D267" s="4" t="inlineStr">
@@ -10613,7 +10613,7 @@
         <v>200</v>
       </c>
       <c r="G267" s="4" t="n">
-        <v>44.87</v>
+        <v>41.36</v>
       </c>
       <c r="H267" s="7" t="inlineStr">
         <is>
@@ -10627,29 +10627,29 @@
       </c>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>User-55</t>
+          <t>User-59</t>
         </is>
       </c>
       <c r="D268" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E268" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F268" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G268" s="4" t="n">
-        <v>59.72</v>
+        <v>43.42</v>
       </c>
       <c r="H268" s="7" t="inlineStr">
         <is>
@@ -10663,12 +10663,12 @@
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>User-30</t>
+          <t>User-2</t>
         </is>
       </c>
       <c r="D269" s="4" t="inlineStr">
@@ -10685,7 +10685,7 @@
         <v>200</v>
       </c>
       <c r="G269" s="4" t="n">
-        <v>44.18</v>
+        <v>47.28</v>
       </c>
       <c r="H269" s="7" t="inlineStr">
         <is>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>User-89</t>
+          <t>User-55</t>
         </is>
       </c>
       <c r="D270" s="4" t="inlineStr">
@@ -10721,7 +10721,7 @@
         <v>200</v>
       </c>
       <c r="G270" s="4" t="n">
-        <v>21.52</v>
+        <v>10.09</v>
       </c>
       <c r="H270" s="7" t="inlineStr">
         <is>
@@ -10735,29 +10735,29 @@
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>User-13</t>
+          <t>User-46</t>
         </is>
       </c>
       <c r="D271" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E271" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F271" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G271" s="4" t="n">
-        <v>85.54000000000001</v>
+        <v>74.19</v>
       </c>
       <c r="H271" s="7" t="inlineStr">
         <is>
@@ -10771,12 +10771,12 @@
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>User-45</t>
+          <t>User-64</t>
         </is>
       </c>
       <c r="D272" s="4" t="inlineStr">
@@ -10793,7 +10793,7 @@
         <v>200</v>
       </c>
       <c r="G272" s="4" t="n">
-        <v>21.65</v>
+        <v>34.81</v>
       </c>
       <c r="H272" s="7" t="inlineStr">
         <is>
@@ -10807,12 +10807,12 @@
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>User-31</t>
+          <t>User-54</t>
         </is>
       </c>
       <c r="D273" s="4" t="inlineStr">
@@ -10829,7 +10829,7 @@
         <v>200</v>
       </c>
       <c r="G273" s="4" t="n">
-        <v>54.46</v>
+        <v>31.06</v>
       </c>
       <c r="H273" s="7" t="inlineStr">
         <is>
@@ -10843,29 +10843,29 @@
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>User-97</t>
+          <t>User-83</t>
         </is>
       </c>
       <c r="D274" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E274" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F274" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G274" s="4" t="n">
-        <v>46.38</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="H274" s="7" t="inlineStr">
         <is>
@@ -10879,29 +10879,29 @@
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>User-86</t>
+          <t>User-43</t>
         </is>
       </c>
       <c r="D275" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E275" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F275" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G275" s="4" t="n">
-        <v>80.92</v>
+        <v>52.6</v>
       </c>
       <c r="H275" s="7" t="inlineStr">
         <is>
@@ -10915,29 +10915,29 @@
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.975</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>User-7</t>
+          <t>User-47</t>
         </is>
       </c>
       <c r="D276" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E276" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F276" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G276" s="4" t="n">
-        <v>43.49</v>
+        <v>47.02</v>
       </c>
       <c r="H276" s="7" t="inlineStr">
         <is>
@@ -10951,29 +10951,29 @@
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.976</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>User-9</t>
+          <t>User-74</t>
         </is>
       </c>
       <c r="D277" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E277" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F277" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G277" s="4" t="n">
-        <v>79.61</v>
+        <v>58.3</v>
       </c>
       <c r="H277" s="7" t="inlineStr">
         <is>
@@ -10987,29 +10987,29 @@
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.976</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>User-33</t>
+          <t>User-13</t>
         </is>
       </c>
       <c r="D278" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E278" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F278" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G278" s="4" t="n">
-        <v>69.81</v>
+        <v>44.73</v>
       </c>
       <c r="H278" s="7" t="inlineStr">
         <is>
@@ -11023,29 +11023,29 @@
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.976</t>
+          <t>2026-06-22 05:44:41.031</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>User-49</t>
+          <t>User-97</t>
         </is>
       </c>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E279" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F279" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G279" s="4" t="n">
-        <v>86.12</v>
+        <v>58.42</v>
       </c>
       <c r="H279" s="7" t="inlineStr">
         <is>
@@ -11059,12 +11059,12 @@
       </c>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.976</t>
+          <t>2026-06-22 05:44:41.032</t>
         </is>
       </c>
       <c r="C280" s="4" t="inlineStr">
         <is>
-          <t>User-1</t>
+          <t>User-21</t>
         </is>
       </c>
       <c r="D280" s="4" t="inlineStr">
@@ -11081,7 +11081,7 @@
         <v>200</v>
       </c>
       <c r="G280" s="4" t="n">
-        <v>19.66</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="H280" s="7" t="inlineStr">
         <is>
@@ -11095,29 +11095,29 @@
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.976</t>
+          <t>2026-06-22 05:44:41.032</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>User-89</t>
+          <t>User-78</t>
         </is>
       </c>
       <c r="D281" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E281" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F281" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G281" s="4" t="n">
-        <v>13.65</v>
+        <v>85.48</v>
       </c>
       <c r="H281" s="7" t="inlineStr">
         <is>
@@ -11131,12 +11131,12 @@
       </c>
       <c r="B282" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.976</t>
+          <t>2026-06-22 05:44:41.032</t>
         </is>
       </c>
       <c r="C282" s="4" t="inlineStr">
         <is>
-          <t>User-59</t>
+          <t>User-99</t>
         </is>
       </c>
       <c r="D282" s="4" t="inlineStr">
@@ -11153,7 +11153,7 @@
         <v>200</v>
       </c>
       <c r="G282" s="4" t="n">
-        <v>49.16</v>
+        <v>14.05</v>
       </c>
       <c r="H282" s="7" t="inlineStr">
         <is>
@@ -11167,12 +11167,12 @@
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.976</t>
+          <t>2026-06-22 05:44:41.032</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>User-96</t>
+          <t>User-87</t>
         </is>
       </c>
       <c r="D283" s="4" t="inlineStr">
@@ -11189,7 +11189,7 @@
         <v>200</v>
       </c>
       <c r="G283" s="4" t="n">
-        <v>50.66</v>
+        <v>76.98</v>
       </c>
       <c r="H283" s="7" t="inlineStr">
         <is>
@@ -11203,29 +11203,29 @@
       </c>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.976</t>
+          <t>2026-06-22 05:44:41.032</t>
         </is>
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>User-77</t>
+          <t>User-21</t>
         </is>
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E284" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F284" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G284" s="4" t="n">
-        <v>44.88</v>
+        <v>75.75</v>
       </c>
       <c r="H284" s="7" t="inlineStr">
         <is>
@@ -11239,29 +11239,29 @@
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.976</t>
+          <t>2026-06-22 05:44:41.032</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>User-38</t>
+          <t>User-88</t>
         </is>
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E285" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F285" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G285" s="4" t="n">
-        <v>74.90000000000001</v>
+        <v>29.34</v>
       </c>
       <c r="H285" s="7" t="inlineStr">
         <is>
@@ -11275,29 +11275,29 @@
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.976</t>
+          <t>2026-06-22 05:44:41.032</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>User-97</t>
+          <t>User-72</t>
         </is>
       </c>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E286" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F286" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G286" s="4" t="n">
-        <v>13.18</v>
+        <v>26.5</v>
       </c>
       <c r="H286" s="7" t="inlineStr">
         <is>
@@ -11311,29 +11311,29 @@
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.976</t>
+          <t>2026-06-22 05:44:41.032</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>User-14</t>
+          <t>User-99</t>
         </is>
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E287" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F287" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G287" s="4" t="n">
-        <v>71.59999999999999</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="H287" s="7" t="inlineStr">
         <is>
@@ -11347,29 +11347,29 @@
       </c>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.976</t>
+          <t>2026-06-22 05:44:41.032</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>User-92</t>
+          <t>User-7</t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E288" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F288" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G288" s="4" t="n">
-        <v>92.5</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="H288" s="7" t="inlineStr">
         <is>
@@ -11383,29 +11383,29 @@
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.976</t>
+          <t>2026-06-22 05:44:41.032</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>User-20</t>
+          <t>User-54</t>
         </is>
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E289" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F289" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G289" s="4" t="n">
-        <v>42.31</v>
+        <v>18.54</v>
       </c>
       <c r="H289" s="7" t="inlineStr">
         <is>
@@ -11419,29 +11419,29 @@
       </c>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.976</t>
+          <t>2026-06-22 05:44:41.032</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr">
         <is>
-          <t>User-100</t>
+          <t>User-1</t>
         </is>
       </c>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E290" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F290" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G290" s="4" t="n">
-        <v>31.14</v>
+        <v>13.53</v>
       </c>
       <c r="H290" s="7" t="inlineStr">
         <is>
@@ -11455,29 +11455,29 @@
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.976</t>
+          <t>2026-06-22 05:44:41.032</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>User-97</t>
+          <t>User-45</t>
         </is>
       </c>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E291" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F291" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G291" s="4" t="n">
-        <v>41.81</v>
+        <v>77.12</v>
       </c>
       <c r="H291" s="7" t="inlineStr">
         <is>
@@ -11491,29 +11491,29 @@
       </c>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.976</t>
+          <t>2026-06-22 05:44:41.032</t>
         </is>
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>User-27</t>
+          <t>User-87</t>
         </is>
       </c>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E292" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F292" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G292" s="4" t="n">
-        <v>68.31</v>
+        <v>80.83</v>
       </c>
       <c r="H292" s="7" t="inlineStr">
         <is>
@@ -11527,12 +11527,12 @@
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.976</t>
+          <t>2026-06-22 05:44:41.032</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>User-30</t>
+          <t>User-79</t>
         </is>
       </c>
       <c r="D293" s="4" t="inlineStr">
@@ -11549,7 +11549,7 @@
         <v>200</v>
       </c>
       <c r="G293" s="4" t="n">
-        <v>79.23</v>
+        <v>15.16</v>
       </c>
       <c r="H293" s="7" t="inlineStr">
         <is>
@@ -11563,12 +11563,12 @@
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.976</t>
+          <t>2026-06-22 05:44:41.032</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>User-23</t>
+          <t>User-84</t>
         </is>
       </c>
       <c r="D294" s="4" t="inlineStr">
@@ -11585,7 +11585,7 @@
         <v>200</v>
       </c>
       <c r="G294" s="4" t="n">
-        <v>22.77</v>
+        <v>22.53</v>
       </c>
       <c r="H294" s="7" t="inlineStr">
         <is>
@@ -11599,29 +11599,29 @@
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.976</t>
+          <t>2026-06-22 05:44:41.032</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>User-43</t>
+          <t>User-27</t>
         </is>
       </c>
       <c r="D295" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E295" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F295" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G295" s="4" t="n">
-        <v>76.98</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="H295" s="7" t="inlineStr">
         <is>
@@ -11635,29 +11635,29 @@
       </c>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.976</t>
+          <t>2026-06-22 05:44:41.032</t>
         </is>
       </c>
       <c r="C296" s="4" t="inlineStr">
         <is>
-          <t>User-21</t>
+          <t>User-70</t>
         </is>
       </c>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E296" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F296" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G296" s="4" t="n">
-        <v>53.83</v>
+        <v>5.53</v>
       </c>
       <c r="H296" s="7" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.976</t>
+          <t>2026-06-22 05:44:41.032</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
@@ -11681,19 +11681,19 @@
       </c>
       <c r="D297" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E297" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F297" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G297" s="4" t="n">
-        <v>44.11</v>
+        <v>22.12</v>
       </c>
       <c r="H297" s="7" t="inlineStr">
         <is>
@@ -11707,29 +11707,29 @@
       </c>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.976</t>
+          <t>2026-06-22 05:44:41.032</t>
         </is>
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>User-49</t>
+          <t>User-46</t>
         </is>
       </c>
       <c r="D298" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E298" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F298" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G298" s="4" t="n">
-        <v>28.26</v>
+        <v>48.93</v>
       </c>
       <c r="H298" s="7" t="inlineStr">
         <is>
@@ -11743,29 +11743,29 @@
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.976</t>
+          <t>2026-06-22 05:44:41.032</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>User-59</t>
+          <t>User-7</t>
         </is>
       </c>
       <c r="D299" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E299" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F299" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G299" s="4" t="n">
-        <v>79.95</v>
+        <v>64.39</v>
       </c>
       <c r="H299" s="7" t="inlineStr">
         <is>
@@ -11779,12 +11779,12 @@
       </c>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.976</t>
+          <t>2026-06-22 05:44:41.032</t>
         </is>
       </c>
       <c r="C300" s="4" t="inlineStr">
         <is>
-          <t>User-65</t>
+          <t>User-73</t>
         </is>
       </c>
       <c r="D300" s="4" t="inlineStr">
@@ -11801,7 +11801,7 @@
         <v>200</v>
       </c>
       <c r="G300" s="4" t="n">
-        <v>26.67</v>
+        <v>63.11</v>
       </c>
       <c r="H300" s="7" t="inlineStr">
         <is>
@@ -11815,12 +11815,12 @@
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:21:39.976</t>
+          <t>2026-06-22 05:44:41.032</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>User-83</t>
+          <t>User-51</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
@@ -11837,7 +11837,7 @@
         <v>200</v>
       </c>
       <c r="G301" s="4" t="n">
-        <v>94.14</v>
+        <v>72.64</v>
       </c>
       <c r="H301" s="7" t="inlineStr">
         <is>

--- a/security-testing/scripts/Sentinel_Load_Test_Report.xlsx
+++ b/security-testing/scripts/Sentinel_Load_Test_Report.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41</t>
+          <t>2026-06-22 06:18:52</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>5.3 ms</t>
+          <t>5.1 ms</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>49.4 ms</t>
+          <t>49.8 ms</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>93.6 ms</t>
+          <t>94.6 ms</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>89.7 ms</t>
+          <t>90.2 ms</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -797,12 +797,12 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -811,19 +811,19 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>1</v>
+        <v>0.53</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>48.5</v>
+        <v>44.2</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>93.40000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -834,12 +834,12 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -848,19 +848,19 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.57</v>
+        <v>1.12</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>48.9</v>
+        <v>50.9</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>87.2</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
@@ -871,12 +871,12 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -885,19 +885,19 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>49.8</v>
+        <v>45.8</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>93.3</v>
+        <v>94.2</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
@@ -908,12 +908,12 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -922,19 +922,19 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.88</v>
+        <v>1.03</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>5.3</v>
+        <v>6.1</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>50</v>
+        <v>55.4</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>93</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -959,19 +959,19 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>49.6</v>
+        <v>50</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>93.59999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
@@ -1051,29 +1051,29 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.107</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>User-13</t>
+          <t>User-25</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F2" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>36.55</v>
+        <v>26.91</v>
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
@@ -1087,29 +1087,29 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.107</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>User-56</t>
+          <t>User-57</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>15.56</v>
+        <v>7.82</v>
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
@@ -1123,29 +1123,29 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.107</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>User-80</t>
+          <t>User-28</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>35.67</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
@@ -1159,29 +1159,29 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.107</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>User-55</t>
+          <t>User-53</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>33.35</v>
+        <v>62.11</v>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
@@ -1195,29 +1195,29 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.107</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>User-45</t>
+          <t>User-23</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>67.2</v>
+        <v>19.18</v>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.107</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>User-80</t>
+          <t>User-58</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1253,7 +1253,7 @@
         <v>200</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>13.83</v>
+        <v>65.75</v>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
@@ -1267,29 +1267,29 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.107</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>User-68</t>
+          <t>User-70</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>42.79</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
@@ -1303,29 +1303,29 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.107</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>User-40</t>
+          <t>User-50</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>81.31999999999999</v>
+        <v>61.17</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
@@ -1339,29 +1339,29 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.107</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>User-9</t>
+          <t>User-18</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>90.06</v>
+        <v>63.76</v>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.107</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>User-12</t>
+          <t>User-44</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1397,7 +1397,7 @@
         <v>200</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>41.7</v>
+        <v>91.37</v>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
@@ -1411,29 +1411,29 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.107</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>User-97</t>
+          <t>User-11</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>67.01000000000001</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
@@ -1447,29 +1447,29 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.107</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>User-41</t>
+          <t>User-73</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>64.78</v>
+        <v>55.4</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -1483,29 +1483,29 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.107</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>User-67</t>
+          <t>User-44</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>67.22</v>
+        <v>8.41</v>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
@@ -1519,29 +1519,29 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.107</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>User-36</t>
+          <t>User-62</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>35.63</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
@@ -1555,29 +1555,29 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.107</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>User-2</t>
+          <t>User-3</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>91.56</v>
+        <v>10.48</v>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
@@ -1591,29 +1591,29 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.107</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>User-5</t>
+          <t>User-26</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>37.12</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
@@ -1627,29 +1627,29 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.107</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>User-76</t>
+          <t>User-7</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>47.88</v>
+        <v>90.2</v>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
@@ -1663,29 +1663,29 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.107</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>User-77</t>
+          <t>User-17</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>87.16</v>
+        <v>79.3</v>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
@@ -1699,29 +1699,29 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.107</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>User-36</t>
+          <t>User-12</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>66.04000000000001</v>
+        <v>35.98</v>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
@@ -1735,12 +1735,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.107</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>User-49</t>
+          <t>User-22</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1757,7 +1757,7 @@
         <v>200</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>6.04</v>
+        <v>40.27</v>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
@@ -1771,12 +1771,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.107</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>User-39</t>
+          <t>User-86</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1793,7 +1793,7 @@
         <v>200</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>70.45999999999999</v>
+        <v>49.65</v>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
@@ -1807,29 +1807,29 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.107</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>User-17</t>
+          <t>User-64</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>83.09</v>
+        <v>18.82</v>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
@@ -1843,29 +1843,29 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.107</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>User-39</t>
+          <t>User-89</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>92.03</v>
+        <v>53.38</v>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
@@ -1879,29 +1879,29 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.107</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>User-67</t>
+          <t>User-30</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>90.23999999999999</v>
+        <v>46.12</v>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
@@ -1915,29 +1915,29 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>User-37</t>
+          <t>User-57</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>36.05</v>
+        <v>31.31</v>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
@@ -1951,29 +1951,29 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>User-88</t>
+          <t>User-85</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>32.7</v>
+        <v>28.58</v>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
@@ -1987,29 +1987,29 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>User-37</t>
+          <t>User-14</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>45.21</v>
+        <v>55.01</v>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
@@ -2023,12 +2023,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>User-22</t>
+          <t>User-8</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -2045,7 +2045,7 @@
         <v>200</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>56.44</v>
+        <v>45.91</v>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
@@ -2059,29 +2059,29 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>User-20</t>
+          <t>User-52</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>58.42</v>
+        <v>87.55</v>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>User-56</t>
+          <t>User-61</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -2117,7 +2117,7 @@
         <v>200</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>57.45</v>
+        <v>71.87</v>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2141,19 +2141,19 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>78.66</v>
+        <v>79.31</v>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
@@ -2167,29 +2167,29 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>User-78</t>
+          <t>User-44</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F33" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>56.94</v>
+        <v>28.32</v>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
@@ -2203,29 +2203,29 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>User-12</t>
+          <t>User-96</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F34" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>59.14</v>
+        <v>48.33</v>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
@@ -2239,12 +2239,12 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>User-94</t>
+          <t>User-25</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2261,7 +2261,7 @@
         <v>200</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>82.38</v>
+        <v>50.4</v>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
@@ -2275,12 +2275,12 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>User-96</t>
+          <t>User-82</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2297,7 +2297,7 @@
         <v>200</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>79.22</v>
+        <v>30.73</v>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
@@ -2311,12 +2311,12 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>User-13</t>
+          <t>User-81</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2333,7 +2333,7 @@
         <v>200</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>64.27</v>
+        <v>59.67</v>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
@@ -2347,29 +2347,29 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>User-55</t>
+          <t>User-94</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F38" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>78.53</v>
+        <v>12.35</v>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
@@ -2383,12 +2383,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>User-41</t>
+          <t>User-9</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2405,7 +2405,7 @@
         <v>200</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>65.56</v>
+        <v>61.22</v>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
@@ -2419,29 +2419,29 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>User-18</t>
+          <t>User-6</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>43.87</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
@@ -2455,29 +2455,29 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>User-81</t>
+          <t>User-2</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>43.97</v>
+        <v>30.95</v>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
@@ -2491,29 +2491,29 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>User-71</t>
+          <t>User-69</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>37.91</v>
+        <v>69.38</v>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
@@ -2527,12 +2527,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>User-27</t>
+          <t>User-16</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2549,7 +2549,7 @@
         <v>200</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>82.8</v>
+        <v>55.26</v>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>User-67</t>
+          <t>User-5</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2585,7 +2585,7 @@
         <v>200</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>49.34</v>
+        <v>6.1</v>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
@@ -2599,29 +2599,29 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>User-95</t>
+          <t>User-80</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>34.84</v>
+        <v>7.39</v>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
@@ -2635,12 +2635,12 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>User-67</t>
+          <t>User-94</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2657,7 +2657,7 @@
         <v>200</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>92.64</v>
+        <v>45.89</v>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
@@ -2671,29 +2671,29 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>User-72</t>
+          <t>User-3</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>49.47</v>
+        <v>56.17</v>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>User-65</t>
+          <t>User-2</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2729,7 +2729,7 @@
         <v>200</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>42.57</v>
+        <v>93.53</v>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
@@ -2743,29 +2743,29 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>User-17</t>
+          <t>User-1</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F49" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>16.18</v>
+        <v>64.55</v>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>User-88</t>
+          <t>User-64</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2801,7 +2801,7 @@
         <v>200</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>76.76000000000001</v>
+        <v>68.45</v>
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
@@ -2815,29 +2815,29 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>User-33</t>
+          <t>User-29</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F51" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>10.22</v>
+        <v>44.91</v>
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
@@ -2851,29 +2851,29 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>User-20</t>
+          <t>User-74</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F52" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>64.12</v>
+        <v>82.31</v>
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
@@ -2887,29 +2887,29 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>User-6</t>
+          <t>User-33</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F53" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>53.09</v>
+        <v>94.56</v>
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
@@ -2923,29 +2923,29 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>User-55</t>
+          <t>User-60</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F54" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>41.65</v>
+        <v>57.24</v>
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
@@ -2959,12 +2959,12 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>User-93</t>
+          <t>User-30</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -2981,7 +2981,7 @@
         <v>200</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>31.77</v>
+        <v>13.78</v>
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
@@ -2995,29 +2995,29 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>User-15</t>
+          <t>User-88</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F56" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>14.45</v>
+        <v>60.75</v>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
@@ -3031,29 +3031,29 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>User-70</t>
+          <t>User-72</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F57" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>34.69</v>
+        <v>20.82</v>
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
@@ -3067,12 +3067,12 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>User-14</t>
+          <t>User-45</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3089,7 +3089,7 @@
         <v>200</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>93.41</v>
+        <v>59.06</v>
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
@@ -3103,29 +3103,29 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>User-37</t>
+          <t>User-5</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F59" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>88.61</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
@@ -3139,29 +3139,29 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>User-26</t>
+          <t>User-61</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F60" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>71.06</v>
+        <v>46.54</v>
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
@@ -3175,12 +3175,12 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>User-31</t>
+          <t>User-26</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -3197,7 +3197,7 @@
         <v>200</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>45.95</v>
+        <v>39.61</v>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
@@ -3211,29 +3211,29 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>User-99</t>
+          <t>User-19</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F62" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>7</v>
+        <v>59.2</v>
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
@@ -3247,29 +3247,29 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>User-49</t>
+          <t>User-71</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F63" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>90.3</v>
+        <v>49.31</v>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
@@ -3283,29 +3283,29 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>User-43</t>
+          <t>User-64</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F64" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>26.52</v>
+        <v>42.24</v>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
@@ -3319,29 +3319,29 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>User-52</t>
+          <t>User-56</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F65" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>54.13</v>
+        <v>39.19</v>
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>User-52</t>
+          <t>User-65</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -3377,7 +3377,7 @@
         <v>200</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>70.26000000000001</v>
+        <v>24.21</v>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
@@ -3391,29 +3391,29 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.030</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>User-47</t>
+          <t>User-76</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F67" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>21.18</v>
+        <v>48.46</v>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
@@ -3427,29 +3427,29 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>User-54</t>
+          <t>User-72</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F68" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>82.75</v>
+        <v>79.39</v>
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
@@ -3463,29 +3463,29 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>User-73</t>
+          <t>User-70</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F69" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>44</v>
+        <v>34.12</v>
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
@@ -3499,29 +3499,29 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>User-68</t>
+          <t>User-65</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F70" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>76.92</v>
+        <v>22.93</v>
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
@@ -3535,29 +3535,29 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>User-15</t>
+          <t>User-66</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F71" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>36.26</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>User-92</t>
+          <t>User-12</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -3593,7 +3593,7 @@
         <v>200</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>8.26</v>
+        <v>73.66</v>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
@@ -3607,29 +3607,29 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>User-58</t>
+          <t>User-6</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F73" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>7.91</v>
+        <v>5.09</v>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
@@ -3643,29 +3643,29 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>User-41</t>
+          <t>User-19</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F74" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>26.25</v>
+        <v>38.83</v>
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
@@ -3679,29 +3679,29 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>User-74</t>
+          <t>User-82</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F75" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>51.22</v>
+        <v>34.41</v>
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
@@ -3715,29 +3715,29 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>User-94</t>
+          <t>User-90</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F76" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>25.61</v>
+        <v>10.99</v>
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
@@ -3751,29 +3751,29 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>User-73</t>
+          <t>User-10</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F77" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>48.17</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
@@ -3787,29 +3787,29 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>User-44</t>
+          <t>User-6</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F78" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>62.03</v>
+        <v>58.08</v>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
@@ -3823,29 +3823,29 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>User-71</t>
+          <t>User-99</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F79" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>40.59</v>
+        <v>39.62</v>
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
@@ -3859,29 +3859,29 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>User-13</t>
+          <t>User-93</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F80" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>31.64</v>
+        <v>49.58</v>
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
@@ -3895,12 +3895,12 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>User-85</t>
+          <t>User-59</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -3917,7 +3917,7 @@
         <v>200</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>21.53</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
@@ -3931,29 +3931,29 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>User-45</t>
+          <t>User-41</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F82" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>59.94</v>
+        <v>71.37</v>
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
@@ -3967,29 +3967,29 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>User-65</t>
+          <t>User-27</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F83" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>33.64</v>
+        <v>57.89</v>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
@@ -4003,29 +4003,29 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>User-34</t>
+          <t>User-31</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F84" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>77.92</v>
+        <v>6.27</v>
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
@@ -4039,12 +4039,12 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>User-46</t>
+          <t>User-17</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -4061,7 +4061,7 @@
         <v>200</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>66.45999999999999</v>
+        <v>40.04</v>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
@@ -4075,12 +4075,12 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>User-89</t>
+          <t>User-12</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -4097,7 +4097,7 @@
         <v>200</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>78.40000000000001</v>
+        <v>53.76</v>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
@@ -4111,29 +4111,29 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>User-80</t>
+          <t>User-40</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F87" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>77.56999999999999</v>
+        <v>44.11</v>
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
@@ -4147,29 +4147,29 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>User-81</t>
+          <t>User-36</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F88" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>32.09</v>
+        <v>66.98</v>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
@@ -4183,29 +4183,29 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>User-27</t>
+          <t>User-70</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F89" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>26.45</v>
+        <v>45.19</v>
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
@@ -4219,29 +4219,29 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>User-17</t>
+          <t>User-26</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F90" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>70.88</v>
+        <v>31.07</v>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
@@ -4255,29 +4255,29 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>User-8</t>
+          <t>User-38</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F91" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
@@ -4291,29 +4291,29 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>User-79</t>
+          <t>User-42</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F92" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>16.75</v>
+        <v>13.55</v>
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
@@ -4327,29 +4327,29 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>User-82</t>
+          <t>User-86</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F93" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>18.27</v>
+        <v>19.59</v>
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
@@ -4363,29 +4363,29 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>User-75</t>
+          <t>User-14</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F94" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>67.56</v>
+        <v>8.56</v>
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
@@ -4399,29 +4399,29 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>User-76</t>
+          <t>User-97</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F95" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>64.52</v>
+        <v>19.67</v>
       </c>
       <c r="H95" s="7" t="inlineStr">
         <is>
@@ -4435,29 +4435,29 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>User-86</t>
+          <t>User-34</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F96" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>50.22</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="H96" s="7" t="inlineStr">
         <is>
@@ -4471,29 +4471,29 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>User-4</t>
+          <t>User-3</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F97" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>63.95</v>
+        <v>34.18</v>
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
@@ -4507,29 +4507,29 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>User-80</t>
+          <t>User-97</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F98" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>71.88</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
@@ -4543,29 +4543,29 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>User-44</t>
+          <t>User-47</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F99" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>85.41</v>
+        <v>16.06</v>
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
@@ -4579,29 +4579,29 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>User-23</t>
+          <t>User-98</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F100" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>30.03</v>
+        <v>59.58</v>
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
@@ -4615,29 +4615,29 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>User-72</t>
+          <t>User-61</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F101" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>13.34</v>
+        <v>91.77</v>
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
@@ -4651,29 +4651,29 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>User-13</t>
+          <t>User-46</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F102" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>10.52</v>
+        <v>41.59</v>
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
@@ -4687,29 +4687,29 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>User-68</t>
+          <t>User-54</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F103" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>93.28</v>
+        <v>22.13</v>
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
@@ -4723,12 +4723,12 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>User-49</t>
+          <t>User-91</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -4745,7 +4745,7 @@
         <v>200</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>93.59999999999999</v>
+        <v>15.81</v>
       </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
@@ -4759,29 +4759,29 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>User-9</t>
+          <t>User-22</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F105" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>51.37</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
@@ -4795,29 +4795,29 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>User-35</t>
+          <t>User-26</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F106" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>54.85</v>
+        <v>65.22</v>
       </c>
       <c r="H106" s="7" t="inlineStr">
         <is>
@@ -4831,29 +4831,29 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>User-33</t>
+          <t>User-56</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F107" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>67.48</v>
+        <v>14.94</v>
       </c>
       <c r="H107" s="7" t="inlineStr">
         <is>
@@ -4867,29 +4867,29 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>User-79</t>
+          <t>User-64</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F108" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>10.77</v>
+        <v>25.17</v>
       </c>
       <c r="H108" s="7" t="inlineStr">
         <is>
@@ -4903,29 +4903,29 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>User-65</t>
+          <t>User-17</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F109" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>85.09</v>
+        <v>23.61</v>
       </c>
       <c r="H109" s="7" t="inlineStr">
         <is>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>User-41</t>
+          <t>User-7</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -4961,7 +4961,7 @@
         <v>200</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>13.21</v>
+        <v>81.17</v>
       </c>
       <c r="H110" s="7" t="inlineStr">
         <is>
@@ -4975,12 +4975,12 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>User-20</t>
+          <t>User-19</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
@@ -4997,7 +4997,7 @@
         <v>200</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>29.47</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="H111" s="7" t="inlineStr">
         <is>
@@ -5011,29 +5011,29 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>User-43</t>
+          <t>User-33</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F112" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>16.64</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="H112" s="7" t="inlineStr">
         <is>
@@ -5047,29 +5047,29 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>User-88</t>
+          <t>User-12</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F113" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>11.86</v>
+        <v>75.06</v>
       </c>
       <c r="H113" s="7" t="inlineStr">
         <is>
@@ -5083,29 +5083,29 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>User-9</t>
+          <t>User-34</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F114" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>24.95</v>
+        <v>6.48</v>
       </c>
       <c r="H114" s="7" t="inlineStr">
         <is>
@@ -5119,29 +5119,29 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>User-92</t>
+          <t>User-57</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F115" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>57.53</v>
+        <v>67.02</v>
       </c>
       <c r="H115" s="7" t="inlineStr">
         <is>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>User-79</t>
+          <t>User-52</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
@@ -5177,7 +5177,7 @@
         <v>200</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>38.58</v>
+        <v>80.15000000000001</v>
       </c>
       <c r="H116" s="7" t="inlineStr">
         <is>
@@ -5191,29 +5191,29 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>User-15</t>
+          <t>User-29</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F117" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>79.16</v>
+        <v>31.66</v>
       </c>
       <c r="H117" s="7" t="inlineStr">
         <is>
@@ -5227,29 +5227,29 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>User-11</t>
+          <t>User-41</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F118" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>90.08</v>
+        <v>60.93</v>
       </c>
       <c r="H118" s="7" t="inlineStr">
         <is>
@@ -5263,29 +5263,29 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>User-2</t>
+          <t>User-81</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F119" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G119" s="4" t="n">
-        <v>62.14</v>
+        <v>41.62</v>
       </c>
       <c r="H119" s="7" t="inlineStr">
         <is>
@@ -5299,29 +5299,29 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>User-83</t>
+          <t>User-36</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F120" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>60.07</v>
+        <v>51.28</v>
       </c>
       <c r="H120" s="7" t="inlineStr">
         <is>
@@ -5335,12 +5335,12 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>User-56</t>
+          <t>User-100</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -5357,7 +5357,7 @@
         <v>200</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>48.09</v>
+        <v>93.25</v>
       </c>
       <c r="H121" s="7" t="inlineStr">
         <is>
@@ -5371,29 +5371,29 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>User-25</t>
+          <t>User-65</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F122" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>66.95</v>
+        <v>53.27</v>
       </c>
       <c r="H122" s="7" t="inlineStr">
         <is>
@@ -5407,29 +5407,29 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>User-50</t>
+          <t>User-11</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F123" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>75.28</v>
+        <v>18.95</v>
       </c>
       <c r="H123" s="7" t="inlineStr">
         <is>
@@ -5443,12 +5443,12 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>User-68</t>
+          <t>User-79</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
@@ -5465,7 +5465,7 @@
         <v>200</v>
       </c>
       <c r="G124" s="4" t="n">
-        <v>36.32</v>
+        <v>31.91</v>
       </c>
       <c r="H124" s="7" t="inlineStr">
         <is>
@@ -5479,29 +5479,29 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>User-36</t>
+          <t>User-74</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F125" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>91.23999999999999</v>
+        <v>38.89</v>
       </c>
       <c r="H125" s="7" t="inlineStr">
         <is>
@@ -5515,29 +5515,29 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>User-66</t>
+          <t>User-64</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F126" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>12.37</v>
+        <v>54.3</v>
       </c>
       <c r="H126" s="7" t="inlineStr">
         <is>
@@ -5551,12 +5551,12 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>User-97</t>
+          <t>User-87</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
@@ -5573,7 +5573,7 @@
         <v>200</v>
       </c>
       <c r="G127" s="4" t="n">
-        <v>9.119999999999999</v>
+        <v>27.74</v>
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
@@ -5587,29 +5587,29 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>User-84</t>
+          <t>User-23</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F128" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>27.86</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="H128" s="7" t="inlineStr">
         <is>
@@ -5623,29 +5623,29 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>User-16</t>
+          <t>User-50</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F129" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G129" s="4" t="n">
-        <v>55.45</v>
+        <v>71.84</v>
       </c>
       <c r="H129" s="7" t="inlineStr">
         <is>
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>User-80</t>
+          <t>User-90</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
@@ -5681,7 +5681,7 @@
         <v>200</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>87.81</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="H130" s="7" t="inlineStr">
         <is>
@@ -5695,12 +5695,12 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>User-53</t>
+          <t>User-96</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -5717,7 +5717,7 @@
         <v>200</v>
       </c>
       <c r="G131" s="4" t="n">
-        <v>62.93</v>
+        <v>22.51</v>
       </c>
       <c r="H131" s="7" t="inlineStr">
         <is>
@@ -5731,29 +5731,29 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>User-73</t>
+          <t>User-4</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F132" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>20.57</v>
+        <v>9.9</v>
       </c>
       <c r="H132" s="7" t="inlineStr">
         <is>
@@ -5767,29 +5767,29 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>User-12</t>
+          <t>User-75</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F133" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G133" s="4" t="n">
-        <v>5.32</v>
+        <v>82.41</v>
       </c>
       <c r="H133" s="7" t="inlineStr">
         <is>
@@ -5803,29 +5803,29 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>User-45</t>
+          <t>User-98</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F134" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>30.86</v>
+        <v>24.93</v>
       </c>
       <c r="H134" s="7" t="inlineStr">
         <is>
@@ -5839,29 +5839,29 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>User-88</t>
+          <t>User-40</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F135" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G135" s="4" t="n">
-        <v>13.8</v>
+        <v>25.76</v>
       </c>
       <c r="H135" s="7" t="inlineStr">
         <is>
@@ -5875,29 +5875,29 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>User-82</t>
+          <t>User-20</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F136" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G136" s="4" t="n">
-        <v>61.76</v>
+        <v>25.26</v>
       </c>
       <c r="H136" s="7" t="inlineStr">
         <is>
@@ -5911,29 +5911,29 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>User-7</t>
+          <t>User-91</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F137" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G137" s="4" t="n">
-        <v>64.70999999999999</v>
+        <v>43.51</v>
       </c>
       <c r="H137" s="7" t="inlineStr">
         <is>
@@ -5947,29 +5947,29 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>User-84</t>
+          <t>User-6</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F138" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>36.79</v>
+        <v>82.92</v>
       </c>
       <c r="H138" s="7" t="inlineStr">
         <is>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>User-17</t>
+          <t>User-3</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
@@ -6005,7 +6005,7 @@
         <v>200</v>
       </c>
       <c r="G139" s="4" t="n">
-        <v>78.95</v>
+        <v>84.81999999999999</v>
       </c>
       <c r="H139" s="7" t="inlineStr">
         <is>
@@ -6019,29 +6019,29 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>User-50</t>
+          <t>User-19</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F140" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>87.75</v>
+        <v>34.18</v>
       </c>
       <c r="H140" s="7" t="inlineStr">
         <is>
@@ -6055,29 +6055,29 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>User-23</t>
+          <t>User-71</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F141" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G141" s="4" t="n">
-        <v>47.57</v>
+        <v>61.59</v>
       </c>
       <c r="H141" s="7" t="inlineStr">
         <is>
@@ -6091,29 +6091,29 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>User-6</t>
+          <t>User-88</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F142" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G142" s="4" t="n">
-        <v>43.19</v>
+        <v>17.3</v>
       </c>
       <c r="H142" s="7" t="inlineStr">
         <is>
@@ -6127,29 +6127,29 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>User-88</t>
+          <t>User-26</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F143" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G143" s="4" t="n">
-        <v>80.84</v>
+        <v>28.72</v>
       </c>
       <c r="H143" s="7" t="inlineStr">
         <is>
@@ -6163,29 +6163,29 @@
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>User-99</t>
+          <t>User-97</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F144" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G144" s="4" t="n">
-        <v>49.82</v>
+        <v>43.68</v>
       </c>
       <c r="H144" s="7" t="inlineStr">
         <is>
@@ -6199,29 +6199,29 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>User-99</t>
+          <t>User-7</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F145" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G145" s="4" t="n">
-        <v>53.12</v>
+        <v>87.39</v>
       </c>
       <c r="H145" s="7" t="inlineStr">
         <is>
@@ -6235,29 +6235,29 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>User-73</t>
+          <t>User-50</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F146" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G146" s="4" t="n">
-        <v>38</v>
+        <v>61.52</v>
       </c>
       <c r="H146" s="7" t="inlineStr">
         <is>
@@ -6271,29 +6271,29 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>User-56</t>
+          <t>User-67</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F147" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G147" s="4" t="n">
-        <v>86.13</v>
+        <v>10.39</v>
       </c>
       <c r="H147" s="7" t="inlineStr">
         <is>
@@ -6307,12 +6307,12 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>User-8</t>
+          <t>User-69</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
@@ -6329,7 +6329,7 @@
         <v>200</v>
       </c>
       <c r="G148" s="4" t="n">
-        <v>11.08</v>
+        <v>29.48</v>
       </c>
       <c r="H148" s="7" t="inlineStr">
         <is>
@@ -6343,29 +6343,29 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>User-79</t>
+          <t>User-37</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F149" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G149" s="4" t="n">
-        <v>80.19</v>
+        <v>27.72</v>
       </c>
       <c r="H149" s="7" t="inlineStr">
         <is>
@@ -6379,29 +6379,29 @@
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>User-59</t>
+          <t>User-23</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F150" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G150" s="4" t="n">
-        <v>56.91</v>
+        <v>55.12</v>
       </c>
       <c r="H150" s="7" t="inlineStr">
         <is>
@@ -6415,29 +6415,29 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>User-1</t>
+          <t>User-52</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F151" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G151" s="4" t="n">
-        <v>85.31</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H151" s="7" t="inlineStr">
         <is>
@@ -6451,29 +6451,29 @@
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>User-35</t>
+          <t>User-46</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F152" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G152" s="4" t="n">
-        <v>48.02</v>
+        <v>56.75</v>
       </c>
       <c r="H152" s="7" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -6497,19 +6497,19 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F153" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G153" s="4" t="n">
-        <v>43.71</v>
+        <v>24.52</v>
       </c>
       <c r="H153" s="7" t="inlineStr">
         <is>
@@ -6523,29 +6523,29 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>User-64</t>
+          <t>User-4</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F154" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G154" s="4" t="n">
-        <v>40.26</v>
+        <v>42.92</v>
       </c>
       <c r="H154" s="7" t="inlineStr">
         <is>
@@ -6559,29 +6559,29 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>User-73</t>
+          <t>User-96</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F155" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G155" s="4" t="n">
-        <v>68.65000000000001</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="H155" s="7" t="inlineStr">
         <is>
@@ -6595,29 +6595,29 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>User-26</t>
+          <t>User-55</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F156" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G156" s="4" t="n">
-        <v>60.57</v>
+        <v>27.14</v>
       </c>
       <c r="H156" s="7" t="inlineStr">
         <is>
@@ -6631,29 +6631,29 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>User-8</t>
+          <t>User-35</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F157" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G157" s="4" t="n">
-        <v>53.13</v>
+        <v>48.39</v>
       </c>
       <c r="H157" s="7" t="inlineStr">
         <is>
@@ -6667,29 +6667,29 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>User-56</t>
+          <t>User-62</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F158" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G158" s="4" t="n">
-        <v>35.61</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="H158" s="7" t="inlineStr">
         <is>
@@ -6703,29 +6703,29 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>User-33</t>
+          <t>User-44</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F159" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G159" s="4" t="n">
-        <v>57.19</v>
+        <v>29.43</v>
       </c>
       <c r="H159" s="7" t="inlineStr">
         <is>
@@ -6739,12 +6739,12 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>User-27</t>
+          <t>User-68</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
@@ -6761,7 +6761,7 @@
         <v>200</v>
       </c>
       <c r="G160" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="H160" s="7" t="inlineStr">
         <is>
@@ -6775,29 +6775,29 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>User-97</t>
+          <t>User-89</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F161" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G161" s="4" t="n">
-        <v>92.95</v>
+        <v>57.48</v>
       </c>
       <c r="H161" s="7" t="inlineStr">
         <is>
@@ -6811,29 +6811,29 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>User-65</t>
+          <t>User-56</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F162" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G162" s="4" t="n">
-        <v>31.39</v>
+        <v>68.86</v>
       </c>
       <c r="H162" s="7" t="inlineStr">
         <is>
@@ -6847,12 +6847,12 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>User-62</t>
+          <t>User-96</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
@@ -6869,7 +6869,7 @@
         <v>200</v>
       </c>
       <c r="G163" s="4" t="n">
-        <v>33.23</v>
+        <v>27.76</v>
       </c>
       <c r="H163" s="7" t="inlineStr">
         <is>
@@ -6883,29 +6883,29 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>User-92</t>
+          <t>User-26</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F164" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G164" s="4" t="n">
-        <v>72.63</v>
+        <v>16.87</v>
       </c>
       <c r="H164" s="7" t="inlineStr">
         <is>
@@ -6919,12 +6919,12 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>User-78</t>
+          <t>User-31</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
@@ -6941,7 +6941,7 @@
         <v>200</v>
       </c>
       <c r="G165" s="4" t="n">
-        <v>14.8</v>
+        <v>59.62</v>
       </c>
       <c r="H165" s="7" t="inlineStr">
         <is>
@@ -6955,29 +6955,29 @@
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>User-55</t>
+          <t>User-51</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F166" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G166" s="4" t="n">
-        <v>23.05</v>
+        <v>52.15</v>
       </c>
       <c r="H166" s="7" t="inlineStr">
         <is>
@@ -6991,12 +6991,12 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>User-80</t>
+          <t>User-5</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
@@ -7013,7 +7013,7 @@
         <v>200</v>
       </c>
       <c r="G167" s="4" t="n">
-        <v>74.63</v>
+        <v>18.76</v>
       </c>
       <c r="H167" s="7" t="inlineStr">
         <is>
@@ -7027,29 +7027,29 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>User-7</t>
+          <t>User-19</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F168" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G168" s="4" t="n">
-        <v>68.65000000000001</v>
+        <v>25.91</v>
       </c>
       <c r="H168" s="7" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
@@ -7073,19 +7073,19 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F169" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G169" s="4" t="n">
-        <v>11.16</v>
+        <v>16.67</v>
       </c>
       <c r="H169" s="7" t="inlineStr">
         <is>
@@ -7099,12 +7099,12 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>User-57</t>
+          <t>User-81</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
@@ -7121,7 +7121,7 @@
         <v>200</v>
       </c>
       <c r="G170" s="4" t="n">
-        <v>24.45</v>
+        <v>94.37</v>
       </c>
       <c r="H170" s="7" t="inlineStr">
         <is>
@@ -7135,29 +7135,29 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>User-8</t>
+          <t>User-22</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F171" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G171" s="4" t="n">
-        <v>23.59</v>
+        <v>78.78</v>
       </c>
       <c r="H171" s="7" t="inlineStr">
         <is>
@@ -7171,29 +7171,29 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>User-15</t>
+          <t>User-63</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F172" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G172" s="4" t="n">
-        <v>71.70999999999999</v>
+        <v>34.76</v>
       </c>
       <c r="H172" s="7" t="inlineStr">
         <is>
@@ -7207,29 +7207,29 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>User-5</t>
+          <t>User-18</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F173" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G173" s="4" t="n">
-        <v>64.18000000000001</v>
+        <v>94.25</v>
       </c>
       <c r="H173" s="7" t="inlineStr">
         <is>
@@ -7243,29 +7243,29 @@
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>User-36</t>
+          <t>User-80</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F174" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G174" s="4" t="n">
-        <v>54.31</v>
+        <v>69</v>
       </c>
       <c r="H174" s="7" t="inlineStr">
         <is>
@@ -7279,29 +7279,29 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>User-13</t>
+          <t>User-97</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F175" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G175" s="4" t="n">
-        <v>75.48999999999999</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="H175" s="7" t="inlineStr">
         <is>
@@ -7315,29 +7315,29 @@
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>User-72</t>
+          <t>User-90</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F176" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G176" s="4" t="n">
-        <v>35.68</v>
+        <v>79.7</v>
       </c>
       <c r="H176" s="7" t="inlineStr">
         <is>
@@ -7351,29 +7351,29 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>User-2</t>
+          <t>User-9</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F177" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G177" s="4" t="n">
-        <v>28.28</v>
+        <v>39.08</v>
       </c>
       <c r="H177" s="7" t="inlineStr">
         <is>
@@ -7387,29 +7387,29 @@
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>User-78</t>
+          <t>User-54</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F178" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G178" s="4" t="n">
-        <v>84.29000000000001</v>
+        <v>87.66</v>
       </c>
       <c r="H178" s="7" t="inlineStr">
         <is>
@@ -7423,29 +7423,29 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>User-87</t>
+          <t>User-19</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F179" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G179" s="4" t="n">
-        <v>39.64</v>
+        <v>44.35</v>
       </c>
       <c r="H179" s="7" t="inlineStr">
         <is>
@@ -7459,29 +7459,29 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>User-2</t>
+          <t>User-79</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F180" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G180" s="4" t="n">
-        <v>38.48</v>
+        <v>28.89</v>
       </c>
       <c r="H180" s="7" t="inlineStr">
         <is>
@@ -7495,29 +7495,29 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>User-74</t>
+          <t>User-52</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F181" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G181" s="4" t="n">
-        <v>19.83</v>
+        <v>94.2</v>
       </c>
       <c r="H181" s="7" t="inlineStr">
         <is>
@@ -7531,29 +7531,29 @@
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>User-8</t>
+          <t>User-86</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F182" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G182" s="4" t="n">
-        <v>18.58</v>
+        <v>14.19</v>
       </c>
       <c r="H182" s="7" t="inlineStr">
         <is>
@@ -7567,29 +7567,29 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>User-100</t>
+          <t>User-93</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F183" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G183" s="4" t="n">
-        <v>31.03</v>
+        <v>33.73</v>
       </c>
       <c r="H183" s="7" t="inlineStr">
         <is>
@@ -7603,29 +7603,29 @@
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>User-30</t>
+          <t>User-25</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F184" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G184" s="4" t="n">
-        <v>15.43</v>
+        <v>68.8</v>
       </c>
       <c r="H184" s="7" t="inlineStr">
         <is>
@@ -7639,29 +7639,29 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>User-17</t>
+          <t>User-19</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F185" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G185" s="4" t="n">
-        <v>39.25</v>
+        <v>11.4</v>
       </c>
       <c r="H185" s="7" t="inlineStr">
         <is>
@@ -7675,29 +7675,29 @@
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>User-22</t>
+          <t>User-82</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F186" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G186" s="4" t="n">
-        <v>29.55</v>
+        <v>18.95</v>
       </c>
       <c r="H186" s="7" t="inlineStr">
         <is>
@@ -7711,29 +7711,29 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>User-43</t>
+          <t>User-66</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F187" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G187" s="4" t="n">
-        <v>43.38</v>
+        <v>44.74</v>
       </c>
       <c r="H187" s="7" t="inlineStr">
         <is>
@@ -7747,29 +7747,29 @@
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>User-10</t>
+          <t>User-1</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F188" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G188" s="4" t="n">
-        <v>19.57</v>
+        <v>9.24</v>
       </c>
       <c r="H188" s="7" t="inlineStr">
         <is>
@@ -7783,29 +7783,29 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>User-16</t>
+          <t>User-37</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F189" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G189" s="4" t="n">
-        <v>45.53</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="H189" s="7" t="inlineStr">
         <is>
@@ -7819,12 +7819,12 @@
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>User-3</t>
+          <t>User-26</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
@@ -7841,7 +7841,7 @@
         <v>200</v>
       </c>
       <c r="G190" s="4" t="n">
-        <v>46.65</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="H190" s="7" t="inlineStr">
         <is>
@@ -7855,29 +7855,29 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>User-99</t>
+          <t>User-71</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F191" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G191" s="4" t="n">
-        <v>16.54</v>
+        <v>43.81</v>
       </c>
       <c r="H191" s="7" t="inlineStr">
         <is>
@@ -7891,29 +7891,29 @@
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>User-60</t>
+          <t>User-20</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F192" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G192" s="4" t="n">
-        <v>24.92</v>
+        <v>13.89</v>
       </c>
       <c r="H192" s="7" t="inlineStr">
         <is>
@@ -7927,29 +7927,29 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>User-3</t>
+          <t>User-25</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F193" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G193" s="4" t="n">
-        <v>76.06999999999999</v>
+        <v>47.83</v>
       </c>
       <c r="H193" s="7" t="inlineStr">
         <is>
@@ -7963,29 +7963,29 @@
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>User-23</t>
+          <t>User-44</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F194" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G194" s="4" t="n">
-        <v>15.3</v>
+        <v>33.63</v>
       </c>
       <c r="H194" s="7" t="inlineStr">
         <is>
@@ -7999,29 +7999,29 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>User-37</t>
+          <t>User-62</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F195" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G195" s="4" t="n">
-        <v>25.16</v>
+        <v>14.89</v>
       </c>
       <c r="H195" s="7" t="inlineStr">
         <is>
@@ -8035,29 +8035,29 @@
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>User-57</t>
+          <t>User-33</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F196" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G196" s="4" t="n">
-        <v>51.21</v>
+        <v>71.13</v>
       </c>
       <c r="H196" s="7" t="inlineStr">
         <is>
@@ -8071,29 +8071,29 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>User-20</t>
+          <t>User-60</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F197" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G197" s="4" t="n">
-        <v>68.18000000000001</v>
+        <v>51.2</v>
       </c>
       <c r="H197" s="7" t="inlineStr">
         <is>
@@ -8107,29 +8107,29 @@
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>User-66</t>
+          <t>User-91</t>
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E198" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F198" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G198" s="4" t="n">
-        <v>41.55</v>
+        <v>15.53</v>
       </c>
       <c r="H198" s="7" t="inlineStr">
         <is>
@@ -8143,29 +8143,29 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>User-20</t>
+          <t>User-18</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F199" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G199" s="4" t="n">
-        <v>87.44</v>
+        <v>18.79</v>
       </c>
       <c r="H199" s="7" t="inlineStr">
         <is>
@@ -8179,29 +8179,29 @@
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>User-13</t>
+          <t>User-67</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E200" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F200" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G200" s="4" t="n">
-        <v>9.640000000000001</v>
+        <v>36.03</v>
       </c>
       <c r="H200" s="7" t="inlineStr">
         <is>
@@ -8215,29 +8215,29 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>User-22</t>
+          <t>User-33</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F201" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G201" s="4" t="n">
-        <v>89.70999999999999</v>
+        <v>5.42</v>
       </c>
       <c r="H201" s="7" t="inlineStr">
         <is>
@@ -8251,29 +8251,29 @@
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>User-94</t>
+          <t>User-91</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E202" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F202" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G202" s="4" t="n">
-        <v>48.71</v>
+        <v>7.25</v>
       </c>
       <c r="H202" s="7" t="inlineStr">
         <is>
@@ -8287,29 +8287,29 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>User-79</t>
+          <t>User-37</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F203" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G203" s="4" t="n">
-        <v>38.66</v>
+        <v>23.18</v>
       </c>
       <c r="H203" s="7" t="inlineStr">
         <is>
@@ -8323,29 +8323,29 @@
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>User-70</t>
+          <t>User-21</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E204" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F204" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G204" s="4" t="n">
-        <v>37.84</v>
+        <v>20.29</v>
       </c>
       <c r="H204" s="7" t="inlineStr">
         <is>
@@ -8359,12 +8359,12 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>User-67</t>
+          <t>User-61</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
@@ -8381,7 +8381,7 @@
         <v>200</v>
       </c>
       <c r="G205" s="4" t="n">
-        <v>44.21</v>
+        <v>87.38</v>
       </c>
       <c r="H205" s="7" t="inlineStr">
         <is>
@@ -8395,29 +8395,29 @@
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>User-8</t>
+          <t>User-80</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F206" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G206" s="4" t="n">
-        <v>90.95</v>
+        <v>19.88</v>
       </c>
       <c r="H206" s="7" t="inlineStr">
         <is>
@@ -8431,29 +8431,29 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>User-29</t>
+          <t>User-6</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F207" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G207" s="4" t="n">
-        <v>19.33</v>
+        <v>53.72</v>
       </c>
       <c r="H207" s="7" t="inlineStr">
         <is>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>User-70</t>
+          <t>User-8</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
@@ -8489,7 +8489,7 @@
         <v>200</v>
       </c>
       <c r="G208" s="4" t="n">
-        <v>81.28</v>
+        <v>27</v>
       </c>
       <c r="H208" s="7" t="inlineStr">
         <is>
@@ -8503,29 +8503,29 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>User-99</t>
+          <t>User-91</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F209" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G209" s="4" t="n">
-        <v>54.2</v>
+        <v>10.24</v>
       </c>
       <c r="H209" s="7" t="inlineStr">
         <is>
@@ -8539,29 +8539,29 @@
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>User-73</t>
+          <t>User-41</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F210" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G210" s="4" t="n">
-        <v>19.07</v>
+        <v>80.72</v>
       </c>
       <c r="H210" s="7" t="inlineStr">
         <is>
@@ -8575,12 +8575,12 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>User-3</t>
+          <t>User-62</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
@@ -8597,7 +8597,7 @@
         <v>200</v>
       </c>
       <c r="G211" s="4" t="n">
-        <v>34.33</v>
+        <v>59</v>
       </c>
       <c r="H211" s="7" t="inlineStr">
         <is>
@@ -8611,12 +8611,12 @@
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>User-19</t>
+          <t>User-72</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
@@ -8633,7 +8633,7 @@
         <v>200</v>
       </c>
       <c r="G212" s="4" t="n">
-        <v>19.2</v>
+        <v>63.58</v>
       </c>
       <c r="H212" s="7" t="inlineStr">
         <is>
@@ -8647,29 +8647,29 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>User-93</t>
+          <t>User-16</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E213" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F213" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G213" s="4" t="n">
-        <v>55.32</v>
+        <v>45.65</v>
       </c>
       <c r="H213" s="7" t="inlineStr">
         <is>
@@ -8683,29 +8683,29 @@
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>User-3</t>
+          <t>User-66</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E214" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F214" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G214" s="4" t="n">
-        <v>53.01</v>
+        <v>21.27</v>
       </c>
       <c r="H214" s="7" t="inlineStr">
         <is>
@@ -8719,29 +8719,29 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>User-87</t>
+          <t>User-85</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F215" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G215" s="4" t="n">
-        <v>75.61</v>
+        <v>51.56</v>
       </c>
       <c r="H215" s="7" t="inlineStr">
         <is>
@@ -8755,29 +8755,29 @@
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>User-72</t>
+          <t>User-21</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E216" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F216" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G216" s="4" t="n">
-        <v>70.67</v>
+        <v>79.52</v>
       </c>
       <c r="H216" s="7" t="inlineStr">
         <is>
@@ -8791,29 +8791,29 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>User-35</t>
+          <t>User-60</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E217" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F217" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G217" s="4" t="n">
-        <v>88.64</v>
+        <v>26.27</v>
       </c>
       <c r="H217" s="7" t="inlineStr">
         <is>
@@ -8827,29 +8827,29 @@
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>User-24</t>
+          <t>User-63</t>
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E218" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F218" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G218" s="4" t="n">
-        <v>7.2</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="H218" s="7" t="inlineStr">
         <is>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>User-77</t>
+          <t>User-23</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
@@ -8885,7 +8885,7 @@
         <v>200</v>
       </c>
       <c r="G219" s="4" t="n">
-        <v>8.140000000000001</v>
+        <v>23.08</v>
       </c>
       <c r="H219" s="7" t="inlineStr">
         <is>
@@ -8899,29 +8899,29 @@
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>User-24</t>
+          <t>User-13</t>
         </is>
       </c>
       <c r="D220" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E220" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F220" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G220" s="4" t="n">
-        <v>23.66</v>
+        <v>31.1</v>
       </c>
       <c r="H220" s="7" t="inlineStr">
         <is>
@@ -8935,29 +8935,29 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>User-29</t>
+          <t>User-45</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E221" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F221" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G221" s="4" t="n">
-        <v>9.82</v>
+        <v>21.25</v>
       </c>
       <c r="H221" s="7" t="inlineStr">
         <is>
@@ -8971,29 +8971,29 @@
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C222" s="4" t="inlineStr">
         <is>
-          <t>User-6</t>
+          <t>User-25</t>
         </is>
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E222" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F222" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G222" s="4" t="n">
-        <v>66.53</v>
+        <v>11.34</v>
       </c>
       <c r="H222" s="7" t="inlineStr">
         <is>
@@ -9007,29 +9007,29 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>User-78</t>
+          <t>User-60</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E223" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F223" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G223" s="4" t="n">
-        <v>61.57</v>
+        <v>60.59</v>
       </c>
       <c r="H223" s="7" t="inlineStr">
         <is>
@@ -9043,29 +9043,29 @@
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.108</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>User-41</t>
+          <t>User-28</t>
         </is>
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E224" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F224" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G224" s="4" t="n">
-        <v>20.83</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="H224" s="7" t="inlineStr">
         <is>
@@ -9079,29 +9079,29 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>User-61</t>
+          <t>User-22</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E225" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F225" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G225" s="4" t="n">
-        <v>80.83</v>
+        <v>11.43</v>
       </c>
       <c r="H225" s="7" t="inlineStr">
         <is>
@@ -9115,29 +9115,29 @@
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>User-21</t>
+          <t>User-4</t>
         </is>
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E226" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F226" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G226" s="4" t="n">
-        <v>42.85</v>
+        <v>31.01</v>
       </c>
       <c r="H226" s="7" t="inlineStr">
         <is>
@@ -9151,29 +9151,29 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>User-41</t>
+          <t>User-71</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E227" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F227" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G227" s="4" t="n">
-        <v>45</v>
+        <v>46.73</v>
       </c>
       <c r="H227" s="7" t="inlineStr">
         <is>
@@ -9187,12 +9187,12 @@
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>User-3</t>
+          <t>User-30</t>
         </is>
       </c>
       <c r="D228" s="4" t="inlineStr">
@@ -9209,7 +9209,7 @@
         <v>200</v>
       </c>
       <c r="G228" s="4" t="n">
-        <v>69.28</v>
+        <v>22.93</v>
       </c>
       <c r="H228" s="7" t="inlineStr">
         <is>
@@ -9223,29 +9223,29 @@
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>User-16</t>
+          <t>User-38</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E229" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F229" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G229" s="4" t="n">
-        <v>23.97</v>
+        <v>82.05</v>
       </c>
       <c r="H229" s="7" t="inlineStr">
         <is>
@@ -9259,29 +9259,29 @@
       </c>
       <c r="B230" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C230" s="4" t="inlineStr">
         <is>
-          <t>User-35</t>
+          <t>User-44</t>
         </is>
       </c>
       <c r="D230" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E230" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F230" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G230" s="4" t="n">
-        <v>63.91</v>
+        <v>74.17</v>
       </c>
       <c r="H230" s="7" t="inlineStr">
         <is>
@@ -9295,12 +9295,12 @@
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>User-97</t>
+          <t>User-69</t>
         </is>
       </c>
       <c r="D231" s="4" t="inlineStr">
@@ -9317,7 +9317,7 @@
         <v>200</v>
       </c>
       <c r="G231" s="4" t="n">
-        <v>31.67</v>
+        <v>78.84</v>
       </c>
       <c r="H231" s="7" t="inlineStr">
         <is>
@@ -9331,29 +9331,29 @@
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>User-63</t>
+          <t>User-25</t>
         </is>
       </c>
       <c r="D232" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E232" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F232" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G232" s="4" t="n">
-        <v>20.22</v>
+        <v>5.62</v>
       </c>
       <c r="H232" s="7" t="inlineStr">
         <is>
@@ -9367,12 +9367,12 @@
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>User-67</t>
+          <t>User-92</t>
         </is>
       </c>
       <c r="D233" s="4" t="inlineStr">
@@ -9389,7 +9389,7 @@
         <v>200</v>
       </c>
       <c r="G233" s="4" t="n">
-        <v>17.26</v>
+        <v>83.03</v>
       </c>
       <c r="H233" s="7" t="inlineStr">
         <is>
@@ -9403,29 +9403,29 @@
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>User-36</t>
+          <t>User-15</t>
         </is>
       </c>
       <c r="D234" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E234" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F234" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G234" s="4" t="n">
-        <v>28.75</v>
+        <v>46.51</v>
       </c>
       <c r="H234" s="7" t="inlineStr">
         <is>
@@ -9439,29 +9439,29 @@
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>User-25</t>
+          <t>User-33</t>
         </is>
       </c>
       <c r="D235" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E235" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F235" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G235" s="4" t="n">
-        <v>86.03</v>
+        <v>81.23</v>
       </c>
       <c r="H235" s="7" t="inlineStr">
         <is>
@@ -9475,29 +9475,29 @@
       </c>
       <c r="B236" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>User-32</t>
+          <t>User-71</t>
         </is>
       </c>
       <c r="D236" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E236" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F236" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G236" s="4" t="n">
-        <v>59.05</v>
+        <v>34.55</v>
       </c>
       <c r="H236" s="7" t="inlineStr">
         <is>
@@ -9511,12 +9511,12 @@
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>User-40</t>
+          <t>User-97</t>
         </is>
       </c>
       <c r="D237" s="4" t="inlineStr">
@@ -9533,7 +9533,7 @@
         <v>200</v>
       </c>
       <c r="G237" s="4" t="n">
-        <v>70.59999999999999</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="H237" s="7" t="inlineStr">
         <is>
@@ -9547,12 +9547,12 @@
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>User-61</t>
+          <t>User-55</t>
         </is>
       </c>
       <c r="D238" s="4" t="inlineStr">
@@ -9569,7 +9569,7 @@
         <v>200</v>
       </c>
       <c r="G238" s="4" t="n">
-        <v>80.18000000000001</v>
+        <v>40.9</v>
       </c>
       <c r="H238" s="7" t="inlineStr">
         <is>
@@ -9583,29 +9583,29 @@
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>User-61</t>
+          <t>User-53</t>
         </is>
       </c>
       <c r="D239" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E239" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F239" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G239" s="4" t="n">
-        <v>31.12</v>
+        <v>8.5</v>
       </c>
       <c r="H239" s="7" t="inlineStr">
         <is>
@@ -9619,29 +9619,29 @@
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>User-2</t>
+          <t>User-59</t>
         </is>
       </c>
       <c r="D240" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E240" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F240" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G240" s="4" t="n">
-        <v>91.63</v>
+        <v>56.76</v>
       </c>
       <c r="H240" s="7" t="inlineStr">
         <is>
@@ -9655,29 +9655,29 @@
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>User-73</t>
+          <t>User-52</t>
         </is>
       </c>
       <c r="D241" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E241" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F241" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G241" s="4" t="n">
-        <v>33.8</v>
+        <v>84.48</v>
       </c>
       <c r="H241" s="7" t="inlineStr">
         <is>
@@ -9691,29 +9691,29 @@
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>User-82</t>
+          <t>User-54</t>
         </is>
       </c>
       <c r="D242" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E242" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F242" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G242" s="4" t="n">
-        <v>67.59999999999999</v>
+        <v>11.61</v>
       </c>
       <c r="H242" s="7" t="inlineStr">
         <is>
@@ -9727,29 +9727,29 @@
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>User-40</t>
+          <t>User-89</t>
         </is>
       </c>
       <c r="D243" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E243" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F243" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G243" s="4" t="n">
-        <v>83.47</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="H243" s="7" t="inlineStr">
         <is>
@@ -9763,29 +9763,29 @@
       </c>
       <c r="B244" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>User-34</t>
+          <t>User-90</t>
         </is>
       </c>
       <c r="D244" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E244" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F244" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G244" s="4" t="n">
-        <v>79.14</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="H244" s="7" t="inlineStr">
         <is>
@@ -9799,29 +9799,29 @@
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>User-28</t>
+          <t>User-36</t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E245" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F245" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G245" s="4" t="n">
-        <v>74.69</v>
+        <v>17.71</v>
       </c>
       <c r="H245" s="7" t="inlineStr">
         <is>
@@ -9835,12 +9835,12 @@
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>User-45</t>
+          <t>User-92</t>
         </is>
       </c>
       <c r="D246" s="4" t="inlineStr">
@@ -9857,7 +9857,7 @@
         <v>200</v>
       </c>
       <c r="G246" s="4" t="n">
-        <v>80.22</v>
+        <v>54.4</v>
       </c>
       <c r="H246" s="7" t="inlineStr">
         <is>
@@ -9871,29 +9871,29 @@
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>User-6</t>
+          <t>User-87</t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E247" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F247" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G247" s="4" t="n">
-        <v>59.3</v>
+        <v>41.49</v>
       </c>
       <c r="H247" s="7" t="inlineStr">
         <is>
@@ -9907,29 +9907,29 @@
       </c>
       <c r="B248" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>User-64</t>
+          <t>User-54</t>
         </is>
       </c>
       <c r="D248" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E248" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F248" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G248" s="4" t="n">
-        <v>31.65</v>
+        <v>20.49</v>
       </c>
       <c r="H248" s="7" t="inlineStr">
         <is>
@@ -9943,29 +9943,29 @@
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>User-73</t>
+          <t>User-93</t>
         </is>
       </c>
       <c r="D249" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E249" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F249" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G249" s="4" t="n">
-        <v>38.15</v>
+        <v>30.78</v>
       </c>
       <c r="H249" s="7" t="inlineStr">
         <is>
@@ -9979,12 +9979,12 @@
       </c>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>User-57</t>
+          <t>User-22</t>
         </is>
       </c>
       <c r="D250" s="4" t="inlineStr">
@@ -10001,7 +10001,7 @@
         <v>200</v>
       </c>
       <c r="G250" s="4" t="n">
-        <v>54.18</v>
+        <v>60.67</v>
       </c>
       <c r="H250" s="7" t="inlineStr">
         <is>
@@ -10015,29 +10015,29 @@
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>User-29</t>
+          <t>User-89</t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E251" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F251" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G251" s="4" t="n">
-        <v>19.48</v>
+        <v>84.94</v>
       </c>
       <c r="H251" s="7" t="inlineStr">
         <is>
@@ -10051,12 +10051,12 @@
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>User-69</t>
+          <t>User-31</t>
         </is>
       </c>
       <c r="D252" s="4" t="inlineStr">
@@ -10073,7 +10073,7 @@
         <v>200</v>
       </c>
       <c r="G252" s="4" t="n">
-        <v>43.81</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H252" s="7" t="inlineStr">
         <is>
@@ -10087,12 +10087,12 @@
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>User-89</t>
+          <t>User-63</t>
         </is>
       </c>
       <c r="D253" s="4" t="inlineStr">
@@ -10109,7 +10109,7 @@
         <v>200</v>
       </c>
       <c r="G253" s="4" t="n">
-        <v>7.82</v>
+        <v>43.44</v>
       </c>
       <c r="H253" s="7" t="inlineStr">
         <is>
@@ -10123,29 +10123,29 @@
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>User-53</t>
+          <t>User-43</t>
         </is>
       </c>
       <c r="D254" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E254" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F254" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G254" s="4" t="n">
-        <v>79.7</v>
+        <v>6.07</v>
       </c>
       <c r="H254" s="7" t="inlineStr">
         <is>
@@ -10159,29 +10159,29 @@
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>User-94</t>
+          <t>User-53</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E255" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F255" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G255" s="4" t="n">
-        <v>64.06</v>
+        <v>81.45</v>
       </c>
       <c r="H255" s="7" t="inlineStr">
         <is>
@@ -10195,12 +10195,12 @@
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>User-53</t>
+          <t>User-44</t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr">
@@ -10217,7 +10217,7 @@
         <v>200</v>
       </c>
       <c r="G256" s="4" t="n">
-        <v>83.61</v>
+        <v>50.11</v>
       </c>
       <c r="H256" s="7" t="inlineStr">
         <is>
@@ -10231,29 +10231,29 @@
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>User-91</t>
+          <t>User-63</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E257" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F257" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G257" s="4" t="n">
-        <v>67.73999999999999</v>
+        <v>47.5</v>
       </c>
       <c r="H257" s="7" t="inlineStr">
         <is>
@@ -10267,29 +10267,29 @@
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>User-53</t>
+          <t>User-91</t>
         </is>
       </c>
       <c r="D258" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E258" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F258" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G258" s="4" t="n">
-        <v>25.57</v>
+        <v>75.33</v>
       </c>
       <c r="H258" s="7" t="inlineStr">
         <is>
@@ -10303,29 +10303,29 @@
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>User-8</t>
+          <t>User-89</t>
         </is>
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E259" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F259" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G259" s="4" t="n">
-        <v>32.72</v>
+        <v>20.15</v>
       </c>
       <c r="H259" s="7" t="inlineStr">
         <is>
@@ -10339,29 +10339,29 @@
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>User-12</t>
+          <t>User-13</t>
         </is>
       </c>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E260" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F260" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G260" s="4" t="n">
-        <v>39.37</v>
+        <v>90.03</v>
       </c>
       <c r="H260" s="7" t="inlineStr">
         <is>
@@ -10375,29 +10375,29 @@
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>User-2</t>
+          <t>User-26</t>
         </is>
       </c>
       <c r="D261" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E261" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F261" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G261" s="4" t="n">
-        <v>66.75</v>
+        <v>27.91</v>
       </c>
       <c r="H261" s="7" t="inlineStr">
         <is>
@@ -10411,29 +10411,29 @@
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>User-15</t>
+          <t>User-70</t>
         </is>
       </c>
       <c r="D262" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E262" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F262" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G262" s="4" t="n">
-        <v>41.77</v>
+        <v>60.15</v>
       </c>
       <c r="H262" s="7" t="inlineStr">
         <is>
@@ -10447,12 +10447,12 @@
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>User-52</t>
+          <t>User-4</t>
         </is>
       </c>
       <c r="D263" s="4" t="inlineStr">
@@ -10469,7 +10469,7 @@
         <v>200</v>
       </c>
       <c r="G263" s="4" t="n">
-        <v>18.17</v>
+        <v>84.67</v>
       </c>
       <c r="H263" s="7" t="inlineStr">
         <is>
@@ -10483,12 +10483,12 @@
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>User-79</t>
+          <t>User-66</t>
         </is>
       </c>
       <c r="D264" s="4" t="inlineStr">
@@ -10505,7 +10505,7 @@
         <v>200</v>
       </c>
       <c r="G264" s="4" t="n">
-        <v>32.95</v>
+        <v>91.44</v>
       </c>
       <c r="H264" s="7" t="inlineStr">
         <is>
@@ -10519,29 +10519,29 @@
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>User-69</t>
+          <t>User-28</t>
         </is>
       </c>
       <c r="D265" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E265" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F265" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G265" s="4" t="n">
-        <v>73.23</v>
+        <v>51.4</v>
       </c>
       <c r="H265" s="7" t="inlineStr">
         <is>
@@ -10555,29 +10555,29 @@
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>User-45</t>
+          <t>User-32</t>
         </is>
       </c>
       <c r="D266" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E266" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F266" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G266" s="4" t="n">
-        <v>32.28</v>
+        <v>78.41</v>
       </c>
       <c r="H266" s="7" t="inlineStr">
         <is>
@@ -10591,29 +10591,29 @@
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>User-3</t>
+          <t>User-38</t>
         </is>
       </c>
       <c r="D267" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E267" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F267" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G267" s="4" t="n">
-        <v>41.36</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="H267" s="7" t="inlineStr">
         <is>
@@ -10627,12 +10627,12 @@
       </c>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>User-59</t>
+          <t>User-80</t>
         </is>
       </c>
       <c r="D268" s="4" t="inlineStr">
@@ -10649,7 +10649,7 @@
         <v>200</v>
       </c>
       <c r="G268" s="4" t="n">
-        <v>43.42</v>
+        <v>83.47</v>
       </c>
       <c r="H268" s="7" t="inlineStr">
         <is>
@@ -10663,29 +10663,29 @@
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>User-2</t>
+          <t>User-72</t>
         </is>
       </c>
       <c r="D269" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E269" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F269" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G269" s="4" t="n">
-        <v>47.28</v>
+        <v>15.19</v>
       </c>
       <c r="H269" s="7" t="inlineStr">
         <is>
@@ -10699,29 +10699,29 @@
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>User-55</t>
+          <t>User-75</t>
         </is>
       </c>
       <c r="D270" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E270" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F270" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G270" s="4" t="n">
-        <v>10.09</v>
+        <v>52.75</v>
       </c>
       <c r="H270" s="7" t="inlineStr">
         <is>
@@ -10735,12 +10735,12 @@
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>User-46</t>
+          <t>User-64</t>
         </is>
       </c>
       <c r="D271" s="4" t="inlineStr">
@@ -10757,7 +10757,7 @@
         <v>200</v>
       </c>
       <c r="G271" s="4" t="n">
-        <v>74.19</v>
+        <v>31.25</v>
       </c>
       <c r="H271" s="7" t="inlineStr">
         <is>
@@ -10771,12 +10771,12 @@
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>User-64</t>
+          <t>User-98</t>
         </is>
       </c>
       <c r="D272" s="4" t="inlineStr">
@@ -10793,7 +10793,7 @@
         <v>200</v>
       </c>
       <c r="G272" s="4" t="n">
-        <v>34.81</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="H272" s="7" t="inlineStr">
         <is>
@@ -10807,29 +10807,29 @@
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>User-54</t>
+          <t>User-13</t>
         </is>
       </c>
       <c r="D273" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E273" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F273" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G273" s="4" t="n">
-        <v>31.06</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="H273" s="7" t="inlineStr">
         <is>
@@ -10843,29 +10843,29 @@
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>User-83</t>
+          <t>User-69</t>
         </is>
       </c>
       <c r="D274" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E274" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F274" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G274" s="4" t="n">
-        <v>70.70999999999999</v>
+        <v>62.58</v>
       </c>
       <c r="H274" s="7" t="inlineStr">
         <is>
@@ -10879,29 +10879,29 @@
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>User-43</t>
+          <t>User-65</t>
         </is>
       </c>
       <c r="D275" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E275" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F275" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G275" s="4" t="n">
-        <v>52.6</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="H275" s="7" t="inlineStr">
         <is>
@@ -10915,29 +10915,29 @@
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>User-47</t>
+          <t>User-78</t>
         </is>
       </c>
       <c r="D276" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E276" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F276" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G276" s="4" t="n">
-        <v>47.02</v>
+        <v>67.64</v>
       </c>
       <c r="H276" s="7" t="inlineStr">
         <is>
@@ -10951,29 +10951,29 @@
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>User-74</t>
+          <t>User-33</t>
         </is>
       </c>
       <c r="D277" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E277" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F277" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G277" s="4" t="n">
-        <v>58.3</v>
+        <v>36.19</v>
       </c>
       <c r="H277" s="7" t="inlineStr">
         <is>
@@ -10987,29 +10987,29 @@
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>User-13</t>
+          <t>User-16</t>
         </is>
       </c>
       <c r="D278" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E278" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F278" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G278" s="4" t="n">
-        <v>44.73</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="H278" s="7" t="inlineStr">
         <is>
@@ -11023,12 +11023,12 @@
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.031</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>User-97</t>
+          <t>User-77</t>
         </is>
       </c>
       <c r="D279" s="4" t="inlineStr">
@@ -11045,7 +11045,7 @@
         <v>200</v>
       </c>
       <c r="G279" s="4" t="n">
-        <v>58.42</v>
+        <v>26.48</v>
       </c>
       <c r="H279" s="7" t="inlineStr">
         <is>
@@ -11059,12 +11059,12 @@
       </c>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.032</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C280" s="4" t="inlineStr">
         <is>
-          <t>User-21</t>
+          <t>User-1</t>
         </is>
       </c>
       <c r="D280" s="4" t="inlineStr">
@@ -11081,7 +11081,7 @@
         <v>200</v>
       </c>
       <c r="G280" s="4" t="n">
-        <v>86.15000000000001</v>
+        <v>49.16</v>
       </c>
       <c r="H280" s="7" t="inlineStr">
         <is>
@@ -11095,29 +11095,29 @@
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.032</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>User-78</t>
+          <t>User-6</t>
         </is>
       </c>
       <c r="D281" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E281" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F281" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G281" s="4" t="n">
-        <v>85.48</v>
+        <v>53.08</v>
       </c>
       <c r="H281" s="7" t="inlineStr">
         <is>
@@ -11131,12 +11131,12 @@
       </c>
       <c r="B282" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.032</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C282" s="4" t="inlineStr">
         <is>
-          <t>User-99</t>
+          <t>User-39</t>
         </is>
       </c>
       <c r="D282" s="4" t="inlineStr">
@@ -11153,7 +11153,7 @@
         <v>200</v>
       </c>
       <c r="G282" s="4" t="n">
-        <v>14.05</v>
+        <v>63.6</v>
       </c>
       <c r="H282" s="7" t="inlineStr">
         <is>
@@ -11167,29 +11167,29 @@
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.032</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>User-87</t>
+          <t>User-33</t>
         </is>
       </c>
       <c r="D283" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E283" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F283" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G283" s="4" t="n">
-        <v>76.98</v>
+        <v>50.72</v>
       </c>
       <c r="H283" s="7" t="inlineStr">
         <is>
@@ -11203,29 +11203,29 @@
       </c>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.032</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>User-21</t>
+          <t>User-15</t>
         </is>
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E284" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F284" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G284" s="4" t="n">
-        <v>75.75</v>
+        <v>76.87</v>
       </c>
       <c r="H284" s="7" t="inlineStr">
         <is>
@@ -11239,29 +11239,29 @@
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.032</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>User-88</t>
+          <t>User-6</t>
         </is>
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E285" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F285" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G285" s="4" t="n">
-        <v>29.34</v>
+        <v>94.61</v>
       </c>
       <c r="H285" s="7" t="inlineStr">
         <is>
@@ -11275,29 +11275,29 @@
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.032</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>User-72</t>
+          <t>User-53</t>
         </is>
       </c>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E286" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F286" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G286" s="4" t="n">
-        <v>26.5</v>
+        <v>56.82</v>
       </c>
       <c r="H286" s="7" t="inlineStr">
         <is>
@@ -11311,29 +11311,29 @@
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.032</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>User-99</t>
+          <t>User-62</t>
         </is>
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E287" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F287" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G287" s="4" t="n">
-        <v>75.31999999999999</v>
+        <v>16.07</v>
       </c>
       <c r="H287" s="7" t="inlineStr">
         <is>
@@ -11347,29 +11347,29 @@
       </c>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.032</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>User-7</t>
+          <t>User-99</t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E288" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F288" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G288" s="4" t="n">
-        <v>9.640000000000001</v>
+        <v>70.83</v>
       </c>
       <c r="H288" s="7" t="inlineStr">
         <is>
@@ -11383,12 +11383,12 @@
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.032</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>User-54</t>
+          <t>User-86</t>
         </is>
       </c>
       <c r="D289" s="4" t="inlineStr">
@@ -11405,7 +11405,7 @@
         <v>200</v>
       </c>
       <c r="G289" s="4" t="n">
-        <v>18.54</v>
+        <v>79.33</v>
       </c>
       <c r="H289" s="7" t="inlineStr">
         <is>
@@ -11419,29 +11419,29 @@
       </c>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.032</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr">
         <is>
-          <t>User-1</t>
+          <t>User-5</t>
         </is>
       </c>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E290" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F290" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G290" s="4" t="n">
-        <v>13.53</v>
+        <v>53.74</v>
       </c>
       <c r="H290" s="7" t="inlineStr">
         <is>
@@ -11455,12 +11455,12 @@
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.032</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>User-45</t>
+          <t>User-11</t>
         </is>
       </c>
       <c r="D291" s="4" t="inlineStr">
@@ -11477,7 +11477,7 @@
         <v>200</v>
       </c>
       <c r="G291" s="4" t="n">
-        <v>77.12</v>
+        <v>69.58</v>
       </c>
       <c r="H291" s="7" t="inlineStr">
         <is>
@@ -11491,29 +11491,29 @@
       </c>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.032</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>User-87</t>
+          <t>User-71</t>
         </is>
       </c>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E292" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F292" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G292" s="4" t="n">
-        <v>80.83</v>
+        <v>30.78</v>
       </c>
       <c r="H292" s="7" t="inlineStr">
         <is>
@@ -11527,12 +11527,12 @@
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.032</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>User-79</t>
+          <t>User-72</t>
         </is>
       </c>
       <c r="D293" s="4" t="inlineStr">
@@ -11549,7 +11549,7 @@
         <v>200</v>
       </c>
       <c r="G293" s="4" t="n">
-        <v>15.16</v>
+        <v>64.39</v>
       </c>
       <c r="H293" s="7" t="inlineStr">
         <is>
@@ -11563,29 +11563,29 @@
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.032</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>User-84</t>
+          <t>User-62</t>
         </is>
       </c>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E294" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F294" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G294" s="4" t="n">
-        <v>22.53</v>
+        <v>68.94</v>
       </c>
       <c r="H294" s="7" t="inlineStr">
         <is>
@@ -11599,12 +11599,12 @@
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.032</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>User-27</t>
+          <t>User-88</t>
         </is>
       </c>
       <c r="D295" s="4" t="inlineStr">
@@ -11621,7 +11621,7 @@
         <v>200</v>
       </c>
       <c r="G295" s="4" t="n">
-        <v>8.359999999999999</v>
+        <v>5.45</v>
       </c>
       <c r="H295" s="7" t="inlineStr">
         <is>
@@ -11635,29 +11635,29 @@
       </c>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.032</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C296" s="4" t="inlineStr">
         <is>
-          <t>User-70</t>
+          <t>User-44</t>
         </is>
       </c>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E296" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F296" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G296" s="4" t="n">
-        <v>5.53</v>
+        <v>61.51</v>
       </c>
       <c r="H296" s="7" t="inlineStr">
         <is>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.032</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>User-56</t>
+          <t>User-68</t>
         </is>
       </c>
       <c r="D297" s="4" t="inlineStr">
@@ -11693,7 +11693,7 @@
         <v>200</v>
       </c>
       <c r="G297" s="4" t="n">
-        <v>22.12</v>
+        <v>72.88</v>
       </c>
       <c r="H297" s="7" t="inlineStr">
         <is>
@@ -11707,29 +11707,29 @@
       </c>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.032</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>User-46</t>
+          <t>User-77</t>
         </is>
       </c>
       <c r="D298" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E298" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F298" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G298" s="4" t="n">
-        <v>48.93</v>
+        <v>83.09</v>
       </c>
       <c r="H298" s="7" t="inlineStr">
         <is>
@@ -11743,29 +11743,29 @@
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.032</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>User-7</t>
+          <t>User-58</t>
         </is>
       </c>
       <c r="D299" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E299" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F299" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G299" s="4" t="n">
-        <v>64.39</v>
+        <v>19.93</v>
       </c>
       <c r="H299" s="7" t="inlineStr">
         <is>
@@ -11779,29 +11779,29 @@
       </c>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.032</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C300" s="4" t="inlineStr">
         <is>
-          <t>User-73</t>
+          <t>User-97</t>
         </is>
       </c>
       <c r="D300" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E300" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F300" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G300" s="4" t="n">
-        <v>63.11</v>
+        <v>87.88</v>
       </c>
       <c r="H300" s="7" t="inlineStr">
         <is>
@@ -11815,29 +11815,29 @@
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:41.032</t>
+          <t>2026-06-22 06:18:52.109</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>User-51</t>
+          <t>User-86</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E301" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F301" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G301" s="4" t="n">
-        <v>72.64</v>
+        <v>84.91</v>
       </c>
       <c r="H301" s="7" t="inlineStr">
         <is>

--- a/security-testing/scripts/Sentinel_Load_Test_Report.xlsx
+++ b/security-testing/scripts/Sentinel_Load_Test_Report.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33</t>
+          <t>2026-06-23 07:09:58</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>5.0 ms</t>
+          <t>5.1 ms</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>49.5 ms</t>
+          <t>49.8 ms</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>94.9 ms</t>
+          <t>93.7 ms</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>88.5 ms</t>
+          <t>88.4 ms</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -797,12 +797,12 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -811,19 +811,19 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>1.52</v>
+        <v>0.5</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>5</v>
+        <v>17.5</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>46.4</v>
+        <v>51.1</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>93.8</v>
+        <v>90.8</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -834,12 +834,12 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -848,19 +848,19 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.52</v>
+        <v>1.42</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>10.8</v>
+        <v>5.1</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>52.9</v>
+        <v>50.6</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>91.59999999999999</v>
+        <v>93.3</v>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
@@ -871,12 +871,12 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -885,19 +885,19 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.87</v>
+        <v>1.02</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>48.5</v>
+        <v>50.3</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>94.40000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
@@ -908,12 +908,12 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -922,19 +922,19 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>50.1</v>
+        <v>47.8</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>94.90000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
@@ -945,12 +945,12 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -959,19 +959,19 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>52.3</v>
+        <v>49.5</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>93.3</v>
+        <v>91.2</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
@@ -1051,29 +1051,29 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.280</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>User-43</t>
+          <t>User-94</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F2" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>51.77</v>
+        <v>56.85</v>
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
@@ -1087,29 +1087,29 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.280</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>User-35</t>
+          <t>User-53</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>76.43000000000001</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.280</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>User-50</t>
+          <t>User-91</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -1145,7 +1145,7 @@
         <v>200</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>5.23</v>
+        <v>80.08</v>
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
@@ -1159,29 +1159,29 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.280</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>User-66</t>
+          <t>User-64</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>71.13</v>
+        <v>80.08</v>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
@@ -1195,29 +1195,29 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.280</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>User-33</t>
+          <t>User-77</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>41.46</v>
+        <v>62.8</v>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
@@ -1231,29 +1231,29 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.280</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>User-20</t>
+          <t>User-71</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>88.43000000000001</v>
+        <v>68.11</v>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
@@ -1267,29 +1267,29 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.280</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>User-11</t>
+          <t>User-76</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>54.44</v>
+        <v>22.5</v>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
@@ -1303,29 +1303,29 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.280</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>User-84</t>
+          <t>User-32</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>55.64</v>
+        <v>11.94</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.280</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>User-40</t>
+          <t>User-85</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1361,7 +1361,7 @@
         <v>200</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>57.26</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.280</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1397,7 +1397,7 @@
         <v>200</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>44.46</v>
+        <v>14.73</v>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
@@ -1411,29 +1411,29 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.280</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>User-41</t>
+          <t>User-44</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>92.06</v>
+        <v>12.77</v>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
@@ -1447,29 +1447,29 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.280</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>User-33</t>
+          <t>User-43</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>52.92</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -1483,29 +1483,29 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.280</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>User-94</t>
+          <t>User-53</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>47.53</v>
+        <v>48.54</v>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
@@ -1519,29 +1519,29 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.280</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>User-77</t>
+          <t>User-78</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>63.96</v>
+        <v>29.08</v>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.280</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>User-3</t>
+          <t>User-59</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1577,7 +1577,7 @@
         <v>200</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>79.34999999999999</v>
+        <v>18.91</v>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
@@ -1591,12 +1591,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.280</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>User-63</t>
+          <t>User-86</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1613,7 +1613,7 @@
         <v>200</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>52.6</v>
+        <v>80.02</v>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.280</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>User-11</t>
+          <t>User-10</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1649,7 +1649,7 @@
         <v>200</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>50.86</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.280</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>User-54</t>
+          <t>User-52</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1685,7 +1685,7 @@
         <v>200</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>73.75</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
@@ -1699,29 +1699,29 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>User-92</t>
+          <t>User-82</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>73.31999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
@@ -1735,12 +1735,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>User-30</t>
+          <t>User-39</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1757,7 +1757,7 @@
         <v>200</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>31.79</v>
+        <v>7.27</v>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
@@ -1771,12 +1771,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>User-24</t>
+          <t>User-9</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1793,7 +1793,7 @@
         <v>200</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>85.02</v>
+        <v>32.31</v>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>User-41</t>
+          <t>User-40</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1829,7 +1829,7 @@
         <v>200</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>48.92</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
@@ -1843,29 +1843,29 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>User-4</t>
+          <t>User-1</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>88.45</v>
+        <v>70.73</v>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
@@ -1879,29 +1879,29 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>User-91</t>
+          <t>User-99</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>72.01000000000001</v>
+        <v>25.09</v>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
@@ -1915,29 +1915,29 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>User-82</t>
+          <t>User-51</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>25.16</v>
+        <v>7.52</v>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
@@ -1951,29 +1951,29 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>User-38</t>
+          <t>User-85</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>10.33</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1997,19 +1997,19 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>26.83</v>
+        <v>33.92</v>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
@@ -2023,29 +2023,29 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>User-82</t>
+          <t>User-48</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>27.38</v>
+        <v>56.5</v>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
@@ -2059,12 +2059,12 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>User-52</t>
+          <t>User-53</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -2081,7 +2081,7 @@
         <v>200</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>40.04</v>
+        <v>44.36</v>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>User-6</t>
+          <t>User-58</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -2117,7 +2117,7 @@
         <v>200</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>27.16</v>
+        <v>37.28</v>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
@@ -2131,29 +2131,29 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>User-3</t>
+          <t>User-96</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>21.7</v>
+        <v>44.42</v>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
@@ -2167,29 +2167,29 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>User-100</t>
+          <t>User-71</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F33" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>47.25</v>
+        <v>9.67</v>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
@@ -2203,29 +2203,29 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>User-15</t>
+          <t>User-49</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F34" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>41.77</v>
+        <v>61.56</v>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
@@ -2239,29 +2239,29 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>User-61</t>
+          <t>User-79</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F35" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>72.26000000000001</v>
+        <v>83.13</v>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
@@ -2275,29 +2275,29 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>User-32</t>
+          <t>User-34</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F36" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>18.95</v>
+        <v>34.56</v>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
@@ -2311,12 +2311,12 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>User-72</t>
+          <t>User-77</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2333,7 +2333,7 @@
         <v>200</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>65.67</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
@@ -2347,29 +2347,29 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>User-91</t>
+          <t>User-84</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F38" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>53.03</v>
+        <v>46.54</v>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
@@ -2383,12 +2383,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>User-43</t>
+          <t>User-94</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2405,7 +2405,7 @@
         <v>200</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>54.78</v>
+        <v>51.1</v>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
@@ -2419,29 +2419,29 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>User-10</t>
+          <t>User-1</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>64.63</v>
+        <v>90.75</v>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
@@ -2455,29 +2455,29 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>User-88</t>
+          <t>User-63</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>6.2</v>
+        <v>66.84</v>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
@@ -2491,29 +2491,29 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>User-72</t>
+          <t>User-31</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>26.63</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
@@ -2527,12 +2527,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>User-40</t>
+          <t>User-35</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2549,7 +2549,7 @@
         <v>200</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>43.73</v>
+        <v>25.76</v>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
@@ -2563,29 +2563,29 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>User-77</t>
+          <t>User-96</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F44" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>56.43</v>
+        <v>7.76</v>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
@@ -2599,29 +2599,29 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>User-48</t>
+          <t>User-53</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>32.96</v>
+        <v>31.61</v>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
@@ -2635,29 +2635,29 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>User-90</t>
+          <t>User-68</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>31.85</v>
+        <v>61.39</v>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
@@ -2671,29 +2671,29 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>User-32</t>
+          <t>User-17</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>19.99</v>
+        <v>24.96</v>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>User-64</t>
+          <t>User-36</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2729,7 +2729,7 @@
         <v>200</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>9.1</v>
+        <v>56.48</v>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
@@ -2743,12 +2743,12 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>User-6</t>
+          <t>User-28</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -2765,7 +2765,7 @@
         <v>200</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>45.65</v>
+        <v>92.66</v>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
@@ -2779,29 +2779,29 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>User-94</t>
+          <t>User-83</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F50" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>94.93000000000001</v>
+        <v>16.8</v>
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
@@ -2815,29 +2815,29 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>User-62</t>
+          <t>User-36</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F51" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>86.13</v>
+        <v>52.51</v>
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
@@ -2851,12 +2851,12 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>User-99</t>
+          <t>User-40</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -2873,7 +2873,7 @@
         <v>200</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>35.5</v>
+        <v>8.43</v>
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
@@ -2887,29 +2887,29 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>User-6</t>
+          <t>User-25</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F53" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>78.09999999999999</v>
+        <v>52.62</v>
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -2933,19 +2933,19 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F54" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>70.09</v>
+        <v>14.71</v>
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
@@ -2959,29 +2959,29 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>User-81</t>
+          <t>User-17</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F55" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>82.91</v>
+        <v>36.03</v>
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
@@ -2995,29 +2995,29 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>User-43</t>
+          <t>User-34</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F56" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>10.36</v>
+        <v>59.12</v>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
@@ -3031,29 +3031,29 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>User-90</t>
+          <t>User-48</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F57" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>64.7</v>
+        <v>16.93</v>
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
@@ -3067,29 +3067,29 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>User-100</t>
+          <t>User-87</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F58" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>38.15</v>
+        <v>26.87</v>
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
@@ -3103,29 +3103,29 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>User-68</t>
+          <t>User-7</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F59" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>92.34</v>
+        <v>53.45</v>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
@@ -3139,29 +3139,29 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>User-38</t>
+          <t>User-67</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F60" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>35.47</v>
+        <v>69.61</v>
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
@@ -3175,29 +3175,29 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>User-72</t>
+          <t>User-86</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F61" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>22.56</v>
+        <v>71.33</v>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>User-57</t>
+          <t>User-77</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -3233,7 +3233,7 @@
         <v>200</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>77.61</v>
+        <v>15.56</v>
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>User-9</t>
+          <t>User-15</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -3269,7 +3269,7 @@
         <v>200</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>84.54000000000001</v>
+        <v>59.38</v>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
@@ -3283,29 +3283,29 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.682</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>User-76</t>
+          <t>User-40</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F64" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>56.37</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
@@ -3319,29 +3319,29 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>User-32</t>
+          <t>User-100</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F65" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>80.01000000000001</v>
+        <v>80.58</v>
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
@@ -3355,29 +3355,29 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>User-32</t>
+          <t>User-39</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F66" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>71.06</v>
+        <v>40.57</v>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
@@ -3391,29 +3391,29 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>User-14</t>
+          <t>User-8</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F67" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>66.7</v>
+        <v>46.42</v>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
@@ -3427,29 +3427,29 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>User-9</t>
+          <t>User-38</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F68" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>15.73</v>
+        <v>59.74</v>
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
@@ -3463,12 +3463,12 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>User-82</t>
+          <t>User-25</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -3485,7 +3485,7 @@
         <v>200</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>25.34</v>
+        <v>6.7</v>
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
@@ -3499,29 +3499,29 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>User-46</t>
+          <t>User-89</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F70" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>42.68</v>
+        <v>80.94</v>
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
@@ -3535,12 +3535,12 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>User-96</t>
+          <t>User-98</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -3557,7 +3557,7 @@
         <v>200</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>11.78</v>
+        <v>11.95</v>
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
@@ -3571,29 +3571,29 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>User-65</t>
+          <t>User-50</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F72" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>84.28</v>
+        <v>49.16</v>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
@@ -3607,29 +3607,29 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>User-75</t>
+          <t>User-2</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F73" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>37.08</v>
+        <v>25.82</v>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
@@ -3643,29 +3643,29 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>User-71</t>
+          <t>User-6</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F74" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>22.45</v>
+        <v>47.99</v>
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
@@ -3679,12 +3679,12 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>User-90</t>
+          <t>User-23</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -3701,7 +3701,7 @@
         <v>200</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>59.94</v>
+        <v>84.33</v>
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
@@ -3715,29 +3715,29 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>User-4</t>
+          <t>User-62</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F76" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>5.01</v>
+        <v>20.81</v>
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
@@ -3751,29 +3751,29 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>User-90</t>
+          <t>User-96</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F77" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>35.76</v>
+        <v>55.42</v>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
@@ -3787,29 +3787,29 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>User-57</t>
+          <t>User-12</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F78" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>16.58</v>
+        <v>23.17</v>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>User-59</t>
+          <t>User-44</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -3845,7 +3845,7 @@
         <v>200</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>38.08</v>
+        <v>41.9</v>
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
@@ -3859,12 +3859,12 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>User-93</t>
+          <t>User-85</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -3881,7 +3881,7 @@
         <v>200</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>88.2</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
@@ -3895,29 +3895,29 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>User-62</t>
+          <t>User-38</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F81" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>54.28</v>
+        <v>22.06</v>
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
@@ -3931,29 +3931,29 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>User-63</t>
+          <t>User-74</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F82" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>47.02</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
@@ -3967,29 +3967,29 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>User-26</t>
+          <t>User-5</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F83" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>37.47</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
@@ -4003,29 +4003,29 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>User-25</t>
+          <t>User-4</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F84" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>26.35</v>
+        <v>81.78</v>
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
@@ -4039,29 +4039,29 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>User-56</t>
+          <t>User-3</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F85" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>26.57</v>
+        <v>69.48</v>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
@@ -4075,29 +4075,29 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>User-99</t>
+          <t>User-72</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F86" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>68.73</v>
+        <v>31.93</v>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
@@ -4111,29 +4111,29 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>User-81</t>
+          <t>User-62</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F87" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>30.87</v>
+        <v>36.47</v>
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>User-9</t>
+          <t>User-32</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -4169,7 +4169,7 @@
         <v>200</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>60.94</v>
+        <v>26.62</v>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
@@ -4183,29 +4183,29 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>User-60</t>
+          <t>User-15</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F89" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>12.65</v>
+        <v>84.91</v>
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
@@ -4219,29 +4219,29 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>User-68</t>
+          <t>User-23</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F90" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>7.63</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
@@ -4255,29 +4255,29 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>User-39</t>
+          <t>User-64</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F91" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>68.06999999999999</v>
+        <v>86.45</v>
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
@@ -4291,29 +4291,29 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>User-15</t>
+          <t>User-70</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F92" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>66.70999999999999</v>
+        <v>11.03</v>
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
@@ -4327,12 +4327,12 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>User-15</t>
+          <t>User-43</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -4349,7 +4349,7 @@
         <v>200</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>91.5</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
@@ -4363,12 +4363,12 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>User-52</t>
+          <t>User-13</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -4385,7 +4385,7 @@
         <v>200</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>81.09</v>
+        <v>23.96</v>
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>User-17</t>
+          <t>User-46</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -4421,7 +4421,7 @@
         <v>200</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>50.09</v>
+        <v>49.27</v>
       </c>
       <c r="H95" s="7" t="inlineStr">
         <is>
@@ -4435,12 +4435,12 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>User-42</t>
+          <t>User-52</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -4457,7 +4457,7 @@
         <v>200</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>38.79</v>
+        <v>39.17</v>
       </c>
       <c r="H96" s="7" t="inlineStr">
         <is>
@@ -4471,29 +4471,29 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>User-38</t>
+          <t>User-15</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F97" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>16.2</v>
+        <v>23.25</v>
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
@@ -4507,12 +4507,12 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>User-50</t>
+          <t>User-20</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -4529,7 +4529,7 @@
         <v>200</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>5.75</v>
+        <v>60.36</v>
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
@@ -4543,12 +4543,12 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>User-70</t>
+          <t>User-98</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -4565,7 +4565,7 @@
         <v>200</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>27.95</v>
+        <v>71.66</v>
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
@@ -4579,12 +4579,12 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>User-48</t>
+          <t>User-19</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -4601,7 +4601,7 @@
         <v>200</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>83.17</v>
+        <v>83.52</v>
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>User-66</t>
+          <t>User-22</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -4637,7 +4637,7 @@
         <v>200</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>7.24</v>
+        <v>25.08</v>
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
@@ -4651,12 +4651,12 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>User-7</t>
+          <t>User-5</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -4673,7 +4673,7 @@
         <v>200</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>23.8</v>
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
@@ -4687,29 +4687,29 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>User-13</t>
+          <t>User-36</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F103" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>52.2</v>
+        <v>43.6</v>
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
@@ -4723,29 +4723,29 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>User-39</t>
+          <t>User-89</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F104" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>42.99</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
@@ -4759,29 +4759,29 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>User-74</t>
+          <t>User-20</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F105" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>14.64</v>
+        <v>30.56</v>
       </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
@@ -4795,12 +4795,12 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>User-65</t>
+          <t>User-51</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -4817,7 +4817,7 @@
         <v>200</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>17.03</v>
+        <v>13.95</v>
       </c>
       <c r="H106" s="7" t="inlineStr">
         <is>
@@ -4831,29 +4831,29 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>User-70</t>
+          <t>User-49</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F107" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>51.76</v>
+        <v>79.02</v>
       </c>
       <c r="H107" s="7" t="inlineStr">
         <is>
@@ -4867,29 +4867,29 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>User-34</t>
+          <t>User-32</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F108" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>10.3</v>
+        <v>12.97</v>
       </c>
       <c r="H108" s="7" t="inlineStr">
         <is>
@@ -4903,29 +4903,29 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>User-28</t>
+          <t>User-86</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F109" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>76.06999999999999</v>
+        <v>23.23</v>
       </c>
       <c r="H109" s="7" t="inlineStr">
         <is>
@@ -4939,29 +4939,29 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>User-73</t>
+          <t>User-71</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F110" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>74.41</v>
+        <v>93.73</v>
       </c>
       <c r="H110" s="7" t="inlineStr">
         <is>
@@ -4975,29 +4975,29 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>User-62</t>
+          <t>User-10</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F111" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>28.71</v>
+        <v>63.97</v>
       </c>
       <c r="H111" s="7" t="inlineStr">
         <is>
@@ -5011,29 +5011,29 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>User-84</t>
+          <t>User-87</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F112" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>7.39</v>
+        <v>26.32</v>
       </c>
       <c r="H112" s="7" t="inlineStr">
         <is>
@@ -5047,29 +5047,29 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>User-38</t>
+          <t>User-43</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F113" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>79.16</v>
+        <v>61.66</v>
       </c>
       <c r="H113" s="7" t="inlineStr">
         <is>
@@ -5083,29 +5083,29 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>User-47</t>
+          <t>User-26</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F114" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>72</v>
+        <v>17.49</v>
       </c>
       <c r="H114" s="7" t="inlineStr">
         <is>
@@ -5119,29 +5119,29 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>User-60</t>
+          <t>User-26</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F115" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>63.13</v>
+        <v>24.72</v>
       </c>
       <c r="H115" s="7" t="inlineStr">
         <is>
@@ -5155,29 +5155,29 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>User-76</t>
+          <t>User-50</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F116" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>40.66</v>
+        <v>25.28</v>
       </c>
       <c r="H116" s="7" t="inlineStr">
         <is>
@@ -5191,29 +5191,29 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>User-43</t>
+          <t>User-7</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F117" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>88.69</v>
+        <v>52.08</v>
       </c>
       <c r="H117" s="7" t="inlineStr">
         <is>
@@ -5227,12 +5227,12 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>User-47</t>
+          <t>User-96</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -5249,7 +5249,7 @@
         <v>200</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>88.40000000000001</v>
+        <v>62.57</v>
       </c>
       <c r="H118" s="7" t="inlineStr">
         <is>
@@ -5263,29 +5263,29 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>User-68</t>
+          <t>User-89</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F119" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G119" s="4" t="n">
-        <v>41.75</v>
+        <v>10.25</v>
       </c>
       <c r="H119" s="7" t="inlineStr">
         <is>
@@ -5299,29 +5299,29 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>User-14</t>
+          <t>User-24</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F120" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>36.34</v>
+        <v>42.84</v>
       </c>
       <c r="H120" s="7" t="inlineStr">
         <is>
@@ -5335,29 +5335,29 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>User-13</t>
+          <t>User-50</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F121" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>74.33</v>
+        <v>30.58</v>
       </c>
       <c r="H121" s="7" t="inlineStr">
         <is>
@@ -5371,29 +5371,29 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>User-91</t>
+          <t>User-85</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F122" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>72.53</v>
+        <v>87.51000000000001</v>
       </c>
       <c r="H122" s="7" t="inlineStr">
         <is>
@@ -5407,29 +5407,29 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>User-1</t>
+          <t>User-38</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F123" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>68.45999999999999</v>
+        <v>41.38</v>
       </c>
       <c r="H123" s="7" t="inlineStr">
         <is>
@@ -5443,29 +5443,29 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>User-66</t>
+          <t>User-49</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F124" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G124" s="4" t="n">
-        <v>82.18000000000001</v>
+        <v>73.08</v>
       </c>
       <c r="H124" s="7" t="inlineStr">
         <is>
@@ -5479,29 +5479,29 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>User-22</t>
+          <t>User-78</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F125" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>36</v>
+        <v>59.08</v>
       </c>
       <c r="H125" s="7" t="inlineStr">
         <is>
@@ -5515,29 +5515,29 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>User-51</t>
+          <t>User-69</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F126" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>93.77</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H126" s="7" t="inlineStr">
         <is>
@@ -5551,29 +5551,29 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>User-55</t>
+          <t>User-61</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F127" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G127" s="4" t="n">
-        <v>12.98</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
@@ -5587,29 +5587,29 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>User-35</t>
+          <t>User-51</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F128" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>73.23</v>
+        <v>88.73</v>
       </c>
       <c r="H128" s="7" t="inlineStr">
         <is>
@@ -5623,29 +5623,29 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>User-1</t>
+          <t>User-80</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F129" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G129" s="4" t="n">
-        <v>10.48</v>
+        <v>91.22</v>
       </c>
       <c r="H129" s="7" t="inlineStr">
         <is>
@@ -5659,29 +5659,29 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>User-39</t>
+          <t>User-14</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F130" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>25.55</v>
+        <v>91.42</v>
       </c>
       <c r="H130" s="7" t="inlineStr">
         <is>
@@ -5695,29 +5695,29 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>User-87</t>
+          <t>User-21</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F131" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G131" s="4" t="n">
-        <v>26.32</v>
+        <v>13.84</v>
       </c>
       <c r="H131" s="7" t="inlineStr">
         <is>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>User-44</t>
+          <t>User-98</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -5753,7 +5753,7 @@
         <v>200</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>78.45999999999999</v>
+        <v>21.86</v>
       </c>
       <c r="H132" s="7" t="inlineStr">
         <is>
@@ -5767,29 +5767,29 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>User-13</t>
+          <t>User-73</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F133" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G133" s="4" t="n">
-        <v>84.62</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="H133" s="7" t="inlineStr">
         <is>
@@ -5803,29 +5803,29 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>User-94</t>
+          <t>User-33</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F134" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>28.13</v>
+        <v>73.86</v>
       </c>
       <c r="H134" s="7" t="inlineStr">
         <is>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>User-93</t>
+          <t>User-8</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
@@ -5861,7 +5861,7 @@
         <v>200</v>
       </c>
       <c r="G135" s="4" t="n">
-        <v>64.97</v>
+        <v>27.67</v>
       </c>
       <c r="H135" s="7" t="inlineStr">
         <is>
@@ -5875,12 +5875,12 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>User-27</t>
+          <t>User-79</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
@@ -5897,7 +5897,7 @@
         <v>200</v>
       </c>
       <c r="G136" s="4" t="n">
-        <v>55.72</v>
+        <v>31.42</v>
       </c>
       <c r="H136" s="7" t="inlineStr">
         <is>
@@ -5911,29 +5911,29 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>User-38</t>
+          <t>User-62</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F137" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G137" s="4" t="n">
-        <v>59.39</v>
+        <v>63.87</v>
       </c>
       <c r="H137" s="7" t="inlineStr">
         <is>
@@ -5947,29 +5947,29 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>User-99</t>
+          <t>User-79</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F138" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>54.49</v>
+        <v>35.12</v>
       </c>
       <c r="H138" s="7" t="inlineStr">
         <is>
@@ -5983,29 +5983,29 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>User-40</t>
+          <t>User-91</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F139" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G139" s="4" t="n">
-        <v>40.89</v>
+        <v>27.67</v>
       </c>
       <c r="H139" s="7" t="inlineStr">
         <is>
@@ -6019,29 +6019,29 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>User-37</t>
+          <t>User-4</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F140" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>58.17</v>
+        <v>83.34</v>
       </c>
       <c r="H140" s="7" t="inlineStr">
         <is>
@@ -6055,29 +6055,29 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>User-49</t>
+          <t>User-63</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F141" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G141" s="4" t="n">
-        <v>82.55</v>
+        <v>60.15</v>
       </c>
       <c r="H141" s="7" t="inlineStr">
         <is>
@@ -6091,29 +6091,29 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>User-82</t>
+          <t>User-61</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F142" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G142" s="4" t="n">
-        <v>35.99</v>
+        <v>48.26</v>
       </c>
       <c r="H142" s="7" t="inlineStr">
         <is>
@@ -6127,29 +6127,29 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>User-18</t>
+          <t>User-13</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F143" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G143" s="4" t="n">
-        <v>51.99</v>
+        <v>41.43</v>
       </c>
       <c r="H143" s="7" t="inlineStr">
         <is>
@@ -6163,29 +6163,29 @@
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>User-27</t>
+          <t>User-83</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F144" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G144" s="4" t="n">
-        <v>28.34</v>
+        <v>35.98</v>
       </c>
       <c r="H144" s="7" t="inlineStr">
         <is>
@@ -6199,29 +6199,29 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>User-14</t>
+          <t>User-87</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F145" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G145" s="4" t="n">
-        <v>89.06999999999999</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H145" s="7" t="inlineStr">
         <is>
@@ -6235,29 +6235,29 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>User-60</t>
+          <t>User-69</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F146" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G146" s="4" t="n">
-        <v>26.38</v>
+        <v>20.02</v>
       </c>
       <c r="H146" s="7" t="inlineStr">
         <is>
@@ -6271,29 +6271,29 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>User-37</t>
+          <t>User-60</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F147" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G147" s="4" t="n">
-        <v>9.02</v>
+        <v>9.07</v>
       </c>
       <c r="H147" s="7" t="inlineStr">
         <is>
@@ -6307,29 +6307,29 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>User-88</t>
+          <t>User-19</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F148" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G148" s="4" t="n">
-        <v>8.390000000000001</v>
+        <v>42.3</v>
       </c>
       <c r="H148" s="7" t="inlineStr">
         <is>
@@ -6343,29 +6343,29 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>User-49</t>
+          <t>User-63</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F149" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G149" s="4" t="n">
-        <v>77.62</v>
+        <v>11.89</v>
       </c>
       <c r="H149" s="7" t="inlineStr">
         <is>
@@ -6379,29 +6379,29 @@
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>User-54</t>
+          <t>User-53</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F150" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G150" s="4" t="n">
-        <v>20.7</v>
+        <v>24.16</v>
       </c>
       <c r="H150" s="7" t="inlineStr">
         <is>
@@ -6415,12 +6415,12 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>User-22</t>
+          <t>User-31</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
@@ -6437,7 +6437,7 @@
         <v>200</v>
       </c>
       <c r="G151" s="4" t="n">
-        <v>67.95999999999999</v>
+        <v>53.3</v>
       </c>
       <c r="H151" s="7" t="inlineStr">
         <is>
@@ -6451,29 +6451,29 @@
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>User-25</t>
+          <t>User-57</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F152" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G152" s="4" t="n">
-        <v>85.81999999999999</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="H152" s="7" t="inlineStr">
         <is>
@@ -6487,29 +6487,29 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>User-69</t>
+          <t>User-67</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F153" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G153" s="4" t="n">
-        <v>79.26000000000001</v>
+        <v>85.66</v>
       </c>
       <c r="H153" s="7" t="inlineStr">
         <is>
@@ -6523,29 +6523,29 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>User-6</t>
+          <t>User-81</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F154" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G154" s="4" t="n">
-        <v>42.64</v>
+        <v>45.16</v>
       </c>
       <c r="H154" s="7" t="inlineStr">
         <is>
@@ -6559,29 +6559,29 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>User-95</t>
+          <t>User-67</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F155" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G155" s="4" t="n">
-        <v>5.24</v>
+        <v>88.64</v>
       </c>
       <c r="H155" s="7" t="inlineStr">
         <is>
@@ -6595,12 +6595,12 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>User-46</t>
+          <t>User-40</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
@@ -6617,7 +6617,7 @@
         <v>200</v>
       </c>
       <c r="G156" s="4" t="n">
-        <v>84.09999999999999</v>
+        <v>79.64</v>
       </c>
       <c r="H156" s="7" t="inlineStr">
         <is>
@@ -6631,12 +6631,12 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>User-32</t>
+          <t>User-46</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
@@ -6653,7 +6653,7 @@
         <v>200</v>
       </c>
       <c r="G157" s="4" t="n">
-        <v>30.34</v>
+        <v>42.79</v>
       </c>
       <c r="H157" s="7" t="inlineStr">
         <is>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>User-22</t>
+          <t>User-21</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
@@ -6689,7 +6689,7 @@
         <v>200</v>
       </c>
       <c r="G158" s="4" t="n">
-        <v>83.04000000000001</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="H158" s="7" t="inlineStr">
         <is>
@@ -6703,12 +6703,12 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>User-33</t>
+          <t>User-78</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
@@ -6725,7 +6725,7 @@
         <v>200</v>
       </c>
       <c r="G159" s="4" t="n">
-        <v>20.21</v>
+        <v>43.24</v>
       </c>
       <c r="H159" s="7" t="inlineStr">
         <is>
@@ -6739,29 +6739,29 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>User-20</t>
+          <t>User-49</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F160" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G160" s="4" t="n">
-        <v>14.71</v>
+        <v>39.94</v>
       </c>
       <c r="H160" s="7" t="inlineStr">
         <is>
@@ -6775,12 +6775,12 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>User-30</t>
+          <t>User-32</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
@@ -6797,7 +6797,7 @@
         <v>200</v>
       </c>
       <c r="G161" s="4" t="n">
-        <v>77.34999999999999</v>
+        <v>40.36</v>
       </c>
       <c r="H161" s="7" t="inlineStr">
         <is>
@@ -6811,29 +6811,29 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>User-25</t>
+          <t>User-98</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F162" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G162" s="4" t="n">
-        <v>82.61</v>
+        <v>25.91</v>
       </c>
       <c r="H162" s="7" t="inlineStr">
         <is>
@@ -6847,12 +6847,12 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>User-19</t>
+          <t>User-77</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
@@ -6869,7 +6869,7 @@
         <v>200</v>
       </c>
       <c r="G163" s="4" t="n">
-        <v>65.84999999999999</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="H163" s="7" t="inlineStr">
         <is>
@@ -6883,29 +6883,29 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>User-19</t>
+          <t>User-23</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F164" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G164" s="4" t="n">
-        <v>79.65000000000001</v>
+        <v>45.83</v>
       </c>
       <c r="H164" s="7" t="inlineStr">
         <is>
@@ -6919,29 +6919,29 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>User-21</t>
+          <t>User-92</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F165" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G165" s="4" t="n">
-        <v>81.87</v>
+        <v>75.88</v>
       </c>
       <c r="H165" s="7" t="inlineStr">
         <is>
@@ -6955,12 +6955,12 @@
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>User-5</t>
+          <t>User-55</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
@@ -6977,7 +6977,7 @@
         <v>200</v>
       </c>
       <c r="G166" s="4" t="n">
-        <v>9.15</v>
+        <v>25.89</v>
       </c>
       <c r="H166" s="7" t="inlineStr">
         <is>
@@ -6991,29 +6991,29 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>User-98</t>
+          <t>User-14</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F167" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G167" s="4" t="n">
-        <v>22.73</v>
+        <v>79.05</v>
       </c>
       <c r="H167" s="7" t="inlineStr">
         <is>
@@ -7027,12 +7027,12 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>User-60</t>
+          <t>User-55</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
@@ -7049,7 +7049,7 @@
         <v>200</v>
       </c>
       <c r="G168" s="4" t="n">
-        <v>59.79</v>
+        <v>62.85</v>
       </c>
       <c r="H168" s="7" t="inlineStr">
         <is>
@@ -7063,29 +7063,29 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>User-67</t>
+          <t>User-9</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F169" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G169" s="4" t="n">
-        <v>37.93</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="H169" s="7" t="inlineStr">
         <is>
@@ -7099,29 +7099,29 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>User-74</t>
+          <t>User-32</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F170" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G170" s="4" t="n">
-        <v>83.59999999999999</v>
+        <v>57.58</v>
       </c>
       <c r="H170" s="7" t="inlineStr">
         <is>
@@ -7135,12 +7135,12 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>User-43</t>
+          <t>User-72</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
@@ -7157,7 +7157,7 @@
         <v>200</v>
       </c>
       <c r="G171" s="4" t="n">
-        <v>59.86</v>
+        <v>74.94</v>
       </c>
       <c r="H171" s="7" t="inlineStr">
         <is>
@@ -7171,29 +7171,29 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>User-13</t>
+          <t>User-4</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F172" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G172" s="4" t="n">
-        <v>40.78</v>
+        <v>54.77</v>
       </c>
       <c r="H172" s="7" t="inlineStr">
         <is>
@@ -7207,29 +7207,29 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>User-77</t>
+          <t>User-3</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F173" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G173" s="4" t="n">
-        <v>31.18</v>
+        <v>17.13</v>
       </c>
       <c r="H173" s="7" t="inlineStr">
         <is>
@@ -7243,29 +7243,29 @@
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>User-87</t>
+          <t>User-44</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F174" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G174" s="4" t="n">
-        <v>27.42</v>
+        <v>81.47</v>
       </c>
       <c r="H174" s="7" t="inlineStr">
         <is>
@@ -7279,29 +7279,29 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>User-33</t>
+          <t>User-79</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F175" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G175" s="4" t="n">
-        <v>80.11</v>
+        <v>15.66</v>
       </c>
       <c r="H175" s="7" t="inlineStr">
         <is>
@@ -7315,29 +7315,29 @@
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>User-1</t>
+          <t>User-26</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F176" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G176" s="4" t="n">
-        <v>11.21</v>
+        <v>44.07</v>
       </c>
       <c r="H176" s="7" t="inlineStr">
         <is>
@@ -7351,29 +7351,29 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>User-27</t>
+          <t>User-42</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F177" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G177" s="4" t="n">
-        <v>68.16</v>
+        <v>12.64</v>
       </c>
       <c r="H177" s="7" t="inlineStr">
         <is>
@@ -7387,12 +7387,12 @@
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>User-84</t>
+          <t>User-55</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
@@ -7409,7 +7409,7 @@
         <v>200</v>
       </c>
       <c r="G178" s="4" t="n">
-        <v>63.67</v>
+        <v>49.35</v>
       </c>
       <c r="H178" s="7" t="inlineStr">
         <is>
@@ -7423,29 +7423,29 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>User-14</t>
+          <t>User-6</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F179" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G179" s="4" t="n">
-        <v>94.38</v>
+        <v>18.04</v>
       </c>
       <c r="H179" s="7" t="inlineStr">
         <is>
@@ -7459,29 +7459,29 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>User-27</t>
+          <t>User-20</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F180" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G180" s="4" t="n">
-        <v>81.18000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H180" s="7" t="inlineStr">
         <is>
@@ -7495,29 +7495,29 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>User-4</t>
+          <t>User-27</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F181" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G181" s="4" t="n">
-        <v>29.18</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="H181" s="7" t="inlineStr">
         <is>
@@ -7531,29 +7531,29 @@
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>User-58</t>
+          <t>User-31</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F182" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G182" s="4" t="n">
-        <v>59.04</v>
+        <v>34.32</v>
       </c>
       <c r="H182" s="7" t="inlineStr">
         <is>
@@ -7567,29 +7567,29 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>User-21</t>
+          <t>User-66</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F183" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G183" s="4" t="n">
-        <v>25.82</v>
+        <v>46.58</v>
       </c>
       <c r="H183" s="7" t="inlineStr">
         <is>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>User-74</t>
+          <t>User-66</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
@@ -7625,7 +7625,7 @@
         <v>200</v>
       </c>
       <c r="G184" s="4" t="n">
-        <v>31.09</v>
+        <v>22.61</v>
       </c>
       <c r="H184" s="7" t="inlineStr">
         <is>
@@ -7639,29 +7639,29 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>User-3</t>
+          <t>User-4</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F185" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G185" s="4" t="n">
-        <v>11.29</v>
+        <v>32.23</v>
       </c>
       <c r="H185" s="7" t="inlineStr">
         <is>
@@ -7675,12 +7675,12 @@
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>User-76</t>
+          <t>User-25</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
@@ -7697,7 +7697,7 @@
         <v>200</v>
       </c>
       <c r="G186" s="4" t="n">
-        <v>33.43</v>
+        <v>39.21</v>
       </c>
       <c r="H186" s="7" t="inlineStr">
         <is>
@@ -7711,29 +7711,29 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>User-7</t>
+          <t>User-97</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F187" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G187" s="4" t="n">
-        <v>85.06</v>
+        <v>46.53</v>
       </c>
       <c r="H187" s="7" t="inlineStr">
         <is>
@@ -7747,29 +7747,29 @@
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>User-9</t>
+          <t>User-82</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F188" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G188" s="4" t="n">
-        <v>44.03</v>
+        <v>53.31</v>
       </c>
       <c r="H188" s="7" t="inlineStr">
         <is>
@@ -7783,29 +7783,29 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>User-79</t>
+          <t>User-46</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F189" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G189" s="4" t="n">
-        <v>85.2</v>
+        <v>17.53</v>
       </c>
       <c r="H189" s="7" t="inlineStr">
         <is>
@@ -7819,29 +7819,29 @@
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>User-92</t>
+          <t>User-11</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E190" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F190" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G190" s="4" t="n">
-        <v>11.67</v>
+        <v>55.46</v>
       </c>
       <c r="H190" s="7" t="inlineStr">
         <is>
@@ -7855,29 +7855,29 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>User-22</t>
+          <t>User-52</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F191" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G191" s="4" t="n">
-        <v>40.91</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="H191" s="7" t="inlineStr">
         <is>
@@ -7891,12 +7891,12 @@
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>User-12</t>
+          <t>User-19</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
@@ -7913,7 +7913,7 @@
         <v>200</v>
       </c>
       <c r="G192" s="4" t="n">
-        <v>71.02</v>
+        <v>89.66</v>
       </c>
       <c r="H192" s="7" t="inlineStr">
         <is>
@@ -7927,29 +7927,29 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>User-53</t>
+          <t>User-48</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F193" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G193" s="4" t="n">
-        <v>36.7</v>
+        <v>33.2</v>
       </c>
       <c r="H193" s="7" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
@@ -7973,19 +7973,19 @@
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F194" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G194" s="4" t="n">
-        <v>7.89</v>
+        <v>80.3</v>
       </c>
       <c r="H194" s="7" t="inlineStr">
         <is>
@@ -7999,29 +7999,29 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>User-54</t>
+          <t>User-13</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F195" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G195" s="4" t="n">
-        <v>31.19</v>
+        <v>87.73</v>
       </c>
       <c r="H195" s="7" t="inlineStr">
         <is>
@@ -8035,29 +8035,29 @@
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>User-50</t>
+          <t>User-74</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F196" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G196" s="4" t="n">
-        <v>70.36</v>
+        <v>32.97</v>
       </c>
       <c r="H196" s="7" t="inlineStr">
         <is>
@@ -8071,29 +8071,29 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>User-46</t>
+          <t>User-20</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F197" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G197" s="4" t="n">
-        <v>93.53</v>
+        <v>12.83</v>
       </c>
       <c r="H197" s="7" t="inlineStr">
         <is>
@@ -8107,12 +8107,12 @@
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>User-65</t>
+          <t>User-93</t>
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
@@ -8129,7 +8129,7 @@
         <v>200</v>
       </c>
       <c r="G198" s="4" t="n">
-        <v>34.72</v>
+        <v>34.44</v>
       </c>
       <c r="H198" s="7" t="inlineStr">
         <is>
@@ -8143,29 +8143,29 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>User-43</t>
+          <t>User-21</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F199" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G199" s="4" t="n">
-        <v>47.61</v>
+        <v>35.6</v>
       </c>
       <c r="H199" s="7" t="inlineStr">
         <is>
@@ -8179,12 +8179,12 @@
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>User-20</t>
+          <t>User-33</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
@@ -8201,7 +8201,7 @@
         <v>200</v>
       </c>
       <c r="G200" s="4" t="n">
-        <v>68.56999999999999</v>
+        <v>90.97</v>
       </c>
       <c r="H200" s="7" t="inlineStr">
         <is>
@@ -8215,12 +8215,12 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>User-65</t>
+          <t>User-58</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
@@ -8237,7 +8237,7 @@
         <v>200</v>
       </c>
       <c r="G201" s="4" t="n">
-        <v>75.25</v>
+        <v>5.48</v>
       </c>
       <c r="H201" s="7" t="inlineStr">
         <is>
@@ -8251,29 +8251,29 @@
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>User-84</t>
+          <t>User-55</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E202" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F202" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G202" s="4" t="n">
-        <v>52.21</v>
+        <v>40.68</v>
       </c>
       <c r="H202" s="7" t="inlineStr">
         <is>
@@ -8287,29 +8287,29 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>User-44</t>
+          <t>User-6</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F203" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G203" s="4" t="n">
-        <v>38.31</v>
+        <v>15.66</v>
       </c>
       <c r="H203" s="7" t="inlineStr">
         <is>
@@ -8323,29 +8323,29 @@
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>User-66</t>
+          <t>User-71</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E204" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F204" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G204" s="4" t="n">
-        <v>76.47</v>
+        <v>50.36</v>
       </c>
       <c r="H204" s="7" t="inlineStr">
         <is>
@@ -8359,12 +8359,12 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>User-2</t>
+          <t>User-51</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
@@ -8381,7 +8381,7 @@
         <v>200</v>
       </c>
       <c r="G205" s="4" t="n">
-        <v>5.88</v>
+        <v>59.3</v>
       </c>
       <c r="H205" s="7" t="inlineStr">
         <is>
@@ -8395,29 +8395,29 @@
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>User-65</t>
+          <t>User-28</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F206" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G206" s="4" t="n">
-        <v>86.13</v>
+        <v>14.19</v>
       </c>
       <c r="H206" s="7" t="inlineStr">
         <is>
@@ -8431,29 +8431,29 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>User-46</t>
+          <t>User-7</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F207" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G207" s="4" t="n">
-        <v>72.13</v>
+        <v>39.11</v>
       </c>
       <c r="H207" s="7" t="inlineStr">
         <is>
@@ -8467,29 +8467,29 @@
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>User-80</t>
+          <t>User-100</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E208" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F208" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G208" s="4" t="n">
-        <v>43.13</v>
+        <v>39.27</v>
       </c>
       <c r="H208" s="7" t="inlineStr">
         <is>
@@ -8503,29 +8503,29 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>User-79</t>
+          <t>User-64</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F209" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G209" s="4" t="n">
-        <v>19.73</v>
+        <v>92.55</v>
       </c>
       <c r="H209" s="7" t="inlineStr">
         <is>
@@ -8539,29 +8539,29 @@
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>User-92</t>
+          <t>User-32</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F210" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G210" s="4" t="n">
-        <v>82.06999999999999</v>
+        <v>53.34</v>
       </c>
       <c r="H210" s="7" t="inlineStr">
         <is>
@@ -8575,29 +8575,29 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>User-29</t>
+          <t>User-88</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F211" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G211" s="4" t="n">
-        <v>30.98</v>
+        <v>62.34</v>
       </c>
       <c r="H211" s="7" t="inlineStr">
         <is>
@@ -8611,29 +8611,29 @@
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>User-81</t>
+          <t>User-44</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E212" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F212" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G212" s="4" t="n">
-        <v>64.44</v>
+        <v>92.01000000000001</v>
       </c>
       <c r="H212" s="7" t="inlineStr">
         <is>
@@ -8647,12 +8647,12 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.281</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>User-95</t>
+          <t>User-94</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
@@ -8669,7 +8669,7 @@
         <v>200</v>
       </c>
       <c r="G213" s="4" t="n">
-        <v>45.16</v>
+        <v>34.44</v>
       </c>
       <c r="H213" s="7" t="inlineStr">
         <is>
@@ -8683,29 +8683,29 @@
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>User-18</t>
+          <t>User-38</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E214" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F214" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G214" s="4" t="n">
-        <v>57.76</v>
+        <v>41.92</v>
       </c>
       <c r="H214" s="7" t="inlineStr">
         <is>
@@ -8719,29 +8719,29 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>User-79</t>
+          <t>User-97</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F215" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G215" s="4" t="n">
-        <v>39.95</v>
+        <v>62.03</v>
       </c>
       <c r="H215" s="7" t="inlineStr">
         <is>
@@ -8755,29 +8755,29 @@
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>User-10</t>
+          <t>User-97</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E216" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F216" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G216" s="4" t="n">
-        <v>5.95</v>
+        <v>84.06</v>
       </c>
       <c r="H216" s="7" t="inlineStr">
         <is>
@@ -8791,29 +8791,29 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>User-90</t>
+          <t>User-88</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E217" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F217" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G217" s="4" t="n">
-        <v>59.5</v>
+        <v>83.09</v>
       </c>
       <c r="H217" s="7" t="inlineStr">
         <is>
@@ -8827,29 +8827,29 @@
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>User-44</t>
+          <t>User-89</t>
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E218" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F218" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G218" s="4" t="n">
-        <v>53.58</v>
+        <v>84.56</v>
       </c>
       <c r="H218" s="7" t="inlineStr">
         <is>
@@ -8863,29 +8863,29 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>User-60</t>
+          <t>User-37</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E219" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F219" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G219" s="4" t="n">
-        <v>39.61</v>
+        <v>42.04</v>
       </c>
       <c r="H219" s="7" t="inlineStr">
         <is>
@@ -8899,29 +8899,29 @@
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>User-6</t>
+          <t>User-38</t>
         </is>
       </c>
       <c r="D220" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E220" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F220" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G220" s="4" t="n">
-        <v>58.47</v>
+        <v>5.12</v>
       </c>
       <c r="H220" s="7" t="inlineStr">
         <is>
@@ -8935,29 +8935,29 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>User-98</t>
+          <t>User-43</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E221" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F221" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G221" s="4" t="n">
-        <v>80.31999999999999</v>
+        <v>61.75</v>
       </c>
       <c r="H221" s="7" t="inlineStr">
         <is>
@@ -8971,29 +8971,29 @@
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C222" s="4" t="inlineStr">
         <is>
-          <t>User-23</t>
+          <t>User-76</t>
         </is>
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E222" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F222" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G222" s="4" t="n">
-        <v>36.19</v>
+        <v>27.61</v>
       </c>
       <c r="H222" s="7" t="inlineStr">
         <is>
@@ -9007,29 +9007,29 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>User-72</t>
+          <t>User-19</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E223" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F223" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G223" s="4" t="n">
-        <v>11.46</v>
+        <v>32.24</v>
       </c>
       <c r="H223" s="7" t="inlineStr">
         <is>
@@ -9043,29 +9043,29 @@
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>User-20</t>
+          <t>User-99</t>
         </is>
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E224" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F224" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G224" s="4" t="n">
-        <v>47.48</v>
+        <v>55.63</v>
       </c>
       <c r="H224" s="7" t="inlineStr">
         <is>
@@ -9079,29 +9079,29 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>User-73</t>
+          <t>User-7</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E225" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F225" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G225" s="4" t="n">
-        <v>45.5</v>
+        <v>80.75</v>
       </c>
       <c r="H225" s="7" t="inlineStr">
         <is>
@@ -9115,29 +9115,29 @@
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>User-54</t>
+          <t>User-43</t>
         </is>
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E226" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F226" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G226" s="4" t="n">
-        <v>8.1</v>
+        <v>60.15</v>
       </c>
       <c r="H226" s="7" t="inlineStr">
         <is>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>User-24</t>
+          <t>User-36</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
@@ -9173,7 +9173,7 @@
         <v>200</v>
       </c>
       <c r="G227" s="4" t="n">
-        <v>54.86</v>
+        <v>28.36</v>
       </c>
       <c r="H227" s="7" t="inlineStr">
         <is>
@@ -9187,29 +9187,29 @@
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>User-26</t>
+          <t>User-1</t>
         </is>
       </c>
       <c r="D228" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E228" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F228" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G228" s="4" t="n">
-        <v>46.92</v>
+        <v>88.37</v>
       </c>
       <c r="H228" s="7" t="inlineStr">
         <is>
@@ -9223,29 +9223,29 @@
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>User-39</t>
+          <t>User-16</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E229" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F229" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G229" s="4" t="n">
-        <v>91.64</v>
+        <v>51.05</v>
       </c>
       <c r="H229" s="7" t="inlineStr">
         <is>
@@ -9259,29 +9259,29 @@
       </c>
       <c r="B230" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C230" s="4" t="inlineStr">
         <is>
-          <t>User-53</t>
+          <t>User-11</t>
         </is>
       </c>
       <c r="D230" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E230" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F230" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G230" s="4" t="n">
-        <v>21.84</v>
+        <v>46.88</v>
       </c>
       <c r="H230" s="7" t="inlineStr">
         <is>
@@ -9295,29 +9295,29 @@
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>User-25</t>
+          <t>User-2</t>
         </is>
       </c>
       <c r="D231" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E231" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F231" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G231" s="4" t="n">
-        <v>26.97</v>
+        <v>5.41</v>
       </c>
       <c r="H231" s="7" t="inlineStr">
         <is>
@@ -9331,29 +9331,29 @@
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>User-21</t>
+          <t>User-90</t>
         </is>
       </c>
       <c r="D232" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E232" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F232" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G232" s="4" t="n">
-        <v>85</v>
+        <v>32.03</v>
       </c>
       <c r="H232" s="7" t="inlineStr">
         <is>
@@ -9367,29 +9367,29 @@
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>User-100</t>
+          <t>User-56</t>
         </is>
       </c>
       <c r="D233" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E233" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F233" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G233" s="4" t="n">
-        <v>46.32</v>
+        <v>63.02</v>
       </c>
       <c r="H233" s="7" t="inlineStr">
         <is>
@@ -9403,12 +9403,12 @@
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>User-63</t>
+          <t>User-41</t>
         </is>
       </c>
       <c r="D234" s="4" t="inlineStr">
@@ -9425,7 +9425,7 @@
         <v>200</v>
       </c>
       <c r="G234" s="4" t="n">
-        <v>61.48</v>
+        <v>15.34</v>
       </c>
       <c r="H234" s="7" t="inlineStr">
         <is>
@@ -9439,29 +9439,29 @@
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>User-26</t>
+          <t>User-35</t>
         </is>
       </c>
       <c r="D235" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E235" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F235" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G235" s="4" t="n">
-        <v>23.17</v>
+        <v>35.38</v>
       </c>
       <c r="H235" s="7" t="inlineStr">
         <is>
@@ -9475,29 +9475,29 @@
       </c>
       <c r="B236" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>User-73</t>
+          <t>User-13</t>
         </is>
       </c>
       <c r="D236" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E236" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F236" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G236" s="4" t="n">
-        <v>71.48999999999999</v>
+        <v>42.48</v>
       </c>
       <c r="H236" s="7" t="inlineStr">
         <is>
@@ -9511,29 +9511,29 @@
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>User-35</t>
+          <t>User-18</t>
         </is>
       </c>
       <c r="D237" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E237" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F237" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G237" s="4" t="n">
-        <v>59.17</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="H237" s="7" t="inlineStr">
         <is>
@@ -9547,29 +9547,29 @@
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>User-23</t>
+          <t>User-43</t>
         </is>
       </c>
       <c r="D238" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E238" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F238" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G238" s="4" t="n">
-        <v>39.9</v>
+        <v>71.55</v>
       </c>
       <c r="H238" s="7" t="inlineStr">
         <is>
@@ -9583,29 +9583,29 @@
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>User-92</t>
+          <t>User-72</t>
         </is>
       </c>
       <c r="D239" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E239" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F239" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G239" s="4" t="n">
-        <v>38.82</v>
+        <v>26.38</v>
       </c>
       <c r="H239" s="7" t="inlineStr">
         <is>
@@ -9619,29 +9619,29 @@
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>User-36</t>
+          <t>User-34</t>
         </is>
       </c>
       <c r="D240" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E240" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F240" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G240" s="4" t="n">
-        <v>90.56999999999999</v>
+        <v>80.17</v>
       </c>
       <c r="H240" s="7" t="inlineStr">
         <is>
@@ -9655,29 +9655,29 @@
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>User-63</t>
+          <t>User-58</t>
         </is>
       </c>
       <c r="D241" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E241" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F241" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G241" s="4" t="n">
-        <v>45.21</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="H241" s="7" t="inlineStr">
         <is>
@@ -9691,12 +9691,12 @@
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>User-37</t>
+          <t>User-69</t>
         </is>
       </c>
       <c r="D242" s="4" t="inlineStr">
@@ -9713,7 +9713,7 @@
         <v>200</v>
       </c>
       <c r="G242" s="4" t="n">
-        <v>13.03</v>
+        <v>61.37</v>
       </c>
       <c r="H242" s="7" t="inlineStr">
         <is>
@@ -9727,29 +9727,29 @@
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>User-73</t>
+          <t>User-14</t>
         </is>
       </c>
       <c r="D243" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E243" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F243" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G243" s="4" t="n">
-        <v>73.20999999999999</v>
+        <v>15.1</v>
       </c>
       <c r="H243" s="7" t="inlineStr">
         <is>
@@ -9763,29 +9763,29 @@
       </c>
       <c r="B244" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>User-28</t>
+          <t>User-81</t>
         </is>
       </c>
       <c r="D244" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E244" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F244" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G244" s="4" t="n">
-        <v>83.19</v>
+        <v>30.77</v>
       </c>
       <c r="H244" s="7" t="inlineStr">
         <is>
@@ -9799,29 +9799,29 @@
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>User-55</t>
+          <t>User-28</t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E245" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F245" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G245" s="4" t="n">
-        <v>58.06</v>
+        <v>44.51</v>
       </c>
       <c r="H245" s="7" t="inlineStr">
         <is>
@@ -9835,29 +9835,29 @@
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>User-3</t>
+          <t>User-10</t>
         </is>
       </c>
       <c r="D246" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E246" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F246" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G246" s="4" t="n">
-        <v>45.44</v>
+        <v>7.43</v>
       </c>
       <c r="H246" s="7" t="inlineStr">
         <is>
@@ -9871,12 +9871,12 @@
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>User-24</t>
+          <t>User-93</t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr">
@@ -9893,7 +9893,7 @@
         <v>200</v>
       </c>
       <c r="G247" s="4" t="n">
-        <v>77.84999999999999</v>
+        <v>37.04</v>
       </c>
       <c r="H247" s="7" t="inlineStr">
         <is>
@@ -9907,12 +9907,12 @@
       </c>
       <c r="B248" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>User-13</t>
+          <t>User-71</t>
         </is>
       </c>
       <c r="D248" s="4" t="inlineStr">
@@ -9929,7 +9929,7 @@
         <v>200</v>
       </c>
       <c r="G248" s="4" t="n">
-        <v>55.66</v>
+        <v>79.28</v>
       </c>
       <c r="H248" s="7" t="inlineStr">
         <is>
@@ -9943,29 +9943,29 @@
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>User-6</t>
+          <t>User-14</t>
         </is>
       </c>
       <c r="D249" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E249" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F249" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G249" s="4" t="n">
-        <v>44.25</v>
+        <v>78.84</v>
       </c>
       <c r="H249" s="7" t="inlineStr">
         <is>
@@ -9979,29 +9979,29 @@
       </c>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>User-13</t>
+          <t>User-80</t>
         </is>
       </c>
       <c r="D250" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E250" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F250" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G250" s="4" t="n">
-        <v>47.59</v>
+        <v>51.31</v>
       </c>
       <c r="H250" s="7" t="inlineStr">
         <is>
@@ -10015,29 +10015,29 @@
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>User-4</t>
+          <t>User-79</t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E251" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F251" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G251" s="4" t="n">
-        <v>31.11</v>
+        <v>36.42</v>
       </c>
       <c r="H251" s="7" t="inlineStr">
         <is>
@@ -10051,29 +10051,29 @@
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>User-47</t>
+          <t>User-59</t>
         </is>
       </c>
       <c r="D252" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E252" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F252" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G252" s="4" t="n">
-        <v>64.29000000000001</v>
+        <v>29.38</v>
       </c>
       <c r="H252" s="7" t="inlineStr">
         <is>
@@ -10087,12 +10087,12 @@
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>User-5</t>
+          <t>User-98</t>
         </is>
       </c>
       <c r="D253" s="4" t="inlineStr">
@@ -10109,7 +10109,7 @@
         <v>200</v>
       </c>
       <c r="G253" s="4" t="n">
-        <v>46.85</v>
+        <v>16.18</v>
       </c>
       <c r="H253" s="7" t="inlineStr">
         <is>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>User-31</t>
+          <t>User-79</t>
         </is>
       </c>
       <c r="D254" s="4" t="inlineStr">
@@ -10145,7 +10145,7 @@
         <v>200</v>
       </c>
       <c r="G254" s="4" t="n">
-        <v>65.23999999999999</v>
+        <v>31.82</v>
       </c>
       <c r="H254" s="7" t="inlineStr">
         <is>
@@ -10159,29 +10159,29 @@
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>User-58</t>
+          <t>User-88</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E255" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F255" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G255" s="4" t="n">
-        <v>7.6</v>
+        <v>26.2</v>
       </c>
       <c r="H255" s="7" t="inlineStr">
         <is>
@@ -10195,29 +10195,29 @@
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>User-81</t>
+          <t>User-67</t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E256" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F256" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G256" s="4" t="n">
-        <v>86.90000000000001</v>
+        <v>88.25</v>
       </c>
       <c r="H256" s="7" t="inlineStr">
         <is>
@@ -10231,29 +10231,29 @@
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>User-69</t>
+          <t>User-41</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E257" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F257" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G257" s="4" t="n">
-        <v>47.3</v>
+        <v>87.5</v>
       </c>
       <c r="H257" s="7" t="inlineStr">
         <is>
@@ -10267,29 +10267,29 @@
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>User-1</t>
+          <t>User-71</t>
         </is>
       </c>
       <c r="D258" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E258" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F258" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G258" s="4" t="n">
-        <v>73.75</v>
+        <v>50.57</v>
       </c>
       <c r="H258" s="7" t="inlineStr">
         <is>
@@ -10303,29 +10303,29 @@
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>User-71</t>
+          <t>User-31</t>
         </is>
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E259" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F259" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G259" s="4" t="n">
-        <v>89.87</v>
+        <v>50.58</v>
       </c>
       <c r="H259" s="7" t="inlineStr">
         <is>
@@ -10339,29 +10339,29 @@
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>User-50</t>
+          <t>User-49</t>
         </is>
       </c>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E260" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F260" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G260" s="4" t="n">
-        <v>40.76</v>
+        <v>84.69</v>
       </c>
       <c r="H260" s="7" t="inlineStr">
         <is>
@@ -10375,29 +10375,29 @@
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>User-50</t>
+          <t>User-34</t>
         </is>
       </c>
       <c r="D261" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E261" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F261" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G261" s="4" t="n">
-        <v>21.51</v>
+        <v>72.27</v>
       </c>
       <c r="H261" s="7" t="inlineStr">
         <is>
@@ -10411,29 +10411,29 @@
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>User-67</t>
+          <t>User-72</t>
         </is>
       </c>
       <c r="D262" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E262" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F262" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G262" s="4" t="n">
-        <v>11.09</v>
+        <v>75.84</v>
       </c>
       <c r="H262" s="7" t="inlineStr">
         <is>
@@ -10447,12 +10447,12 @@
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>User-57</t>
+          <t>User-45</t>
         </is>
       </c>
       <c r="D263" s="4" t="inlineStr">
@@ -10469,7 +10469,7 @@
         <v>200</v>
       </c>
       <c r="G263" s="4" t="n">
-        <v>36.41</v>
+        <v>16.18</v>
       </c>
       <c r="H263" s="7" t="inlineStr">
         <is>
@@ -10483,12 +10483,12 @@
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>User-23</t>
+          <t>User-28</t>
         </is>
       </c>
       <c r="D264" s="4" t="inlineStr">
@@ -10505,7 +10505,7 @@
         <v>200</v>
       </c>
       <c r="G264" s="4" t="n">
-        <v>8.050000000000001</v>
+        <v>69.28</v>
       </c>
       <c r="H264" s="7" t="inlineStr">
         <is>
@@ -10519,29 +10519,29 @@
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>User-94</t>
+          <t>User-99</t>
         </is>
       </c>
       <c r="D265" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E265" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F265" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G265" s="4" t="n">
-        <v>88.31</v>
+        <v>75.81</v>
       </c>
       <c r="H265" s="7" t="inlineStr">
         <is>
@@ -10555,29 +10555,29 @@
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>User-92</t>
+          <t>User-90</t>
         </is>
       </c>
       <c r="D266" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E266" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F266" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G266" s="4" t="n">
-        <v>42.77</v>
+        <v>32.96</v>
       </c>
       <c r="H266" s="7" t="inlineStr">
         <is>
@@ -10591,29 +10591,29 @@
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>User-63</t>
+          <t>User-42</t>
         </is>
       </c>
       <c r="D267" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E267" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F267" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G267" s="4" t="n">
-        <v>82.97</v>
+        <v>86.73</v>
       </c>
       <c r="H267" s="7" t="inlineStr">
         <is>
@@ -10627,29 +10627,29 @@
       </c>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>User-54</t>
+          <t>User-10</t>
         </is>
       </c>
       <c r="D268" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E268" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F268" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G268" s="4" t="n">
-        <v>16.79</v>
+        <v>71.03</v>
       </c>
       <c r="H268" s="7" t="inlineStr">
         <is>
@@ -10663,12 +10663,12 @@
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>User-50</t>
+          <t>User-4</t>
         </is>
       </c>
       <c r="D269" s="4" t="inlineStr">
@@ -10685,7 +10685,7 @@
         <v>200</v>
       </c>
       <c r="G269" s="4" t="n">
-        <v>20.87</v>
+        <v>80.56</v>
       </c>
       <c r="H269" s="7" t="inlineStr">
         <is>
@@ -10699,29 +10699,29 @@
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>User-49</t>
+          <t>User-19</t>
         </is>
       </c>
       <c r="D270" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E270" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F270" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G270" s="4" t="n">
-        <v>91.98</v>
+        <v>59.61</v>
       </c>
       <c r="H270" s="7" t="inlineStr">
         <is>
@@ -10735,29 +10735,29 @@
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>User-63</t>
+          <t>User-72</t>
         </is>
       </c>
       <c r="D271" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E271" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F271" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G271" s="4" t="n">
-        <v>7.91</v>
+        <v>40.65</v>
       </c>
       <c r="H271" s="7" t="inlineStr">
         <is>
@@ -10771,29 +10771,29 @@
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>User-93</t>
+          <t>User-43</t>
         </is>
       </c>
       <c r="D272" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E272" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F272" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G272" s="4" t="n">
-        <v>45.08</v>
+        <v>73.55</v>
       </c>
       <c r="H272" s="7" t="inlineStr">
         <is>
@@ -10807,12 +10807,12 @@
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>User-28</t>
+          <t>User-100</t>
         </is>
       </c>
       <c r="D273" s="4" t="inlineStr">
@@ -10829,7 +10829,7 @@
         <v>200</v>
       </c>
       <c r="G273" s="4" t="n">
-        <v>76.72</v>
+        <v>33.93</v>
       </c>
       <c r="H273" s="7" t="inlineStr">
         <is>
@@ -10843,29 +10843,29 @@
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>User-2</t>
+          <t>User-5</t>
         </is>
       </c>
       <c r="D274" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E274" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F274" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G274" s="4" t="n">
-        <v>88</v>
+        <v>61.6</v>
       </c>
       <c r="H274" s="7" t="inlineStr">
         <is>
@@ -10879,29 +10879,29 @@
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>User-74</t>
+          <t>User-54</t>
         </is>
       </c>
       <c r="D275" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E275" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F275" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G275" s="4" t="n">
-        <v>5.96</v>
+        <v>52.15</v>
       </c>
       <c r="H275" s="7" t="inlineStr">
         <is>
@@ -10915,12 +10915,12 @@
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>User-87</t>
+          <t>User-17</t>
         </is>
       </c>
       <c r="D276" s="4" t="inlineStr">
@@ -10937,7 +10937,7 @@
         <v>200</v>
       </c>
       <c r="G276" s="4" t="n">
-        <v>39.52</v>
+        <v>22.04</v>
       </c>
       <c r="H276" s="7" t="inlineStr">
         <is>
@@ -10951,29 +10951,29 @@
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>User-79</t>
+          <t>User-54</t>
         </is>
       </c>
       <c r="D277" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E277" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F277" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G277" s="4" t="n">
-        <v>25.98</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="H277" s="7" t="inlineStr">
         <is>
@@ -10987,29 +10987,29 @@
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.683</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>User-43</t>
+          <t>User-28</t>
         </is>
       </c>
       <c r="D278" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E278" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F278" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G278" s="4" t="n">
-        <v>43.32</v>
+        <v>81.19</v>
       </c>
       <c r="H278" s="7" t="inlineStr">
         <is>
@@ -11023,29 +11023,29 @@
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.684</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>User-18</t>
+          <t>User-94</t>
         </is>
       </c>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E279" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F279" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G279" s="4" t="n">
-        <v>40.1</v>
+        <v>65.13</v>
       </c>
       <c r="H279" s="7" t="inlineStr">
         <is>
@@ -11059,12 +11059,12 @@
       </c>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.684</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C280" s="4" t="inlineStr">
         <is>
-          <t>User-58</t>
+          <t>User-47</t>
         </is>
       </c>
       <c r="D280" s="4" t="inlineStr">
@@ -11081,7 +11081,7 @@
         <v>200</v>
       </c>
       <c r="G280" s="4" t="n">
-        <v>30.09</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H280" s="7" t="inlineStr">
         <is>
@@ -11095,29 +11095,29 @@
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.684</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>User-70</t>
+          <t>User-56</t>
         </is>
       </c>
       <c r="D281" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E281" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F281" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G281" s="4" t="n">
-        <v>52.71</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H281" s="7" t="inlineStr">
         <is>
@@ -11131,29 +11131,29 @@
       </c>
       <c r="B282" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.684</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C282" s="4" t="inlineStr">
         <is>
-          <t>User-39</t>
+          <t>User-25</t>
         </is>
       </c>
       <c r="D282" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E282" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F282" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G282" s="4" t="n">
-        <v>79.61</v>
+        <v>27.59</v>
       </c>
       <c r="H282" s="7" t="inlineStr">
         <is>
@@ -11167,29 +11167,29 @@
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.684</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>User-82</t>
+          <t>User-2</t>
         </is>
       </c>
       <c r="D283" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E283" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F283" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G283" s="4" t="n">
-        <v>84.56999999999999</v>
+        <v>51.5</v>
       </c>
       <c r="H283" s="7" t="inlineStr">
         <is>
@@ -11203,29 +11203,29 @@
       </c>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.684</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>User-50</t>
+          <t>User-17</t>
         </is>
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E284" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F284" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G284" s="4" t="n">
-        <v>77</v>
+        <v>75.28</v>
       </c>
       <c r="H284" s="7" t="inlineStr">
         <is>
@@ -11239,29 +11239,29 @@
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.684</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>User-98</t>
+          <t>User-90</t>
         </is>
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E285" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F285" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G285" s="4" t="n">
-        <v>22.21</v>
+        <v>34.65</v>
       </c>
       <c r="H285" s="7" t="inlineStr">
         <is>
@@ -11275,12 +11275,12 @@
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.684</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>User-65</t>
+          <t>User-96</t>
         </is>
       </c>
       <c r="D286" s="4" t="inlineStr">
@@ -11297,7 +11297,7 @@
         <v>200</v>
       </c>
       <c r="G286" s="4" t="n">
-        <v>74.40000000000001</v>
+        <v>23.28</v>
       </c>
       <c r="H286" s="7" t="inlineStr">
         <is>
@@ -11311,29 +11311,29 @@
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.684</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>User-18</t>
+          <t>User-9</t>
         </is>
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Root Check</t>
         </is>
       </c>
       <c r="E287" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F287" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G287" s="4" t="n">
-        <v>67.48</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="H287" s="7" t="inlineStr">
         <is>
@@ -11347,12 +11347,12 @@
       </c>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.684</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>User-53</t>
+          <t>User-51</t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
@@ -11369,7 +11369,7 @@
         <v>200</v>
       </c>
       <c r="G288" s="4" t="n">
-        <v>13.32</v>
+        <v>55.13</v>
       </c>
       <c r="H288" s="7" t="inlineStr">
         <is>
@@ -11383,29 +11383,29 @@
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.684</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>User-48</t>
+          <t>User-18</t>
         </is>
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>Contacts List</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E289" s="4" t="inlineStr">
         <is>
-          <t>/contacts/user%40sentinel.com</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F289" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G289" s="4" t="n">
-        <v>11.72</v>
+        <v>67.97</v>
       </c>
       <c r="H289" s="7" t="inlineStr">
         <is>
@@ -11419,29 +11419,29 @@
       </c>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.684</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr">
         <is>
-          <t>User-99</t>
+          <t>User-79</t>
         </is>
       </c>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E290" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F290" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G290" s="4" t="n">
-        <v>62.38</v>
+        <v>31.23</v>
       </c>
       <c r="H290" s="7" t="inlineStr">
         <is>
@@ -11455,12 +11455,12 @@
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.684</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>User-46</t>
+          <t>User-14</t>
         </is>
       </c>
       <c r="D291" s="4" t="inlineStr">
@@ -11477,7 +11477,7 @@
         <v>200</v>
       </c>
       <c r="G291" s="4" t="n">
-        <v>25.9</v>
+        <v>46.31</v>
       </c>
       <c r="H291" s="7" t="inlineStr">
         <is>
@@ -11491,29 +11491,29 @@
       </c>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.684</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>User-13</t>
+          <t>User-55</t>
         </is>
       </c>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>Root Check</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="E292" s="4" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="F292" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G292" s="4" t="n">
-        <v>41.89</v>
+        <v>66.72</v>
       </c>
       <c r="H292" s="7" t="inlineStr">
         <is>
@@ -11527,29 +11527,29 @@
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.684</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>User-77</t>
+          <t>User-10</t>
         </is>
       </c>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Dashboard Stats</t>
         </is>
       </c>
       <c r="E293" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/dashboard/stats</t>
         </is>
       </c>
       <c r="F293" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G293" s="4" t="n">
-        <v>88.17</v>
+        <v>25.85</v>
       </c>
       <c r="H293" s="7" t="inlineStr">
         <is>
@@ -11563,29 +11563,29 @@
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.684</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>User-18</t>
+          <t>User-86</t>
         </is>
       </c>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E294" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F294" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G294" s="4" t="n">
-        <v>93.29000000000001</v>
+        <v>19.66</v>
       </c>
       <c r="H294" s="7" t="inlineStr">
         <is>
@@ -11599,12 +11599,12 @@
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.684</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>User-30</t>
+          <t>User-41</t>
         </is>
       </c>
       <c r="D295" s="4" t="inlineStr">
@@ -11621,7 +11621,7 @@
         <v>200</v>
       </c>
       <c r="G295" s="4" t="n">
-        <v>21.52</v>
+        <v>45.94</v>
       </c>
       <c r="H295" s="7" t="inlineStr">
         <is>
@@ -11635,29 +11635,29 @@
       </c>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.684</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C296" s="4" t="inlineStr">
         <is>
-          <t>User-59</t>
+          <t>User-23</t>
         </is>
       </c>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E296" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F296" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G296" s="4" t="n">
-        <v>37.94</v>
+        <v>64.84</v>
       </c>
       <c r="H296" s="7" t="inlineStr">
         <is>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.684</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>User-42</t>
+          <t>User-93</t>
         </is>
       </c>
       <c r="D297" s="4" t="inlineStr">
@@ -11693,7 +11693,7 @@
         <v>200</v>
       </c>
       <c r="G297" s="4" t="n">
-        <v>34.31</v>
+        <v>25.62</v>
       </c>
       <c r="H297" s="7" t="inlineStr">
         <is>
@@ -11707,29 +11707,29 @@
       </c>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.684</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>User-84</t>
+          <t>User-81</t>
         </is>
       </c>
       <c r="D298" s="4" t="inlineStr">
         <is>
-          <t>Active Emergencies</t>
+          <t>Contacts List</t>
         </is>
       </c>
       <c r="E298" s="4" t="inlineStr">
         <is>
-          <t>/emergency/active</t>
+          <t>/contacts/user%40sentinel.com</t>
         </is>
       </c>
       <c r="F298" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G298" s="4" t="n">
-        <v>18.71</v>
+        <v>87.45999999999999</v>
       </c>
       <c r="H298" s="7" t="inlineStr">
         <is>
@@ -11743,12 +11743,12 @@
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.684</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>User-42</t>
+          <t>User-12</t>
         </is>
       </c>
       <c r="D299" s="4" t="inlineStr">
@@ -11765,7 +11765,7 @@
         <v>200</v>
       </c>
       <c r="G299" s="4" t="n">
-        <v>81.23</v>
+        <v>46.82</v>
       </c>
       <c r="H299" s="7" t="inlineStr">
         <is>
@@ -11779,29 +11779,29 @@
       </c>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.684</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C300" s="4" t="inlineStr">
         <is>
-          <t>User-37</t>
+          <t>User-38</t>
         </is>
       </c>
       <c r="D300" s="4" t="inlineStr">
         <is>
-          <t>Health Check</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E300" s="4" t="inlineStr">
         <is>
-          <t>/health</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F300" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G300" s="4" t="n">
-        <v>39.56</v>
+        <v>22.8</v>
       </c>
       <c r="H300" s="7" t="inlineStr">
         <is>
@@ -11815,29 +11815,29 @@
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:33.684</t>
+          <t>2026-06-23 07:09:58.282</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>User-35</t>
+          <t>User-31</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
         <is>
-          <t>Dashboard Stats</t>
+          <t>Active Emergencies</t>
         </is>
       </c>
       <c r="E301" s="4" t="inlineStr">
         <is>
-          <t>/dashboard/stats</t>
+          <t>/emergency/active</t>
         </is>
       </c>
       <c r="F301" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G301" s="4" t="n">
-        <v>10.75</v>
+        <v>42.16</v>
       </c>
       <c r="H301" s="7" t="inlineStr">
         <is>
